--- a/EJEMPLO/evento PICANTE 29 06 2026cierre bodega.xlsx
+++ b/EJEMPLO/evento PICANTE 29 06 2026cierre bodega.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d22d8bc0accc0d32/Documentos/DAVID/PICANTE ESTRIDENTE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin17\Documents\barra david\barrapro\barrapro\EJEMPLO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="8_{4CE75D0F-4A21-4FE0-8CF8-078653255427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{251D80AE-FF31-4285-8E1C-90DA80D4288E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E477E0-3DBC-4739-9274-ED545AAF4A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BODEGA PRINCIPAL" sheetId="10" r:id="rId1"/>
@@ -32,15 +32,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="181">
   <si>
     <t>Producto</t>
   </si>
@@ -580,6 +577,9 @@
   </si>
   <si>
     <t>PROPINAS</t>
+  </si>
+  <si>
+    <t>wpp uniminuto</t>
   </si>
 </sst>
 </file>
@@ -1057,16 +1057,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+  <cellXfs count="103">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1074,7 +1074,7 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1087,21 +1087,21 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="4" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1111,9 +1111,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1141,9 +1139,7 @@
     <xf numFmtId="3" fontId="4" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1180,13 +1176,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="4" xfId="2" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1205,20 +1200,19 @@
     <xf numFmtId="8" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="6" fontId="13" fillId="16" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="13" fillId="16" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1230,58 +1224,57 @@
     <xf numFmtId="0" fontId="11" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="22" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="11" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
@@ -1303,10 +1296,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1560,25 +1549,25 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="46" t="s">
+      <c r="K1" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="L1" s="74" t="s">
+      <c r="L1" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="54"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56"/>
-      <c r="W1" s="56"/>
-      <c r="X1" s="56"/>
-      <c r="Y1" s="56"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="37"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="37"/>
     </row>
     <row r="2" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1592,26 +1581,26 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="75"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="81" t="s">
+      <c r="J2" s="55"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="75" t="s">
         <v>170</v>
       </c>
-      <c r="O2" s="83" t="s">
+      <c r="O2" s="77" t="s">
         <v>171</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="58"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="56"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="57"/>
-      <c r="Y2" s="56"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="53"/>
+      <c r="S2" s="52"/>
+      <c r="T2" s="52"/>
+      <c r="U2" s="52"/>
+      <c r="V2" s="37"/>
+      <c r="W2" s="52"/>
+      <c r="X2" s="52"/>
+      <c r="Y2" s="37"/>
     </row>
     <row r="3" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -1628,49 +1617,49 @@
         <v>240</v>
       </c>
       <c r="E3" s="11"/>
-      <c r="F3" s="29">
+      <c r="F3" s="27">
         <v>55</v>
       </c>
       <c r="G3" s="11"/>
-      <c r="H3" s="29">
+      <c r="H3" s="27">
         <v>50</v>
       </c>
       <c r="I3" s="11">
         <f>(D3+E3-G3-H3-F3)</f>
         <v>135</v>
       </c>
-      <c r="J3" s="61">
+      <c r="J3" s="56">
         <f t="shared" ref="J3:J43" si="0">I3*C3</f>
         <v>2430000</v>
       </c>
-      <c r="K3" s="64">
+      <c r="K3" s="59">
         <v>500</v>
       </c>
-      <c r="L3" s="76">
+      <c r="L3" s="70">
         <f>K3*I3</f>
         <v>67500</v>
       </c>
-      <c r="M3" s="78">
+      <c r="M3" s="72">
         <v>6500</v>
       </c>
-      <c r="N3" s="82">
+      <c r="N3" s="76">
         <f>F3+I3</f>
         <v>190</v>
       </c>
-      <c r="O3" s="79">
+      <c r="O3" s="73">
         <f>N3*M3</f>
         <v>1235000</v>
       </c>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="58"/>
-      <c r="S3" s="59"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="56"/>
-      <c r="W3" s="59"/>
-      <c r="X3" s="48"/>
-      <c r="Y3" s="56"/>
+      <c r="P3" s="44"/>
+      <c r="Q3" s="44"/>
+      <c r="R3" s="53"/>
+      <c r="S3" s="54"/>
+      <c r="T3" s="44"/>
+      <c r="U3" s="44"/>
+      <c r="V3" s="37"/>
+      <c r="W3" s="54"/>
+      <c r="X3" s="44"/>
+      <c r="Y3" s="37"/>
     </row>
     <row r="4" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -1685,49 +1674,49 @@
         <v>1200</v>
       </c>
       <c r="E4" s="11"/>
-      <c r="F4" s="29">
+      <c r="F4" s="27">
         <v>59</v>
       </c>
       <c r="G4" s="11"/>
-      <c r="H4" s="31">
+      <c r="H4" s="29">
         <v>457</v>
       </c>
       <c r="I4" s="11">
         <f>(D4+E4-G4-H4-F4)</f>
         <v>684</v>
       </c>
-      <c r="J4" s="61">
+      <c r="J4" s="56">
         <f t="shared" si="0"/>
         <v>10944000</v>
       </c>
-      <c r="K4" s="64">
+      <c r="K4" s="59">
         <v>500</v>
       </c>
-      <c r="L4" s="76">
+      <c r="L4" s="70">
         <f t="shared" ref="L4:L42" si="1">K4*I4</f>
         <v>342000</v>
       </c>
-      <c r="M4" s="78">
+      <c r="M4" s="72">
         <v>3100</v>
       </c>
-      <c r="N4" s="82">
-        <f t="shared" ref="N4:N43" si="2">F4+I4</f>
+      <c r="N4" s="76">
+        <f>F4+I4</f>
         <v>743</v>
       </c>
-      <c r="O4" s="79">
-        <f t="shared" ref="O4:O43" si="3">N4*M4</f>
+      <c r="O4" s="73">
+        <f t="shared" ref="O4:O43" si="2">N4*M4</f>
         <v>2303300</v>
       </c>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="41"/>
-      <c r="R4" s="55"/>
-      <c r="S4" s="41"/>
-      <c r="T4" s="41"/>
-      <c r="U4" s="41"/>
-      <c r="V4" s="56"/>
-      <c r="W4" s="41"/>
-      <c r="X4" s="41"/>
-      <c r="Y4" s="56"/>
+      <c r="P4" s="37"/>
+      <c r="Q4" s="37"/>
+      <c r="R4" s="51"/>
+      <c r="S4" s="37"/>
+      <c r="T4" s="37"/>
+      <c r="U4" s="37"/>
+      <c r="V4" s="37"/>
+      <c r="W4" s="37"/>
+      <c r="X4" s="37"/>
+      <c r="Y4" s="37"/>
     </row>
     <row r="5" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
@@ -1742,51 +1731,51 @@
         <v>2000</v>
       </c>
       <c r="E5" s="11"/>
-      <c r="F5" s="29">
+      <c r="F5" s="27">
         <v>94</v>
       </c>
       <c r="G5" s="11">
         <v>4</v>
       </c>
-      <c r="H5" s="29">
+      <c r="H5" s="27">
         <v>442</v>
       </c>
       <c r="I5" s="11">
-        <f t="shared" ref="I5:I42" si="4">(D5+E5-G5-H5-F5)</f>
+        <f t="shared" ref="I5:I42" si="3">(D5+E5-G5-H5-F5)</f>
         <v>1460</v>
       </c>
-      <c r="J5" s="61">
+      <c r="J5" s="56">
         <f t="shared" si="0"/>
         <v>17520000</v>
       </c>
-      <c r="K5" s="64">
+      <c r="K5" s="59">
         <v>500</v>
       </c>
-      <c r="L5" s="76">
+      <c r="L5" s="70">
         <f t="shared" si="1"/>
         <v>730000</v>
       </c>
-      <c r="M5" s="78">
+      <c r="M5" s="72">
         <v>750</v>
       </c>
-      <c r="N5" s="82">
+      <c r="N5" s="76">
+        <f>F5+I5</f>
+        <v>1554</v>
+      </c>
+      <c r="O5" s="73">
         <f t="shared" si="2"/>
-        <v>1554</v>
-      </c>
-      <c r="O5" s="79">
-        <f t="shared" si="3"/>
         <v>1165500</v>
       </c>
-      <c r="P5" s="41"/>
-      <c r="Q5" s="41"/>
-      <c r="R5" s="58"/>
-      <c r="S5" s="41"/>
-      <c r="T5" s="41"/>
-      <c r="U5" s="41"/>
-      <c r="V5" s="56"/>
-      <c r="W5" s="41"/>
-      <c r="X5" s="41"/>
-      <c r="Y5" s="56"/>
+      <c r="P5" s="37"/>
+      <c r="Q5" s="37"/>
+      <c r="R5" s="53"/>
+      <c r="S5" s="37"/>
+      <c r="T5" s="37"/>
+      <c r="U5" s="37"/>
+      <c r="V5" s="37"/>
+      <c r="W5" s="37"/>
+      <c r="X5" s="37"/>
+      <c r="Y5" s="37"/>
     </row>
     <row r="6" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
@@ -1801,49 +1790,49 @@
         <v>120</v>
       </c>
       <c r="E6" s="11"/>
-      <c r="F6" s="29">
+      <c r="F6" s="27">
         <v>1</v>
       </c>
       <c r="G6" s="11"/>
-      <c r="H6" s="29">
+      <c r="H6" s="27">
         <v>92</v>
       </c>
       <c r="I6" s="11">
         <f>(D6+E6-G6-H6-F6)</f>
         <v>27</v>
       </c>
-      <c r="J6" s="61">
+      <c r="J6" s="56">
         <f t="shared" si="0"/>
         <v>324000</v>
       </c>
-      <c r="K6" s="64">
+      <c r="K6" s="59">
         <v>500</v>
       </c>
-      <c r="L6" s="76">
+      <c r="L6" s="70">
         <f t="shared" si="1"/>
         <v>13500</v>
       </c>
-      <c r="M6" s="78">
+      <c r="M6" s="72">
         <v>2120</v>
       </c>
-      <c r="N6" s="82">
+      <c r="N6" s="76">
+        <f t="shared" ref="N4:N43" si="4">F6+I6</f>
+        <v>28</v>
+      </c>
+      <c r="O6" s="73">
         <f t="shared" si="2"/>
-        <v>28</v>
-      </c>
-      <c r="O6" s="79">
-        <f t="shared" si="3"/>
         <v>59360</v>
       </c>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="41"/>
-      <c r="R6" s="58"/>
-      <c r="S6" s="41"/>
-      <c r="T6" s="41"/>
-      <c r="U6" s="41"/>
-      <c r="V6" s="56"/>
-      <c r="W6" s="41"/>
-      <c r="X6" s="41"/>
-      <c r="Y6" s="56"/>
+      <c r="P6" s="37"/>
+      <c r="Q6" s="37"/>
+      <c r="R6" s="53"/>
+      <c r="S6" s="37"/>
+      <c r="T6" s="37"/>
+      <c r="U6" s="37"/>
+      <c r="V6" s="37"/>
+      <c r="W6" s="37"/>
+      <c r="X6" s="37"/>
+      <c r="Y6" s="37"/>
     </row>
     <row r="7" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
@@ -1858,49 +1847,49 @@
         <v>96</v>
       </c>
       <c r="E7" s="11"/>
-      <c r="F7" s="29">
+      <c r="F7" s="27">
         <v>4</v>
       </c>
       <c r="G7" s="11"/>
-      <c r="H7" s="29">
+      <c r="H7" s="27">
         <v>66</v>
       </c>
       <c r="I7" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
-      <c r="J7" s="61">
+      <c r="J7" s="56">
         <f t="shared" si="0"/>
         <v>312000</v>
       </c>
-      <c r="K7" s="64">
+      <c r="K7" s="59">
         <v>500</v>
       </c>
-      <c r="L7" s="76">
+      <c r="L7" s="70">
         <f t="shared" si="1"/>
         <v>13000</v>
       </c>
-      <c r="M7" s="78">
+      <c r="M7" s="72">
         <v>2400</v>
       </c>
-      <c r="N7" s="82">
+      <c r="N7" s="76">
+        <f>F7+I7</f>
+        <v>30</v>
+      </c>
+      <c r="O7" s="73">
         <f t="shared" si="2"/>
-        <v>30</v>
-      </c>
-      <c r="O7" s="79">
-        <f t="shared" si="3"/>
         <v>72000</v>
       </c>
-      <c r="P7" s="41"/>
-      <c r="Q7" s="41"/>
-      <c r="R7" s="55"/>
-      <c r="S7" s="41"/>
-      <c r="T7" s="41"/>
-      <c r="U7" s="41"/>
-      <c r="V7" s="56"/>
-      <c r="W7" s="41"/>
-      <c r="X7" s="41"/>
-      <c r="Y7" s="56"/>
+      <c r="P7" s="37"/>
+      <c r="Q7" s="37"/>
+      <c r="R7" s="51"/>
+      <c r="S7" s="37"/>
+      <c r="T7" s="37"/>
+      <c r="U7" s="37"/>
+      <c r="V7" s="37"/>
+      <c r="W7" s="37"/>
+      <c r="X7" s="37"/>
+      <c r="Y7" s="37"/>
     </row>
     <row r="8" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
@@ -1914,49 +1903,49 @@
         <v>96</v>
       </c>
       <c r="E8" s="11"/>
-      <c r="F8" s="29">
+      <c r="F8" s="27">
         <v>25</v>
       </c>
       <c r="G8" s="11"/>
-      <c r="H8" s="29">
+      <c r="H8" s="27">
         <v>64</v>
       </c>
       <c r="I8" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="J8" s="61">
+      <c r="J8" s="56">
         <f t="shared" si="0"/>
         <v>84000</v>
       </c>
-      <c r="K8" s="64">
+      <c r="K8" s="59">
         <v>500</v>
       </c>
-      <c r="L8" s="76">
+      <c r="L8" s="70">
         <f t="shared" si="1"/>
         <v>3500</v>
       </c>
-      <c r="M8" s="78">
+      <c r="M8" s="72">
         <v>2120</v>
       </c>
-      <c r="N8" s="82">
+      <c r="N8" s="76">
+        <f t="shared" si="4"/>
+        <v>32</v>
+      </c>
+      <c r="O8" s="73">
         <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-      <c r="O8" s="79">
-        <f t="shared" si="3"/>
         <v>67840</v>
       </c>
-      <c r="P8" s="41"/>
-      <c r="Q8" s="41"/>
-      <c r="R8" s="58"/>
-      <c r="S8" s="41"/>
-      <c r="T8" s="41"/>
-      <c r="U8" s="41"/>
-      <c r="V8" s="56"/>
-      <c r="W8" s="41"/>
-      <c r="X8" s="41"/>
-      <c r="Y8" s="56"/>
+      <c r="P8" s="37"/>
+      <c r="Q8" s="37"/>
+      <c r="R8" s="53"/>
+      <c r="S8" s="37"/>
+      <c r="T8" s="37"/>
+      <c r="U8" s="37"/>
+      <c r="V8" s="37"/>
+      <c r="W8" s="37"/>
+      <c r="X8" s="37"/>
+      <c r="Y8" s="37"/>
     </row>
     <row r="9" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
@@ -1971,49 +1960,49 @@
         <v>60</v>
       </c>
       <c r="E9" s="11"/>
-      <c r="F9" s="29">
+      <c r="F9" s="27">
         <v>2</v>
       </c>
       <c r="G9" s="11"/>
-      <c r="H9" s="29">
+      <c r="H9" s="27">
         <v>42</v>
       </c>
       <c r="I9" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="J9" s="61">
+      <c r="J9" s="56">
         <f t="shared" si="0"/>
         <v>192000</v>
       </c>
-      <c r="K9" s="64">
+      <c r="K9" s="59">
         <v>500</v>
       </c>
-      <c r="L9" s="76">
+      <c r="L9" s="70">
         <f t="shared" si="1"/>
         <v>8000</v>
       </c>
-      <c r="M9" s="78">
+      <c r="M9" s="72">
         <v>1666</v>
       </c>
-      <c r="N9" s="82">
+      <c r="N9" s="76">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="O9" s="73">
         <f t="shared" si="2"/>
-        <v>18</v>
-      </c>
-      <c r="O9" s="79">
-        <f t="shared" si="3"/>
         <v>29988</v>
       </c>
-      <c r="P9" s="41"/>
-      <c r="Q9" s="41"/>
-      <c r="R9" s="58"/>
-      <c r="S9" s="41"/>
-      <c r="T9" s="41"/>
-      <c r="U9" s="41"/>
-      <c r="V9" s="56"/>
-      <c r="W9" s="41"/>
-      <c r="X9" s="41"/>
-      <c r="Y9" s="56"/>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="37"/>
+      <c r="R9" s="53"/>
+      <c r="S9" s="37"/>
+      <c r="T9" s="37"/>
+      <c r="U9" s="37"/>
+      <c r="V9" s="37"/>
+      <c r="W9" s="37"/>
+      <c r="X9" s="37"/>
+      <c r="Y9" s="37"/>
     </row>
     <row r="10" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
@@ -2028,49 +2017,49 @@
         <v>120</v>
       </c>
       <c r="E10" s="11"/>
-      <c r="F10" s="29">
+      <c r="F10" s="27">
         <v>8</v>
       </c>
       <c r="G10" s="11"/>
-      <c r="H10" s="29">
+      <c r="H10" s="27">
         <v>106</v>
       </c>
       <c r="I10" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="J10" s="61">
+      <c r="J10" s="56">
         <f t="shared" si="0"/>
         <v>72000</v>
       </c>
-      <c r="K10" s="64">
+      <c r="K10" s="59">
         <v>500</v>
       </c>
-      <c r="L10" s="76">
+      <c r="L10" s="70">
         <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-      <c r="M10" s="78">
+      <c r="M10" s="72">
         <v>2500</v>
       </c>
-      <c r="N10" s="82">
+      <c r="N10" s="76">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="O10" s="73">
         <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-      <c r="O10" s="79">
-        <f t="shared" si="3"/>
         <v>35000</v>
       </c>
-      <c r="P10" s="41"/>
-      <c r="Q10" s="41"/>
-      <c r="R10" s="58"/>
-      <c r="S10" s="41"/>
-      <c r="T10" s="41"/>
-      <c r="U10" s="41"/>
-      <c r="V10" s="56"/>
-      <c r="W10" s="41"/>
-      <c r="X10" s="41"/>
-      <c r="Y10" s="56"/>
+      <c r="P10" s="37"/>
+      <c r="Q10" s="37"/>
+      <c r="R10" s="53"/>
+      <c r="S10" s="37"/>
+      <c r="T10" s="37"/>
+      <c r="U10" s="37"/>
+      <c r="V10" s="37"/>
+      <c r="W10" s="37"/>
+      <c r="X10" s="37"/>
+      <c r="Y10" s="37"/>
     </row>
     <row r="11" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
@@ -2084,49 +2073,49 @@
         <v>144</v>
       </c>
       <c r="E11" s="13"/>
-      <c r="F11" s="28">
+      <c r="F11" s="26">
         <v>7</v>
       </c>
       <c r="G11" s="15"/>
-      <c r="H11" s="32">
+      <c r="H11" s="30">
         <v>54</v>
       </c>
       <c r="I11" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>83</v>
       </c>
-      <c r="J11" s="61">
+      <c r="J11" s="56">
         <f t="shared" si="0"/>
         <v>2075000</v>
       </c>
-      <c r="K11" s="64">
+      <c r="K11" s="59">
         <v>500</v>
       </c>
-      <c r="L11" s="76">
+      <c r="L11" s="70">
         <f t="shared" si="1"/>
         <v>41500</v>
       </c>
-      <c r="M11" s="78">
+      <c r="M11" s="72">
         <v>7000</v>
       </c>
-      <c r="N11" s="82">
+      <c r="N11" s="76">
+        <f t="shared" si="4"/>
+        <v>90</v>
+      </c>
+      <c r="O11" s="73">
         <f t="shared" si="2"/>
-        <v>90</v>
-      </c>
-      <c r="O11" s="79">
-        <f t="shared" si="3"/>
         <v>630000</v>
       </c>
-      <c r="P11" s="41"/>
-      <c r="Q11" s="41"/>
-      <c r="R11" s="55"/>
-      <c r="S11" s="41"/>
-      <c r="T11" s="41"/>
-      <c r="U11" s="41"/>
-      <c r="V11" s="56"/>
-      <c r="W11" s="41"/>
-      <c r="X11" s="41"/>
-      <c r="Y11" s="56"/>
+      <c r="P11" s="37"/>
+      <c r="Q11" s="37"/>
+      <c r="R11" s="51"/>
+      <c r="S11" s="37"/>
+      <c r="T11" s="37"/>
+      <c r="U11" s="37"/>
+      <c r="V11" s="37"/>
+      <c r="W11" s="37"/>
+      <c r="X11" s="37"/>
+      <c r="Y11" s="37"/>
     </row>
     <row r="12" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
@@ -2136,26 +2125,26 @@
       <c r="C12" s="17"/>
       <c r="D12" s="23"/>
       <c r="E12" s="16"/>
-      <c r="F12" s="35"/>
+      <c r="F12" s="33"/>
       <c r="G12" s="18"/>
-      <c r="H12" s="33"/>
+      <c r="H12" s="31"/>
       <c r="I12" s="18"/>
-      <c r="J12" s="62"/>
-      <c r="K12" s="65"/>
-      <c r="L12" s="77"/>
-      <c r="M12" s="77"/>
-      <c r="N12" s="77"/>
-      <c r="O12" s="77"/>
-      <c r="P12" s="41"/>
-      <c r="Q12" s="41"/>
-      <c r="R12" s="58"/>
-      <c r="S12" s="41"/>
-      <c r="T12" s="41"/>
-      <c r="U12" s="41"/>
-      <c r="V12" s="56"/>
-      <c r="W12" s="41"/>
-      <c r="X12" s="41"/>
-      <c r="Y12" s="56"/>
+      <c r="J12" s="57"/>
+      <c r="K12" s="60"/>
+      <c r="L12" s="71"/>
+      <c r="M12" s="71"/>
+      <c r="N12" s="71"/>
+      <c r="O12" s="71"/>
+      <c r="P12" s="37"/>
+      <c r="Q12" s="37"/>
+      <c r="R12" s="53"/>
+      <c r="S12" s="37"/>
+      <c r="T12" s="37"/>
+      <c r="U12" s="37"/>
+      <c r="V12" s="37"/>
+      <c r="W12" s="37"/>
+      <c r="X12" s="37"/>
+      <c r="Y12" s="37"/>
     </row>
     <row r="13" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
@@ -2169,55 +2158,55 @@
         <f>792</f>
         <v>792</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="27">
         <v>240</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="27">
         <v>44</v>
       </c>
       <c r="G13" s="11">
         <v>2</v>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="27">
         <f>577-9</f>
         <v>568</v>
       </c>
       <c r="I13" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>418</v>
       </c>
-      <c r="J13" s="61">
+      <c r="J13" s="56">
         <f t="shared" si="0"/>
         <v>5434000</v>
       </c>
-      <c r="K13" s="64">
+      <c r="K13" s="59">
         <v>500</v>
       </c>
-      <c r="L13" s="76">
+      <c r="L13" s="70">
         <f t="shared" si="1"/>
         <v>209000</v>
       </c>
-      <c r="M13" s="78">
+      <c r="M13" s="72">
         <v>2254</v>
       </c>
-      <c r="N13" s="82">
+      <c r="N13" s="76">
+        <f>F13+I13</f>
+        <v>462</v>
+      </c>
+      <c r="O13" s="73">
         <f t="shared" si="2"/>
-        <v>462</v>
-      </c>
-      <c r="O13" s="79">
-        <f t="shared" si="3"/>
         <v>1041348</v>
       </c>
-      <c r="P13" s="41"/>
-      <c r="Q13" s="41"/>
-      <c r="R13" s="58"/>
-      <c r="S13" s="41"/>
-      <c r="T13" s="41"/>
-      <c r="U13" s="41"/>
-      <c r="V13" s="56"/>
-      <c r="W13" s="41"/>
-      <c r="X13" s="41"/>
-      <c r="Y13" s="56"/>
+      <c r="P13" s="37"/>
+      <c r="Q13" s="37"/>
+      <c r="R13" s="53"/>
+      <c r="S13" s="37"/>
+      <c r="T13" s="37"/>
+      <c r="U13" s="37"/>
+      <c r="V13" s="37"/>
+      <c r="W13" s="37"/>
+      <c r="X13" s="37"/>
+      <c r="Y13" s="37"/>
     </row>
     <row r="14" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
@@ -2231,52 +2220,52 @@
         <f>288</f>
         <v>288</v>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="26">
         <v>360</v>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="26">
         <v>17</v>
       </c>
       <c r="G14" s="15"/>
-      <c r="H14" s="32">
+      <c r="H14" s="30">
         <v>348</v>
       </c>
       <c r="I14" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>283</v>
       </c>
-      <c r="J14" s="61">
+      <c r="J14" s="56">
         <f t="shared" si="0"/>
         <v>4528000</v>
       </c>
-      <c r="K14" s="64">
+      <c r="K14" s="59">
         <v>500</v>
       </c>
-      <c r="L14" s="76">
+      <c r="L14" s="70">
         <f t="shared" si="1"/>
         <v>141500</v>
       </c>
-      <c r="M14" s="78">
+      <c r="M14" s="72">
         <v>3787</v>
       </c>
-      <c r="N14" s="82">
+      <c r="N14" s="76">
+        <f t="shared" si="4"/>
+        <v>300</v>
+      </c>
+      <c r="O14" s="73">
         <f t="shared" si="2"/>
-        <v>300</v>
-      </c>
-      <c r="O14" s="79">
-        <f t="shared" si="3"/>
         <v>1136100</v>
       </c>
-      <c r="P14" s="41"/>
-      <c r="Q14" s="41"/>
-      <c r="R14" s="58"/>
-      <c r="S14" s="41"/>
-      <c r="T14" s="41"/>
-      <c r="U14" s="41"/>
-      <c r="V14" s="56"/>
-      <c r="W14" s="41"/>
-      <c r="X14" s="41"/>
-      <c r="Y14" s="56"/>
+      <c r="P14" s="37"/>
+      <c r="Q14" s="37"/>
+      <c r="R14" s="53"/>
+      <c r="S14" s="37"/>
+      <c r="T14" s="37"/>
+      <c r="U14" s="37"/>
+      <c r="V14" s="37"/>
+      <c r="W14" s="37"/>
+      <c r="X14" s="37"/>
+      <c r="Y14" s="37"/>
     </row>
     <row r="15" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
@@ -2286,26 +2275,26 @@
       <c r="C15" s="17"/>
       <c r="D15" s="23"/>
       <c r="E15" s="16"/>
-      <c r="F15" s="35"/>
+      <c r="F15" s="33"/>
       <c r="G15" s="18"/>
-      <c r="H15" s="33"/>
+      <c r="H15" s="31"/>
       <c r="I15" s="18"/>
-      <c r="J15" s="62"/>
-      <c r="K15" s="65"/>
-      <c r="L15" s="77"/>
-      <c r="M15" s="77"/>
-      <c r="N15" s="77"/>
-      <c r="O15" s="77"/>
-      <c r="P15" s="41"/>
-      <c r="Q15" s="41"/>
-      <c r="R15" s="58"/>
-      <c r="S15" s="41"/>
-      <c r="T15" s="41"/>
-      <c r="U15" s="41"/>
-      <c r="V15" s="56"/>
-      <c r="W15" s="41"/>
-      <c r="X15" s="41"/>
-      <c r="Y15" s="56"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="60"/>
+      <c r="L15" s="71"/>
+      <c r="M15" s="71"/>
+      <c r="N15" s="71"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="37"/>
+      <c r="Q15" s="37"/>
+      <c r="R15" s="53"/>
+      <c r="S15" s="37"/>
+      <c r="T15" s="37"/>
+      <c r="U15" s="37"/>
+      <c r="V15" s="37"/>
+      <c r="W15" s="37"/>
+      <c r="X15" s="37"/>
+      <c r="Y15" s="37"/>
     </row>
     <row r="16" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
@@ -2320,49 +2309,49 @@
         <v>96</v>
       </c>
       <c r="E16" s="13"/>
-      <c r="F16" s="28">
+      <c r="F16" s="26">
         <v>2</v>
       </c>
       <c r="G16" s="15"/>
-      <c r="H16" s="32">
+      <c r="H16" s="30">
         <v>71</v>
       </c>
       <c r="I16" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
-      <c r="J16" s="61">
+      <c r="J16" s="56">
         <f t="shared" si="0"/>
         <v>575000</v>
       </c>
-      <c r="K16" s="64">
+      <c r="K16" s="59">
         <v>500</v>
       </c>
-      <c r="L16" s="76">
+      <c r="L16" s="70">
         <f t="shared" si="1"/>
         <v>11500</v>
       </c>
-      <c r="M16" s="78">
+      <c r="M16" s="72">
         <v>6173</v>
       </c>
-      <c r="N16" s="82">
+      <c r="N16" s="76">
+        <f t="shared" si="4"/>
+        <v>25</v>
+      </c>
+      <c r="O16" s="73">
         <f t="shared" si="2"/>
-        <v>25</v>
-      </c>
-      <c r="O16" s="79">
-        <f t="shared" si="3"/>
         <v>154325</v>
       </c>
-      <c r="P16" s="41"/>
-      <c r="Q16" s="41"/>
-      <c r="R16" s="58"/>
-      <c r="S16" s="41"/>
-      <c r="T16" s="41"/>
-      <c r="U16" s="41"/>
-      <c r="V16" s="56"/>
-      <c r="W16" s="41"/>
-      <c r="X16" s="41"/>
-      <c r="Y16" s="56"/>
+      <c r="P16" s="37"/>
+      <c r="Q16" s="37"/>
+      <c r="R16" s="53"/>
+      <c r="S16" s="37"/>
+      <c r="T16" s="37"/>
+      <c r="U16" s="37"/>
+      <c r="V16" s="37"/>
+      <c r="W16" s="37"/>
+      <c r="X16" s="37"/>
+      <c r="Y16" s="37"/>
     </row>
     <row r="17" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
@@ -2372,88 +2361,88 @@
       <c r="C17" s="17"/>
       <c r="D17" s="23"/>
       <c r="E17" s="16"/>
-      <c r="F17" s="35"/>
+      <c r="F17" s="33"/>
       <c r="G17" s="18"/>
-      <c r="H17" s="33"/>
+      <c r="H17" s="31"/>
       <c r="I17" s="18"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="65"/>
-      <c r="L17" s="77"/>
-      <c r="M17" s="78"/>
-      <c r="N17" s="82">
+      <c r="J17" s="57"/>
+      <c r="K17" s="60"/>
+      <c r="L17" s="71"/>
+      <c r="M17" s="72"/>
+      <c r="N17" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O17" s="73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O17" s="79">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P17" s="41"/>
-      <c r="Q17" s="41"/>
-      <c r="R17" s="58"/>
-      <c r="S17" s="41"/>
-      <c r="T17" s="41"/>
-      <c r="U17" s="41"/>
-      <c r="V17" s="56"/>
-      <c r="W17" s="41"/>
-      <c r="X17" s="41"/>
-      <c r="Y17" s="56"/>
+      <c r="P17" s="37"/>
+      <c r="Q17" s="37"/>
+      <c r="R17" s="53"/>
+      <c r="S17" s="37"/>
+      <c r="T17" s="37"/>
+      <c r="U17" s="37"/>
+      <c r="V17" s="37"/>
+      <c r="W17" s="37"/>
+      <c r="X17" s="37"/>
+      <c r="Y17" s="37"/>
     </row>
     <row r="18" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B18" s="11"/>
-      <c r="C18" s="52">
+      <c r="C18" s="48">
         <v>400000</v>
       </c>
       <c r="D18" s="22">
         <v>12</v>
       </c>
       <c r="E18" s="11"/>
-      <c r="F18" s="29">
+      <c r="F18" s="27">
         <v>0</v>
       </c>
       <c r="G18" s="11"/>
-      <c r="H18" s="29">
+      <c r="H18" s="27">
         <v>12</v>
       </c>
       <c r="I18" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="56">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="61">
+        <v>10000</v>
+      </c>
+      <c r="L18" s="70">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="72">
+        <v>167000</v>
+      </c>
+      <c r="N18" s="76">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J18" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K18" s="66">
-        <v>10000</v>
-      </c>
-      <c r="L18" s="76">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="78">
-        <v>167000</v>
-      </c>
-      <c r="N18" s="82">
+      <c r="O18" s="73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O18" s="79">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P18" s="41"/>
-      <c r="Q18" s="41"/>
-      <c r="R18" s="58"/>
-      <c r="S18" s="41"/>
-      <c r="T18" s="41"/>
-      <c r="U18" s="41"/>
-      <c r="V18" s="56"/>
-      <c r="W18" s="41"/>
-      <c r="X18" s="41"/>
-      <c r="Y18" s="56"/>
+      <c r="P18" s="37"/>
+      <c r="Q18" s="37"/>
+      <c r="R18" s="53"/>
+      <c r="S18" s="37"/>
+      <c r="T18" s="37"/>
+      <c r="U18" s="37"/>
+      <c r="V18" s="37"/>
+      <c r="W18" s="37"/>
+      <c r="X18" s="37"/>
+      <c r="Y18" s="37"/>
     </row>
     <row r="19" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
@@ -2467,49 +2456,49 @@
         <v>24</v>
       </c>
       <c r="E19" s="11"/>
-      <c r="F19" s="29">
+      <c r="F19" s="27">
         <v>0</v>
       </c>
       <c r="G19" s="11"/>
-      <c r="H19" s="29">
+      <c r="H19" s="27">
         <v>20</v>
       </c>
       <c r="I19" s="11">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="J19" s="56">
+        <f t="shared" si="0"/>
+        <v>1440000</v>
+      </c>
+      <c r="K19" s="61">
+        <v>10000</v>
+      </c>
+      <c r="L19" s="70">
+        <f t="shared" si="1"/>
+        <v>40000</v>
+      </c>
+      <c r="M19" s="72">
+        <v>135000</v>
+      </c>
+      <c r="N19" s="76">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="J19" s="61">
-        <f t="shared" si="0"/>
-        <v>1440000</v>
-      </c>
-      <c r="K19" s="66">
-        <v>10000</v>
-      </c>
-      <c r="L19" s="76">
-        <f t="shared" si="1"/>
-        <v>40000</v>
-      </c>
-      <c r="M19" s="78">
-        <v>135000</v>
-      </c>
-      <c r="N19" s="82">
+      <c r="O19" s="73">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="O19" s="79">
-        <f t="shared" si="3"/>
         <v>540000</v>
       </c>
-      <c r="P19" s="41"/>
-      <c r="Q19" s="41"/>
-      <c r="R19" s="58"/>
-      <c r="S19" s="41"/>
-      <c r="T19" s="41"/>
-      <c r="U19" s="41"/>
-      <c r="V19" s="56"/>
-      <c r="W19" s="41"/>
-      <c r="X19" s="41"/>
-      <c r="Y19" s="56"/>
+      <c r="P19" s="37"/>
+      <c r="Q19" s="37"/>
+      <c r="R19" s="53"/>
+      <c r="S19" s="37"/>
+      <c r="T19" s="37"/>
+      <c r="U19" s="37"/>
+      <c r="V19" s="37"/>
+      <c r="W19" s="37"/>
+      <c r="X19" s="37"/>
+      <c r="Y19" s="37"/>
     </row>
     <row r="20" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
@@ -2524,49 +2513,49 @@
         <v>24</v>
       </c>
       <c r="E20" s="13"/>
-      <c r="F20" s="28">
+      <c r="F20" s="26">
         <v>0</v>
       </c>
       <c r="G20" s="15"/>
-      <c r="H20" s="32">
+      <c r="H20" s="30">
         <v>21</v>
       </c>
       <c r="I20" s="11">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="J20" s="56">
+        <f t="shared" si="0"/>
+        <v>780000</v>
+      </c>
+      <c r="K20" s="61">
+        <v>5000</v>
+      </c>
+      <c r="L20" s="70">
+        <f t="shared" si="1"/>
+        <v>15000</v>
+      </c>
+      <c r="M20" s="72">
+        <v>62522</v>
+      </c>
+      <c r="N20" s="76">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="J20" s="61">
-        <f t="shared" si="0"/>
-        <v>780000</v>
-      </c>
-      <c r="K20" s="66">
-        <v>5000</v>
-      </c>
-      <c r="L20" s="76">
-        <f t="shared" si="1"/>
-        <v>15000</v>
-      </c>
-      <c r="M20" s="78">
-        <v>62522</v>
-      </c>
-      <c r="N20" s="82">
+      <c r="O20" s="73">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="O20" s="79">
-        <f t="shared" si="3"/>
         <v>187566</v>
       </c>
-      <c r="P20" s="41"/>
-      <c r="Q20" s="41"/>
-      <c r="R20" s="58"/>
-      <c r="S20" s="41"/>
-      <c r="T20" s="41"/>
-      <c r="U20" s="41"/>
-      <c r="V20" s="56"/>
-      <c r="W20" s="41"/>
-      <c r="X20" s="41"/>
-      <c r="Y20" s="56"/>
+      <c r="P20" s="37"/>
+      <c r="Q20" s="37"/>
+      <c r="R20" s="53"/>
+      <c r="S20" s="37"/>
+      <c r="T20" s="37"/>
+      <c r="U20" s="37"/>
+      <c r="V20" s="37"/>
+      <c r="W20" s="37"/>
+      <c r="X20" s="37"/>
+      <c r="Y20" s="37"/>
     </row>
     <row r="21" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
@@ -2576,26 +2565,26 @@
       <c r="C21" s="17"/>
       <c r="D21" s="23"/>
       <c r="E21" s="16"/>
-      <c r="F21" s="35"/>
+      <c r="F21" s="33"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="33"/>
+      <c r="H21" s="31"/>
       <c r="I21" s="18"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="65"/>
-      <c r="L21" s="77"/>
-      <c r="M21" s="77"/>
-      <c r="N21" s="77"/>
-      <c r="O21" s="77"/>
-      <c r="P21" s="41"/>
-      <c r="Q21" s="41"/>
-      <c r="R21" s="55"/>
-      <c r="S21" s="41"/>
-      <c r="T21" s="41"/>
-      <c r="U21" s="41"/>
-      <c r="V21" s="56"/>
-      <c r="W21" s="41"/>
-      <c r="X21" s="41"/>
-      <c r="Y21" s="56"/>
+      <c r="J21" s="57"/>
+      <c r="K21" s="60"/>
+      <c r="L21" s="71"/>
+      <c r="M21" s="71"/>
+      <c r="N21" s="71"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="37"/>
+      <c r="Q21" s="37"/>
+      <c r="R21" s="51"/>
+      <c r="S21" s="37"/>
+      <c r="T21" s="37"/>
+      <c r="U21" s="37"/>
+      <c r="V21" s="37"/>
+      <c r="W21" s="37"/>
+      <c r="X21" s="37"/>
+      <c r="Y21" s="37"/>
     </row>
     <row r="22" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
@@ -2609,49 +2598,49 @@
         <v>6</v>
       </c>
       <c r="E22" s="11"/>
-      <c r="F22" s="29">
+      <c r="F22" s="27">
         <v>0</v>
       </c>
       <c r="G22" s="11"/>
-      <c r="H22" s="29">
+      <c r="H22" s="27">
         <v>6</v>
       </c>
       <c r="I22" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="56">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="61">
+        <v>5000</v>
+      </c>
+      <c r="L22" s="70">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="72">
+        <v>77000</v>
+      </c>
+      <c r="N22" s="76">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J22" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="66">
-        <v>5000</v>
-      </c>
-      <c r="L22" s="76">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M22" s="78">
-        <v>77000</v>
-      </c>
-      <c r="N22" s="82">
+      <c r="O22" s="73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O22" s="79">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P22" s="41"/>
-      <c r="Q22" s="41"/>
-      <c r="R22" s="58"/>
-      <c r="S22" s="41"/>
-      <c r="T22" s="41"/>
-      <c r="U22" s="41"/>
-      <c r="V22" s="56"/>
-      <c r="W22" s="41"/>
-      <c r="X22" s="41"/>
-      <c r="Y22" s="56"/>
+      <c r="P22" s="37"/>
+      <c r="Q22" s="37"/>
+      <c r="R22" s="53"/>
+      <c r="S22" s="37"/>
+      <c r="T22" s="37"/>
+      <c r="U22" s="37"/>
+      <c r="V22" s="37"/>
+      <c r="W22" s="37"/>
+      <c r="X22" s="37"/>
+      <c r="Y22" s="37"/>
     </row>
     <row r="23" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
@@ -2665,49 +2654,49 @@
         <v>12</v>
       </c>
       <c r="E23" s="13"/>
-      <c r="F23" s="28">
+      <c r="F23" s="26">
         <v>0</v>
       </c>
       <c r="G23" s="15"/>
-      <c r="H23" s="32">
+      <c r="H23" s="30">
         <v>9</v>
       </c>
       <c r="I23" s="11">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="J23" s="56">
+        <f t="shared" si="0"/>
+        <v>480000</v>
+      </c>
+      <c r="K23" s="61">
+        <v>5000</v>
+      </c>
+      <c r="L23" s="70">
+        <f t="shared" si="1"/>
+        <v>15000</v>
+      </c>
+      <c r="M23" s="72">
+        <v>58766</v>
+      </c>
+      <c r="N23" s="76">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="J23" s="61">
-        <f t="shared" si="0"/>
-        <v>480000</v>
-      </c>
-      <c r="K23" s="66">
-        <v>5000</v>
-      </c>
-      <c r="L23" s="76">
-        <f t="shared" si="1"/>
-        <v>15000</v>
-      </c>
-      <c r="M23" s="78">
-        <v>58766</v>
-      </c>
-      <c r="N23" s="82">
+      <c r="O23" s="73">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="O23" s="79">
-        <f t="shared" si="3"/>
         <v>176298</v>
       </c>
-      <c r="P23" s="41"/>
-      <c r="Q23" s="41"/>
-      <c r="R23" s="58"/>
-      <c r="S23" s="41"/>
-      <c r="T23" s="41"/>
-      <c r="U23" s="41"/>
-      <c r="V23" s="56"/>
-      <c r="W23" s="41"/>
-      <c r="X23" s="41"/>
-      <c r="Y23" s="56"/>
+      <c r="P23" s="37"/>
+      <c r="Q23" s="37"/>
+      <c r="R23" s="53"/>
+      <c r="S23" s="37"/>
+      <c r="T23" s="37"/>
+      <c r="U23" s="37"/>
+      <c r="V23" s="37"/>
+      <c r="W23" s="37"/>
+      <c r="X23" s="37"/>
+      <c r="Y23" s="37"/>
     </row>
     <row r="24" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
@@ -2717,26 +2706,26 @@
       <c r="C24" s="17"/>
       <c r="D24" s="23"/>
       <c r="E24" s="16"/>
-      <c r="F24" s="35"/>
+      <c r="F24" s="33"/>
       <c r="G24" s="18"/>
-      <c r="H24" s="33"/>
+      <c r="H24" s="31"/>
       <c r="I24" s="18"/>
-      <c r="J24" s="62"/>
-      <c r="K24" s="65"/>
-      <c r="L24" s="77"/>
-      <c r="M24" s="77"/>
-      <c r="N24" s="77"/>
-      <c r="O24" s="77"/>
-      <c r="P24" s="48"/>
-      <c r="Q24" s="48"/>
-      <c r="R24" s="56"/>
-      <c r="S24" s="59"/>
-      <c r="T24" s="48"/>
-      <c r="U24" s="48"/>
-      <c r="V24" s="56"/>
-      <c r="W24" s="59"/>
-      <c r="X24" s="48"/>
-      <c r="Y24" s="56"/>
+      <c r="J24" s="57"/>
+      <c r="K24" s="60"/>
+      <c r="L24" s="71"/>
+      <c r="M24" s="71"/>
+      <c r="N24" s="71"/>
+      <c r="O24" s="71"/>
+      <c r="P24" s="44"/>
+      <c r="Q24" s="44"/>
+      <c r="R24" s="37"/>
+      <c r="S24" s="54"/>
+      <c r="T24" s="44"/>
+      <c r="U24" s="44"/>
+      <c r="V24" s="37"/>
+      <c r="W24" s="54"/>
+      <c r="X24" s="44"/>
+      <c r="Y24" s="37"/>
     </row>
     <row r="25" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
@@ -2750,49 +2739,49 @@
         <v>6</v>
       </c>
       <c r="E25" s="11"/>
-      <c r="F25" s="29">
+      <c r="F25" s="27">
         <v>0</v>
       </c>
       <c r="G25" s="11"/>
-      <c r="H25" s="29">
+      <c r="H25" s="27">
         <v>5</v>
       </c>
       <c r="I25" s="11">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="J25" s="56">
+        <f t="shared" si="0"/>
+        <v>800000</v>
+      </c>
+      <c r="K25" s="61">
+        <v>10000</v>
+      </c>
+      <c r="L25" s="70">
+        <f t="shared" si="1"/>
+        <v>10000</v>
+      </c>
+      <c r="M25" s="72">
+        <v>338899</v>
+      </c>
+      <c r="N25" s="76">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="J25" s="61">
-        <f t="shared" si="0"/>
-        <v>800000</v>
-      </c>
-      <c r="K25" s="66">
-        <v>10000</v>
-      </c>
-      <c r="L25" s="76">
-        <f t="shared" si="1"/>
-        <v>10000</v>
-      </c>
-      <c r="M25" s="78">
+      <c r="O25" s="73">
+        <f t="shared" si="2"/>
         <v>338899</v>
       </c>
-      <c r="N25" s="82">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="O25" s="79">
-        <f t="shared" si="3"/>
-        <v>338899</v>
-      </c>
-      <c r="P25" s="41"/>
-      <c r="Q25" s="41"/>
-      <c r="R25" s="56"/>
-      <c r="S25" s="41"/>
-      <c r="T25" s="41"/>
-      <c r="U25" s="41"/>
-      <c r="V25" s="56"/>
-      <c r="W25" s="41"/>
-      <c r="X25" s="41"/>
-      <c r="Y25" s="56"/>
+      <c r="P25" s="37"/>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="37"/>
+      <c r="S25" s="37"/>
+      <c r="T25" s="37"/>
+      <c r="U25" s="37"/>
+      <c r="V25" s="37"/>
+      <c r="W25" s="37"/>
+      <c r="X25" s="37"/>
+      <c r="Y25" s="37"/>
     </row>
     <row r="26" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
@@ -2806,49 +2795,49 @@
         <v>6</v>
       </c>
       <c r="E26" s="11"/>
-      <c r="F26" s="29">
+      <c r="F26" s="27">
         <v>0</v>
       </c>
       <c r="G26" s="11"/>
-      <c r="H26" s="29">
+      <c r="H26" s="27">
         <v>6</v>
       </c>
       <c r="I26" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="56">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="61">
+        <v>10000</v>
+      </c>
+      <c r="L26" s="70">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M26" s="72">
+        <v>199153</v>
+      </c>
+      <c r="N26" s="76">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J26" s="61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="66">
-        <v>10000</v>
-      </c>
-      <c r="L26" s="76">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M26" s="78">
-        <v>199153</v>
-      </c>
-      <c r="N26" s="82">
+      <c r="O26" s="73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O26" s="79">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P26" s="41"/>
-      <c r="Q26" s="41"/>
-      <c r="R26" s="56"/>
-      <c r="S26" s="41"/>
-      <c r="T26" s="41"/>
-      <c r="U26" s="41"/>
-      <c r="V26" s="56"/>
-      <c r="W26" s="41"/>
-      <c r="X26" s="41"/>
-      <c r="Y26" s="56"/>
+      <c r="P26" s="37"/>
+      <c r="Q26" s="37"/>
+      <c r="R26" s="37"/>
+      <c r="S26" s="37"/>
+      <c r="T26" s="37"/>
+      <c r="U26" s="37"/>
+      <c r="V26" s="37"/>
+      <c r="W26" s="37"/>
+      <c r="X26" s="37"/>
+      <c r="Y26" s="37"/>
     </row>
     <row r="27" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
@@ -2862,49 +2851,49 @@
         <v>15</v>
       </c>
       <c r="E27" s="19"/>
-      <c r="F27" s="36">
+      <c r="F27" s="34">
         <v>0</v>
       </c>
       <c r="G27" s="20"/>
-      <c r="H27" s="34">
+      <c r="H27" s="32">
         <v>13</v>
       </c>
       <c r="I27" s="11">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="J27" s="56">
+        <f t="shared" si="0"/>
+        <v>520000</v>
+      </c>
+      <c r="K27" s="61">
+        <v>5000</v>
+      </c>
+      <c r="L27" s="70">
+        <f t="shared" si="1"/>
+        <v>10000</v>
+      </c>
+      <c r="M27" s="72">
+        <v>94397</v>
+      </c>
+      <c r="N27" s="76">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="J27" s="61">
-        <f t="shared" si="0"/>
-        <v>520000</v>
-      </c>
-      <c r="K27" s="66">
-        <v>5000</v>
-      </c>
-      <c r="L27" s="76">
-        <f t="shared" si="1"/>
-        <v>10000</v>
-      </c>
-      <c r="M27" s="78">
-        <v>94397</v>
-      </c>
-      <c r="N27" s="82">
+      <c r="O27" s="73">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="O27" s="79">
-        <f t="shared" si="3"/>
         <v>188794</v>
       </c>
-      <c r="P27" s="48"/>
-      <c r="Q27" s="48"/>
-      <c r="R27" s="56"/>
-      <c r="S27" s="59"/>
-      <c r="T27" s="48"/>
-      <c r="U27" s="48"/>
-      <c r="V27" s="56"/>
-      <c r="W27" s="59"/>
-      <c r="X27" s="48"/>
-      <c r="Y27" s="56"/>
+      <c r="P27" s="44"/>
+      <c r="Q27" s="44"/>
+      <c r="R27" s="37"/>
+      <c r="S27" s="54"/>
+      <c r="T27" s="44"/>
+      <c r="U27" s="44"/>
+      <c r="V27" s="37"/>
+      <c r="W27" s="54"/>
+      <c r="X27" s="44"/>
+      <c r="Y27" s="37"/>
     </row>
     <row r="28" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
@@ -2914,26 +2903,26 @@
       <c r="C28" s="17"/>
       <c r="D28" s="23"/>
       <c r="E28" s="16"/>
-      <c r="F28" s="35"/>
+      <c r="F28" s="33"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="33"/>
+      <c r="H28" s="31"/>
       <c r="I28" s="18"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="77"/>
-      <c r="M28" s="77"/>
-      <c r="N28" s="77"/>
-      <c r="O28" s="77"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="56"/>
-      <c r="S28" s="41"/>
-      <c r="T28" s="41"/>
-      <c r="U28" s="41"/>
-      <c r="V28" s="56"/>
-      <c r="W28" s="41"/>
-      <c r="X28" s="41"/>
-      <c r="Y28" s="56"/>
+      <c r="J28" s="57"/>
+      <c r="K28" s="60"/>
+      <c r="L28" s="71"/>
+      <c r="M28" s="71"/>
+      <c r="N28" s="71"/>
+      <c r="O28" s="71"/>
+      <c r="P28" s="37"/>
+      <c r="Q28" s="37"/>
+      <c r="R28" s="37"/>
+      <c r="S28" s="37"/>
+      <c r="T28" s="37"/>
+      <c r="U28" s="37"/>
+      <c r="V28" s="37"/>
+      <c r="W28" s="37"/>
+      <c r="X28" s="37"/>
+      <c r="Y28" s="37"/>
     </row>
     <row r="29" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
@@ -2947,49 +2936,49 @@
         <v>12</v>
       </c>
       <c r="E29" s="11"/>
-      <c r="F29" s="29">
+      <c r="F29" s="27">
         <v>0</v>
       </c>
       <c r="G29" s="11"/>
-      <c r="H29" s="29">
+      <c r="H29" s="27">
         <v>11</v>
       </c>
       <c r="I29" s="11">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="J29" s="56">
+        <f t="shared" si="0"/>
+        <v>260000</v>
+      </c>
+      <c r="K29" s="61">
+        <v>5000</v>
+      </c>
+      <c r="L29" s="70">
+        <f t="shared" si="1"/>
+        <v>5000</v>
+      </c>
+      <c r="M29" s="102">
+        <v>90000</v>
+      </c>
+      <c r="N29" s="76">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="J29" s="61">
-        <f t="shared" si="0"/>
-        <v>260000</v>
-      </c>
-      <c r="K29" s="66">
-        <v>5000</v>
-      </c>
-      <c r="L29" s="76">
-        <f t="shared" si="1"/>
-        <v>5000</v>
-      </c>
-      <c r="M29" s="109">
+      <c r="O29" s="73">
+        <f t="shared" si="2"/>
         <v>90000</v>
       </c>
-      <c r="N29" s="82">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="O29" s="79">
-        <f t="shared" si="3"/>
-        <v>90000</v>
-      </c>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="56"/>
-      <c r="S29" s="41"/>
-      <c r="T29" s="41"/>
-      <c r="U29" s="41"/>
-      <c r="V29" s="56"/>
-      <c r="W29" s="41"/>
-      <c r="X29" s="41"/>
-      <c r="Y29" s="56"/>
+      <c r="P29" s="37"/>
+      <c r="Q29" s="37"/>
+      <c r="R29" s="37"/>
+      <c r="S29" s="37"/>
+      <c r="T29" s="37"/>
+      <c r="U29" s="37"/>
+      <c r="V29" s="37"/>
+      <c r="W29" s="37"/>
+      <c r="X29" s="37"/>
+      <c r="Y29" s="37"/>
     </row>
     <row r="30" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
@@ -3003,49 +2992,49 @@
         <v>15</v>
       </c>
       <c r="E30" s="11"/>
-      <c r="F30" s="29">
+      <c r="F30" s="27">
         <v>0</v>
       </c>
       <c r="G30" s="11"/>
-      <c r="H30" s="29">
+      <c r="H30" s="27">
         <v>14</v>
       </c>
       <c r="I30" s="11">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="J30" s="56">
+        <f t="shared" si="0"/>
+        <v>160000</v>
+      </c>
+      <c r="K30" s="61">
+        <v>5000</v>
+      </c>
+      <c r="L30" s="70">
+        <f t="shared" si="1"/>
+        <v>5000</v>
+      </c>
+      <c r="M30" s="72">
+        <v>37667</v>
+      </c>
+      <c r="N30" s="76">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="J30" s="61">
-        <f t="shared" si="0"/>
-        <v>160000</v>
-      </c>
-      <c r="K30" s="66">
-        <v>5000</v>
-      </c>
-      <c r="L30" s="76">
-        <f t="shared" si="1"/>
-        <v>5000</v>
-      </c>
-      <c r="M30" s="78">
+      <c r="O30" s="73">
+        <f t="shared" si="2"/>
         <v>37667</v>
       </c>
-      <c r="N30" s="82">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="O30" s="79">
-        <f t="shared" si="3"/>
-        <v>37667</v>
-      </c>
-      <c r="P30" s="48"/>
-      <c r="Q30" s="48"/>
-      <c r="R30" s="56"/>
-      <c r="S30" s="59"/>
-      <c r="T30" s="48"/>
-      <c r="U30" s="48"/>
-      <c r="V30" s="56"/>
-      <c r="W30" s="59"/>
-      <c r="X30" s="48"/>
-      <c r="Y30" s="56"/>
+      <c r="P30" s="44"/>
+      <c r="Q30" s="44"/>
+      <c r="R30" s="37"/>
+      <c r="S30" s="54"/>
+      <c r="T30" s="44"/>
+      <c r="U30" s="44"/>
+      <c r="V30" s="37"/>
+      <c r="W30" s="54"/>
+      <c r="X30" s="44"/>
+      <c r="Y30" s="37"/>
     </row>
     <row r="31" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
@@ -3060,49 +3049,49 @@
         <v>60</v>
       </c>
       <c r="E31" s="13"/>
-      <c r="F31" s="28">
+      <c r="F31" s="26">
         <v>4</v>
       </c>
       <c r="G31" s="15"/>
-      <c r="H31" s="32">
+      <c r="H31" s="30">
         <v>45</v>
       </c>
       <c r="I31" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
-      <c r="J31" s="61">
+      <c r="J31" s="56">
         <f t="shared" si="0"/>
         <v>1760000</v>
       </c>
-      <c r="K31" s="66">
+      <c r="K31" s="61">
         <v>5000</v>
       </c>
-      <c r="L31" s="76">
+      <c r="L31" s="70">
         <f t="shared" si="1"/>
         <v>55000</v>
       </c>
-      <c r="M31" s="78">
+      <c r="M31" s="72">
         <v>41667</v>
       </c>
-      <c r="N31" s="82">
+      <c r="N31" s="76">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="O31" s="73">
         <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-      <c r="O31" s="79">
-        <f t="shared" si="3"/>
         <v>625005</v>
       </c>
-      <c r="P31" s="41"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="56"/>
-      <c r="S31" s="41"/>
-      <c r="T31" s="41"/>
-      <c r="U31" s="41"/>
-      <c r="V31" s="56"/>
-      <c r="W31" s="41"/>
-      <c r="X31" s="41"/>
-      <c r="Y31" s="56"/>
+      <c r="P31" s="37"/>
+      <c r="Q31" s="37"/>
+      <c r="R31" s="37"/>
+      <c r="S31" s="37"/>
+      <c r="T31" s="37"/>
+      <c r="U31" s="37"/>
+      <c r="V31" s="37"/>
+      <c r="W31" s="37"/>
+      <c r="X31" s="37"/>
+      <c r="Y31" s="37"/>
     </row>
     <row r="32" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
@@ -3112,26 +3101,26 @@
       <c r="C32" s="17"/>
       <c r="D32" s="23"/>
       <c r="E32" s="16"/>
-      <c r="F32" s="35"/>
+      <c r="F32" s="33"/>
       <c r="G32" s="18"/>
-      <c r="H32" s="33"/>
+      <c r="H32" s="31"/>
       <c r="I32" s="18"/>
-      <c r="J32" s="62"/>
-      <c r="K32" s="65"/>
-      <c r="L32" s="77"/>
-      <c r="M32" s="77"/>
-      <c r="N32" s="77"/>
-      <c r="O32" s="77"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="56"/>
-      <c r="S32" s="41"/>
-      <c r="T32" s="41"/>
-      <c r="U32" s="41"/>
-      <c r="V32" s="56"/>
-      <c r="W32" s="41"/>
-      <c r="X32" s="41"/>
-      <c r="Y32" s="56"/>
+      <c r="J32" s="57"/>
+      <c r="K32" s="60"/>
+      <c r="L32" s="71"/>
+      <c r="M32" s="71"/>
+      <c r="N32" s="71"/>
+      <c r="O32" s="71"/>
+      <c r="P32" s="37"/>
+      <c r="Q32" s="37"/>
+      <c r="R32" s="37"/>
+      <c r="S32" s="37"/>
+      <c r="T32" s="37"/>
+      <c r="U32" s="37"/>
+      <c r="V32" s="37"/>
+      <c r="W32" s="37"/>
+      <c r="X32" s="37"/>
+      <c r="Y32" s="37"/>
     </row>
     <row r="33" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
@@ -3146,49 +3135,49 @@
         <v>5</v>
       </c>
       <c r="E33" s="11"/>
-      <c r="F33" s="29">
+      <c r="F33" s="27">
         <v>0</v>
       </c>
       <c r="G33" s="11"/>
-      <c r="H33" s="29">
+      <c r="H33" s="27">
         <v>4</v>
       </c>
       <c r="I33" s="11">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="J33" s="56">
+        <f t="shared" si="0"/>
+        <v>360000</v>
+      </c>
+      <c r="K33" s="61">
+        <v>10000</v>
+      </c>
+      <c r="L33" s="70">
+        <f t="shared" si="1"/>
+        <v>10000</v>
+      </c>
+      <c r="M33" s="72">
+        <v>133305</v>
+      </c>
+      <c r="N33" s="76">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="J33" s="61">
-        <f t="shared" si="0"/>
-        <v>360000</v>
-      </c>
-      <c r="K33" s="66">
-        <v>10000</v>
-      </c>
-      <c r="L33" s="76">
-        <f t="shared" si="1"/>
-        <v>10000</v>
-      </c>
-      <c r="M33" s="78">
+      <c r="O33" s="73">
+        <f t="shared" si="2"/>
         <v>133305</v>
       </c>
-      <c r="N33" s="82">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="O33" s="79">
-        <f t="shared" si="3"/>
-        <v>133305</v>
-      </c>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="56"/>
-      <c r="S33" s="41"/>
-      <c r="T33" s="41"/>
-      <c r="U33" s="41"/>
-      <c r="V33" s="56"/>
-      <c r="W33" s="41"/>
-      <c r="X33" s="41"/>
-      <c r="Y33" s="56"/>
+      <c r="P33" s="37"/>
+      <c r="Q33" s="37"/>
+      <c r="R33" s="37"/>
+      <c r="S33" s="37"/>
+      <c r="T33" s="37"/>
+      <c r="U33" s="37"/>
+      <c r="V33" s="37"/>
+      <c r="W33" s="37"/>
+      <c r="X33" s="37"/>
+      <c r="Y33" s="37"/>
     </row>
     <row r="34" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
@@ -3203,49 +3192,49 @@
         <v>24</v>
       </c>
       <c r="E34" s="13"/>
-      <c r="F34" s="28">
+      <c r="F34" s="26">
         <v>4</v>
       </c>
       <c r="G34" s="15"/>
-      <c r="H34" s="32">
+      <c r="H34" s="30">
         <v>15</v>
       </c>
       <c r="I34" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="J34" s="61">
+      <c r="J34" s="56">
         <f t="shared" si="0"/>
         <v>1300000</v>
       </c>
-      <c r="K34" s="66">
+      <c r="K34" s="61">
         <v>5000</v>
       </c>
-      <c r="L34" s="76">
+      <c r="L34" s="70">
         <f t="shared" si="1"/>
         <v>25000</v>
       </c>
-      <c r="M34" s="78">
+      <c r="M34" s="72">
         <v>61489</v>
       </c>
-      <c r="N34" s="82">
+      <c r="N34" s="76">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="O34" s="73">
         <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="O34" s="79">
-        <f t="shared" si="3"/>
         <v>553401</v>
       </c>
-      <c r="P34" s="48"/>
-      <c r="Q34" s="48"/>
-      <c r="R34" s="56"/>
-      <c r="S34" s="59"/>
-      <c r="T34" s="48"/>
-      <c r="U34" s="48"/>
-      <c r="V34" s="56"/>
-      <c r="W34" s="59"/>
-      <c r="X34" s="48"/>
-      <c r="Y34" s="56"/>
+      <c r="P34" s="44"/>
+      <c r="Q34" s="44"/>
+      <c r="R34" s="37"/>
+      <c r="S34" s="54"/>
+      <c r="T34" s="44"/>
+      <c r="U34" s="44"/>
+      <c r="V34" s="37"/>
+      <c r="W34" s="54"/>
+      <c r="X34" s="44"/>
+      <c r="Y34" s="37"/>
     </row>
     <row r="35" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
@@ -3255,26 +3244,26 @@
       <c r="C35" s="17"/>
       <c r="D35" s="24"/>
       <c r="E35" s="16"/>
-      <c r="F35" s="35"/>
+      <c r="F35" s="33"/>
       <c r="G35" s="18"/>
-      <c r="H35" s="33"/>
+      <c r="H35" s="31"/>
       <c r="I35" s="18"/>
-      <c r="J35" s="62"/>
-      <c r="K35" s="45"/>
-      <c r="L35" s="77"/>
-      <c r="M35" s="77"/>
-      <c r="N35" s="77"/>
-      <c r="O35" s="77"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="56"/>
-      <c r="S35" s="41"/>
-      <c r="T35" s="41"/>
-      <c r="U35" s="41"/>
-      <c r="V35" s="56"/>
-      <c r="W35" s="41"/>
-      <c r="X35" s="41"/>
-      <c r="Y35" s="56"/>
+      <c r="J35" s="57"/>
+      <c r="K35" s="41"/>
+      <c r="L35" s="71"/>
+      <c r="M35" s="71"/>
+      <c r="N35" s="71"/>
+      <c r="O35" s="71"/>
+      <c r="P35" s="37"/>
+      <c r="Q35" s="37"/>
+      <c r="R35" s="37"/>
+      <c r="S35" s="37"/>
+      <c r="T35" s="37"/>
+      <c r="U35" s="37"/>
+      <c r="V35" s="37"/>
+      <c r="W35" s="37"/>
+      <c r="X35" s="37"/>
+      <c r="Y35" s="37"/>
     </row>
     <row r="36" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
@@ -3288,49 +3277,49 @@
         <v>24</v>
       </c>
       <c r="E36" s="11"/>
-      <c r="F36" s="29">
+      <c r="F36" s="27">
         <v>0</v>
       </c>
       <c r="G36" s="11"/>
-      <c r="H36" s="29">
+      <c r="H36" s="27">
         <v>21</v>
       </c>
       <c r="I36" s="11">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="J36" s="56">
+        <f t="shared" si="0"/>
+        <v>540000</v>
+      </c>
+      <c r="K36" s="61">
+        <v>5000</v>
+      </c>
+      <c r="L36" s="70">
+        <f t="shared" si="1"/>
+        <v>15000</v>
+      </c>
+      <c r="M36" s="72">
+        <v>47500</v>
+      </c>
+      <c r="N36" s="76">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="J36" s="61">
-        <f t="shared" si="0"/>
-        <v>540000</v>
-      </c>
-      <c r="K36" s="66">
-        <v>5000</v>
-      </c>
-      <c r="L36" s="76">
-        <f t="shared" si="1"/>
-        <v>15000</v>
-      </c>
-      <c r="M36" s="78">
-        <v>47500</v>
-      </c>
-      <c r="N36" s="82">
+      <c r="O36" s="73">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="O36" s="79">
-        <f t="shared" si="3"/>
         <v>142500</v>
       </c>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="56"/>
-      <c r="S36" s="41"/>
-      <c r="T36" s="41"/>
-      <c r="U36" s="41"/>
-      <c r="V36" s="56"/>
-      <c r="W36" s="41"/>
-      <c r="X36" s="41"/>
-      <c r="Y36" s="56"/>
+      <c r="P36" s="37"/>
+      <c r="Q36" s="37"/>
+      <c r="R36" s="37"/>
+      <c r="S36" s="37"/>
+      <c r="T36" s="37"/>
+      <c r="U36" s="37"/>
+      <c r="V36" s="37"/>
+      <c r="W36" s="37"/>
+      <c r="X36" s="37"/>
+      <c r="Y36" s="37"/>
     </row>
     <row r="37" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
@@ -3340,56 +3329,56 @@
       <c r="C37" s="12">
         <v>260000</v>
       </c>
-      <c r="D37" s="29">
+      <c r="D37" s="27">
         <f>42</f>
         <v>42</v>
       </c>
       <c r="E37" s="11"/>
-      <c r="F37" s="29">
+      <c r="F37" s="27">
         <v>0</v>
       </c>
       <c r="G37" s="11">
         <v>1</v>
       </c>
-      <c r="H37" s="29">
+      <c r="H37" s="27">
         <v>19</v>
       </c>
       <c r="I37" s="11">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="J37" s="56">
+        <f t="shared" si="0"/>
+        <v>5720000</v>
+      </c>
+      <c r="K37" s="61">
+        <v>5000</v>
+      </c>
+      <c r="L37" s="70">
+        <f t="shared" si="1"/>
+        <v>110000</v>
+      </c>
+      <c r="M37" s="72">
+        <v>97000</v>
+      </c>
+      <c r="N37" s="76">
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="J37" s="61">
-        <f t="shared" si="0"/>
-        <v>5720000</v>
-      </c>
-      <c r="K37" s="66">
-        <v>5000</v>
-      </c>
-      <c r="L37" s="76">
-        <f t="shared" si="1"/>
-        <v>110000</v>
-      </c>
-      <c r="M37" s="78">
-        <v>97000</v>
-      </c>
-      <c r="N37" s="82">
+      <c r="O37" s="73">
         <f t="shared" si="2"/>
-        <v>22</v>
-      </c>
-      <c r="O37" s="79">
-        <f t="shared" si="3"/>
         <v>2134000</v>
       </c>
-      <c r="P37" s="41"/>
-      <c r="Q37" s="41"/>
-      <c r="R37" s="56"/>
-      <c r="S37" s="41"/>
-      <c r="T37" s="41"/>
-      <c r="U37" s="41"/>
-      <c r="V37" s="56"/>
-      <c r="W37" s="41"/>
-      <c r="X37" s="41"/>
-      <c r="Y37" s="56"/>
+      <c r="P37" s="37"/>
+      <c r="Q37" s="37"/>
+      <c r="R37" s="37"/>
+      <c r="S37" s="37"/>
+      <c r="T37" s="37"/>
+      <c r="U37" s="37"/>
+      <c r="V37" s="37"/>
+      <c r="W37" s="37"/>
+      <c r="X37" s="37"/>
+      <c r="Y37" s="37"/>
     </row>
     <row r="38" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
@@ -3403,49 +3392,49 @@
         <v>36</v>
       </c>
       <c r="E38" s="13"/>
-      <c r="F38" s="28">
+      <c r="F38" s="26">
         <v>0</v>
       </c>
       <c r="G38" s="15"/>
-      <c r="H38" s="32">
+      <c r="H38" s="30">
         <v>24</v>
       </c>
       <c r="I38" s="11">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="J38" s="56">
+        <f t="shared" si="0"/>
+        <v>1920000</v>
+      </c>
+      <c r="K38" s="61">
+        <v>5000</v>
+      </c>
+      <c r="L38" s="70">
+        <f t="shared" si="1"/>
+        <v>60000</v>
+      </c>
+      <c r="M38" s="72">
+        <v>43500</v>
+      </c>
+      <c r="N38" s="76">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="J38" s="61">
-        <f t="shared" si="0"/>
-        <v>1920000</v>
-      </c>
-      <c r="K38" s="66">
-        <v>5000</v>
-      </c>
-      <c r="L38" s="76">
-        <f t="shared" si="1"/>
-        <v>60000</v>
-      </c>
-      <c r="M38" s="78">
-        <v>43500</v>
-      </c>
-      <c r="N38" s="82">
+      <c r="O38" s="73">
         <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="O38" s="79">
-        <f t="shared" si="3"/>
         <v>522000</v>
       </c>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="56"/>
-      <c r="S38" s="41"/>
-      <c r="T38" s="41"/>
-      <c r="U38" s="41"/>
-      <c r="V38" s="56"/>
-      <c r="W38" s="41"/>
-      <c r="X38" s="41"/>
-      <c r="Y38" s="56"/>
+      <c r="P38" s="37"/>
+      <c r="Q38" s="37"/>
+      <c r="R38" s="37"/>
+      <c r="S38" s="37"/>
+      <c r="T38" s="37"/>
+      <c r="U38" s="37"/>
+      <c r="V38" s="37"/>
+      <c r="W38" s="37"/>
+      <c r="X38" s="37"/>
+      <c r="Y38" s="37"/>
     </row>
     <row r="39" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="7" t="s">
@@ -3455,29 +3444,29 @@
       <c r="C39" s="17"/>
       <c r="D39" s="24"/>
       <c r="E39" s="16"/>
-      <c r="F39" s="35"/>
+      <c r="F39" s="33"/>
       <c r="G39" s="18"/>
-      <c r="H39" s="33"/>
-      <c r="I39" s="33"/>
-      <c r="J39" s="62"/>
-      <c r="K39" s="45"/>
-      <c r="L39" s="77"/>
-      <c r="M39" s="77"/>
-      <c r="N39" s="77"/>
-      <c r="O39" s="77"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="56"/>
-      <c r="S39" s="41"/>
-      <c r="T39" s="41"/>
-      <c r="U39" s="41"/>
-      <c r="V39" s="56"/>
-      <c r="W39" s="41"/>
-      <c r="X39" s="41"/>
-      <c r="Y39" s="56"/>
+      <c r="H39" s="31"/>
+      <c r="I39" s="31"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="41"/>
+      <c r="L39" s="71"/>
+      <c r="M39" s="71"/>
+      <c r="N39" s="71"/>
+      <c r="O39" s="71"/>
+      <c r="P39" s="37"/>
+      <c r="Q39" s="37"/>
+      <c r="R39" s="37"/>
+      <c r="S39" s="37"/>
+      <c r="T39" s="37"/>
+      <c r="U39" s="37"/>
+      <c r="V39" s="37"/>
+      <c r="W39" s="37"/>
+      <c r="X39" s="37"/>
+      <c r="Y39" s="37"/>
     </row>
     <row r="40" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="43" t="s">
+      <c r="A40" s="39" t="s">
         <v>21</v>
       </c>
       <c r="B40" s="11"/>
@@ -3488,52 +3477,52 @@
         <v>105</v>
       </c>
       <c r="E40" s="11"/>
-      <c r="F40" s="29">
+      <c r="F40" s="27">
         <v>0</v>
       </c>
       <c r="G40" s="11"/>
-      <c r="H40" s="29">
+      <c r="H40" s="27">
         <v>22</v>
       </c>
       <c r="I40" s="11">
+        <f t="shared" si="3"/>
+        <v>83</v>
+      </c>
+      <c r="J40" s="56">
+        <f t="shared" si="0"/>
+        <v>415000</v>
+      </c>
+      <c r="K40" s="59">
+        <v>0</v>
+      </c>
+      <c r="L40" s="70">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M40" s="72">
+        <v>1250</v>
+      </c>
+      <c r="N40" s="76">
         <f t="shared" si="4"/>
         <v>83</v>
       </c>
-      <c r="J40" s="61">
-        <f t="shared" si="0"/>
-        <v>415000</v>
-      </c>
-      <c r="K40" s="64">
-        <v>0</v>
-      </c>
-      <c r="L40" s="76">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M40" s="78">
-        <v>1250</v>
-      </c>
-      <c r="N40" s="82">
+      <c r="O40" s="73">
         <f t="shared" si="2"/>
-        <v>83</v>
-      </c>
-      <c r="O40" s="79">
-        <f t="shared" si="3"/>
         <v>103750</v>
       </c>
-      <c r="P40" s="41"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="56"/>
-      <c r="S40" s="41"/>
-      <c r="T40" s="41"/>
-      <c r="U40" s="41"/>
-      <c r="V40" s="56"/>
-      <c r="W40" s="41"/>
-      <c r="X40" s="41"/>
-      <c r="Y40" s="56"/>
+      <c r="P40" s="37"/>
+      <c r="Q40" s="37"/>
+      <c r="R40" s="37"/>
+      <c r="S40" s="37"/>
+      <c r="T40" s="37"/>
+      <c r="U40" s="37"/>
+      <c r="V40" s="37"/>
+      <c r="W40" s="37"/>
+      <c r="X40" s="37"/>
+      <c r="Y40" s="37"/>
     </row>
     <row r="41" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="42" t="s">
+      <c r="A41" s="38" t="s">
         <v>50</v>
       </c>
       <c r="B41" s="11"/>
@@ -3545,52 +3534,52 @@
         <v>480</v>
       </c>
       <c r="E41" s="11"/>
-      <c r="F41" s="29">
+      <c r="F41" s="27">
         <v>0</v>
       </c>
       <c r="G41" s="11"/>
-      <c r="H41" s="29">
+      <c r="H41" s="27">
         <v>240</v>
       </c>
       <c r="I41" s="11">
+        <f t="shared" si="3"/>
+        <v>240</v>
+      </c>
+      <c r="J41" s="56">
+        <f t="shared" si="0"/>
+        <v>480000</v>
+      </c>
+      <c r="K41" s="59">
+        <v>0</v>
+      </c>
+      <c r="L41" s="70">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M41" s="72">
+        <v>375</v>
+      </c>
+      <c r="N41" s="76">
         <f t="shared" si="4"/>
         <v>240</v>
       </c>
-      <c r="J41" s="61">
-        <f t="shared" si="0"/>
-        <v>480000</v>
-      </c>
-      <c r="K41" s="64">
-        <v>0</v>
-      </c>
-      <c r="L41" s="76">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M41" s="78">
-        <v>375</v>
-      </c>
-      <c r="N41" s="82">
+      <c r="O41" s="73">
         <f t="shared" si="2"/>
-        <v>240</v>
-      </c>
-      <c r="O41" s="79">
-        <f t="shared" si="3"/>
         <v>90000</v>
       </c>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="56"/>
-      <c r="S41" s="41"/>
-      <c r="T41" s="41"/>
-      <c r="U41" s="41"/>
-      <c r="V41" s="56"/>
-      <c r="W41" s="41"/>
-      <c r="X41" s="41"/>
-      <c r="Y41" s="56"/>
+      <c r="P41" s="37"/>
+      <c r="Q41" s="37"/>
+      <c r="R41" s="37"/>
+      <c r="S41" s="37"/>
+      <c r="T41" s="37"/>
+      <c r="U41" s="37"/>
+      <c r="V41" s="37"/>
+      <c r="W41" s="37"/>
+      <c r="X41" s="37"/>
+      <c r="Y41" s="37"/>
     </row>
     <row r="42" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="42" t="s">
+      <c r="A42" s="38" t="s">
         <v>51</v>
       </c>
       <c r="B42" s="15"/>
@@ -3602,85 +3591,85 @@
         <v>120</v>
       </c>
       <c r="E42" s="15"/>
-      <c r="F42" s="32">
+      <c r="F42" s="30">
         <v>2</v>
       </c>
       <c r="G42" s="15"/>
-      <c r="H42" s="32">
+      <c r="H42" s="30">
         <v>32</v>
       </c>
       <c r="I42" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>86</v>
       </c>
-      <c r="J42" s="61">
+      <c r="J42" s="56">
         <f t="shared" si="0"/>
         <v>1290000</v>
       </c>
-      <c r="K42" s="64">
+      <c r="K42" s="59">
         <v>500</v>
       </c>
-      <c r="L42" s="76">
+      <c r="L42" s="70">
         <f t="shared" si="1"/>
         <v>43000</v>
       </c>
-      <c r="M42" s="109">
+      <c r="M42" s="102">
         <v>8000</v>
       </c>
-      <c r="N42" s="82">
+      <c r="N42" s="76">
+        <f t="shared" si="4"/>
+        <v>88</v>
+      </c>
+      <c r="O42" s="73">
         <f t="shared" si="2"/>
-        <v>88</v>
-      </c>
-      <c r="O42" s="79">
-        <f t="shared" si="3"/>
         <v>704000</v>
       </c>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="56"/>
-      <c r="S42" s="41"/>
-      <c r="T42" s="41"/>
-      <c r="U42" s="41"/>
-      <c r="V42" s="56"/>
-      <c r="W42" s="41"/>
-      <c r="X42" s="41"/>
-      <c r="Y42" s="56"/>
+      <c r="P42" s="37"/>
+      <c r="Q42" s="37"/>
+      <c r="R42" s="37"/>
+      <c r="S42" s="37"/>
+      <c r="T42" s="37"/>
+      <c r="U42" s="37"/>
+      <c r="V42" s="37"/>
+      <c r="W42" s="37"/>
+      <c r="X42" s="37"/>
+      <c r="Y42" s="37"/>
     </row>
     <row r="43" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="44"/>
+      <c r="A43" s="40"/>
       <c r="B43" s="11"/>
       <c r="C43" s="12"/>
-      <c r="D43" s="29"/>
+      <c r="D43" s="27"/>
       <c r="E43" s="11"/>
-      <c r="F43" s="29"/>
+      <c r="F43" s="27"/>
       <c r="G43" s="11"/>
-      <c r="H43" s="29"/>
+      <c r="H43" s="27"/>
       <c r="I43" s="11"/>
-      <c r="J43" s="61">
+      <c r="J43" s="56">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K43" s="37"/>
-      <c r="L43" s="75"/>
-      <c r="M43" s="78"/>
-      <c r="N43" s="82">
+      <c r="K43" s="21"/>
+      <c r="L43" s="69"/>
+      <c r="M43" s="72"/>
+      <c r="N43" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O43" s="73">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O43" s="79">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="56"/>
-      <c r="S43" s="41"/>
-      <c r="T43" s="41"/>
-      <c r="U43" s="41"/>
-      <c r="V43" s="56"/>
-      <c r="W43" s="41"/>
-      <c r="X43" s="41"/>
-      <c r="Y43" s="56"/>
+      <c r="P43" s="37"/>
+      <c r="Q43" s="37"/>
+      <c r="R43" s="37"/>
+      <c r="S43" s="37"/>
+      <c r="T43" s="37"/>
+      <c r="U43" s="37"/>
+      <c r="V43" s="37"/>
+      <c r="W43" s="37"/>
+      <c r="X43" s="37"/>
+      <c r="Y43" s="37"/>
     </row>
     <row r="44" spans="1:25" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="4"/>
@@ -3694,799 +3683,787 @@
       <c r="I44" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J44" s="63">
+      <c r="J44" s="58">
         <f>SUM(J3:J43)</f>
         <v>62715000</v>
       </c>
-      <c r="K44" s="37"/>
-      <c r="L44" s="67">
+      <c r="K44" s="21"/>
+      <c r="L44" s="62">
         <f>SUM(L3:L43)</f>
         <v>2002000</v>
       </c>
-      <c r="M44" s="73"/>
-      <c r="N44" s="73"/>
-      <c r="O44" s="80">
+      <c r="M44" s="67"/>
+      <c r="N44" s="67"/>
+      <c r="O44" s="74">
         <f>SUM(O3:O43)</f>
         <v>14496946</v>
       </c>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="56"/>
-      <c r="S44" s="41"/>
-      <c r="T44" s="41"/>
-      <c r="U44" s="41"/>
-      <c r="V44" s="56"/>
-      <c r="W44" s="41"/>
-      <c r="X44" s="41"/>
-      <c r="Y44" s="56"/>
+      <c r="P44" s="37"/>
+      <c r="Q44" s="37"/>
+      <c r="R44" s="37"/>
+      <c r="S44" s="37"/>
+      <c r="T44" s="37"/>
+      <c r="U44" s="37"/>
+      <c r="V44" s="37"/>
+      <c r="W44" s="37"/>
+      <c r="X44" s="37"/>
+      <c r="Y44" s="37"/>
     </row>
     <row r="45" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O45" s="59"/>
-      <c r="P45" s="48"/>
-      <c r="Q45" s="48"/>
-      <c r="R45" s="56"/>
-      <c r="S45" s="59"/>
-      <c r="T45" s="48"/>
-      <c r="U45" s="48"/>
-      <c r="V45" s="56"/>
-      <c r="W45" s="59"/>
-      <c r="X45" s="48"/>
-      <c r="Y45" s="56"/>
+      <c r="O45" s="54"/>
+      <c r="P45" s="44"/>
+      <c r="Q45" s="44"/>
+      <c r="R45" s="37"/>
+      <c r="S45" s="54"/>
+      <c r="T45" s="44"/>
+      <c r="U45" s="44"/>
+      <c r="V45" s="37"/>
+      <c r="W45" s="54"/>
+      <c r="X45" s="44"/>
+      <c r="Y45" s="37"/>
     </row>
     <row r="46" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="105" t="s">
+      <c r="A46" s="98" t="s">
         <v>176</v>
       </c>
-      <c r="B46" s="106"/>
-      <c r="I46" s="84" t="s">
+      <c r="B46" s="99"/>
+      <c r="F46">
+        <v>3173651958</v>
+      </c>
+      <c r="G46" t="s">
+        <v>180</v>
+      </c>
+      <c r="I46" s="78" t="s">
         <v>172</v>
       </c>
-      <c r="J46" s="78">
+      <c r="J46" s="72">
         <v>570000</v>
       </c>
-      <c r="O46" s="41"/>
-      <c r="P46" s="41"/>
-      <c r="Q46" s="41"/>
-      <c r="R46" s="56"/>
-      <c r="S46" s="41"/>
-      <c r="T46" s="41"/>
-      <c r="U46" s="41"/>
-      <c r="V46" s="56"/>
-      <c r="W46" s="41"/>
-      <c r="X46" s="41"/>
-      <c r="Y46" s="56"/>
+      <c r="O46" s="37"/>
+      <c r="P46" s="37"/>
+      <c r="Q46" s="37"/>
+      <c r="R46" s="37"/>
+      <c r="S46" s="37"/>
+      <c r="T46" s="37"/>
+      <c r="U46" s="37"/>
+      <c r="V46" s="37"/>
+      <c r="W46" s="37"/>
+      <c r="X46" s="37"/>
+      <c r="Y46" s="37"/>
     </row>
     <row r="47" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="84" t="s">
+      <c r="A47" s="78" t="s">
         <v>177</v>
       </c>
-      <c r="B47" s="78">
+      <c r="B47" s="72">
         <v>1350000</v>
       </c>
-      <c r="I47" s="84" t="s">
+      <c r="I47" s="78" t="s">
         <v>173</v>
       </c>
-      <c r="J47" s="78">
+      <c r="J47" s="72">
         <v>37766000</v>
       </c>
-      <c r="O47" s="41"/>
-      <c r="P47" s="41"/>
-      <c r="Q47" s="41"/>
-      <c r="R47" s="56"/>
-      <c r="S47" s="41"/>
-      <c r="T47" s="41"/>
-      <c r="U47" s="41"/>
-      <c r="V47" s="56"/>
-      <c r="W47" s="41"/>
-      <c r="X47" s="41"/>
-      <c r="Y47" s="56"/>
+      <c r="O47" s="37"/>
+      <c r="P47" s="37"/>
+      <c r="Q47" s="37"/>
+      <c r="R47" s="37"/>
+      <c r="S47" s="37"/>
+      <c r="T47" s="37"/>
+      <c r="U47" s="37"/>
+      <c r="V47" s="37"/>
+      <c r="W47" s="37"/>
+      <c r="X47" s="37"/>
+      <c r="Y47" s="37"/>
     </row>
     <row r="48" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="84" t="s">
+      <c r="A48" s="78" t="s">
         <v>178</v>
       </c>
-      <c r="B48" s="78">
+      <c r="B48" s="72">
         <v>1715900</v>
       </c>
-      <c r="I48" s="85" t="s">
+      <c r="I48" s="78" t="s">
         <v>174</v>
       </c>
-      <c r="J48" s="78">
+      <c r="J48" s="72">
         <v>25201600</v>
       </c>
-      <c r="P48" s="26"/>
-      <c r="Q48" s="26"/>
     </row>
     <row r="49" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="84" t="s">
+      <c r="A49" s="78" t="s">
         <v>179</v>
       </c>
-      <c r="B49" s="78">
+      <c r="B49" s="72">
         <v>822600</v>
       </c>
-      <c r="I49" s="85" t="s">
+      <c r="I49" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="J49" s="78">
+      <c r="J49" s="72">
         <f>J44-J46-J47-J48</f>
         <v>-822600</v>
       </c>
-      <c r="P49" s="26"/>
-      <c r="Q49" s="26"/>
     </row>
     <row r="50" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="107" t="s">
+      <c r="A50" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="B50" s="108">
+      <c r="B50" s="101">
         <f>SUM(B47:B49)</f>
         <v>3888500</v>
       </c>
-      <c r="I50" s="86" t="s">
+      <c r="I50" s="79" t="s">
         <v>175</v>
       </c>
-      <c r="J50" s="87">
+      <c r="J50" s="80">
         <f>J44-O44</f>
         <v>48218054</v>
       </c>
-      <c r="P50" s="26"/>
-      <c r="Q50" s="26"/>
-    </row>
-    <row r="51" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P51" s="26"/>
-      <c r="Q51" s="26"/>
-    </row>
-    <row r="52" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P52" s="26"/>
-      <c r="Q52" s="26"/>
-    </row>
-    <row r="53" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="P53" s="26"/>
-      <c r="Q53" s="26"/>
     </row>
     <row r="54" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H54" s="39"/>
-      <c r="I54" s="39"/>
-      <c r="J54" s="39"/>
-      <c r="K54" s="39"/>
-      <c r="L54" s="39"/>
-      <c r="M54" s="39"/>
-      <c r="N54" s="39"/>
-      <c r="O54" s="39"/>
-      <c r="P54" s="39"/>
-      <c r="Q54" s="39"/>
-      <c r="R54" s="39"/>
-      <c r="S54" s="39"/>
+      <c r="H54" s="35"/>
+      <c r="I54" s="35"/>
+      <c r="J54" s="35"/>
+      <c r="K54" s="35"/>
+      <c r="L54" s="35"/>
+      <c r="M54" s="35"/>
+      <c r="N54" s="35"/>
+      <c r="O54" s="35"/>
+      <c r="P54" s="35"/>
+      <c r="Q54" s="35"/>
+      <c r="R54" s="35"/>
+      <c r="S54" s="35"/>
     </row>
     <row r="55" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H55" s="39"/>
-      <c r="I55" s="39"/>
-      <c r="J55" s="39"/>
-      <c r="K55" s="39"/>
-      <c r="L55" s="39"/>
-      <c r="M55" s="39"/>
-      <c r="N55" s="39"/>
-      <c r="O55" s="39"/>
-      <c r="P55" s="39"/>
-      <c r="Q55" s="39"/>
-      <c r="R55" s="39"/>
-      <c r="S55" s="39"/>
+      <c r="H55" s="35"/>
+      <c r="I55" s="35"/>
+      <c r="J55" s="35"/>
+      <c r="K55" s="35"/>
+      <c r="L55" s="35"/>
+      <c r="M55" s="35"/>
+      <c r="N55" s="35"/>
+      <c r="O55" s="35"/>
+      <c r="P55" s="35"/>
+      <c r="Q55" s="35"/>
+      <c r="R55" s="35"/>
+      <c r="S55" s="35"/>
     </row>
     <row r="56" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H56" s="39"/>
-      <c r="I56" s="92"/>
-      <c r="J56" s="92"/>
-      <c r="K56" s="39"/>
-      <c r="L56" s="39"/>
-      <c r="M56" s="39"/>
-      <c r="N56" s="39"/>
-      <c r="O56" s="39"/>
-      <c r="P56" s="39"/>
-      <c r="Q56" s="39"/>
-      <c r="R56" s="39"/>
-      <c r="S56" s="39"/>
+      <c r="H56" s="35"/>
+      <c r="I56" s="85"/>
+      <c r="J56" s="85"/>
+      <c r="K56" s="35"/>
+      <c r="L56" s="35"/>
+      <c r="M56" s="35"/>
+      <c r="N56" s="35"/>
+      <c r="O56" s="35"/>
+      <c r="P56" s="35"/>
+      <c r="Q56" s="35"/>
+      <c r="R56" s="35"/>
+      <c r="S56" s="35"/>
     </row>
     <row r="57" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H57" s="93"/>
-      <c r="I57" s="94"/>
-      <c r="J57" s="95"/>
-      <c r="K57" s="39"/>
-      <c r="L57" s="39"/>
-      <c r="M57" s="39"/>
-      <c r="N57" s="39"/>
-      <c r="O57" s="39"/>
-      <c r="P57" s="39"/>
-      <c r="Q57" s="92"/>
-      <c r="R57" s="39"/>
-      <c r="S57" s="39"/>
+      <c r="H57" s="86"/>
+      <c r="I57" s="87"/>
+      <c r="J57" s="88"/>
+      <c r="K57" s="35"/>
+      <c r="L57" s="35"/>
+      <c r="M57" s="35"/>
+      <c r="N57" s="35"/>
+      <c r="O57" s="35"/>
+      <c r="P57" s="35"/>
+      <c r="Q57" s="85"/>
+      <c r="R57" s="35"/>
+      <c r="S57" s="35"/>
     </row>
     <row r="58" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H58" s="96"/>
-      <c r="I58" s="97"/>
-      <c r="J58" s="98"/>
-      <c r="K58" s="98"/>
-      <c r="L58" s="98"/>
-      <c r="M58" s="98"/>
-      <c r="N58" s="98"/>
-      <c r="O58" s="39"/>
-      <c r="P58" s="93"/>
-      <c r="Q58" s="94"/>
-      <c r="R58" s="95"/>
-      <c r="S58" s="39"/>
+      <c r="H58" s="89"/>
+      <c r="I58" s="90"/>
+      <c r="J58" s="91"/>
+      <c r="K58" s="91"/>
+      <c r="L58" s="91"/>
+      <c r="M58" s="91"/>
+      <c r="N58" s="91"/>
+      <c r="O58" s="35"/>
+      <c r="P58" s="86"/>
+      <c r="Q58" s="87"/>
+      <c r="R58" s="88"/>
+      <c r="S58" s="35"/>
     </row>
     <row r="59" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H59" s="96"/>
-      <c r="I59" s="99"/>
-      <c r="J59" s="98"/>
-      <c r="K59" s="98"/>
-      <c r="L59" s="98"/>
-      <c r="M59" s="98"/>
-      <c r="N59" s="98"/>
-      <c r="O59" s="39"/>
-      <c r="P59" s="96"/>
-      <c r="Q59" s="97"/>
-      <c r="R59" s="98"/>
-      <c r="S59" s="39"/>
+      <c r="H59" s="89"/>
+      <c r="I59" s="92"/>
+      <c r="J59" s="91"/>
+      <c r="K59" s="91"/>
+      <c r="L59" s="91"/>
+      <c r="M59" s="91"/>
+      <c r="N59" s="91"/>
+      <c r="O59" s="35"/>
+      <c r="P59" s="89"/>
+      <c r="Q59" s="90"/>
+      <c r="R59" s="91"/>
+      <c r="S59" s="35"/>
     </row>
     <row r="60" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H60" s="96"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="98"/>
-      <c r="K60" s="98"/>
-      <c r="L60" s="98"/>
-      <c r="M60" s="98"/>
-      <c r="N60" s="98"/>
-      <c r="O60" s="39"/>
-      <c r="P60" s="96"/>
-      <c r="Q60" s="97"/>
-      <c r="R60" s="98"/>
-      <c r="S60" s="39"/>
+      <c r="H60" s="89"/>
+      <c r="I60" s="90"/>
+      <c r="J60" s="91"/>
+      <c r="K60" s="91"/>
+      <c r="L60" s="91"/>
+      <c r="M60" s="91"/>
+      <c r="N60" s="91"/>
+      <c r="O60" s="35"/>
+      <c r="P60" s="89"/>
+      <c r="Q60" s="90"/>
+      <c r="R60" s="91"/>
+      <c r="S60" s="35"/>
     </row>
     <row r="61" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H61" s="96"/>
-      <c r="I61" s="97"/>
-      <c r="J61" s="98"/>
-      <c r="K61" s="98"/>
-      <c r="L61" s="98"/>
-      <c r="M61" s="98"/>
-      <c r="N61" s="98"/>
-      <c r="O61" s="39"/>
-      <c r="P61" s="96"/>
-      <c r="Q61" s="97"/>
-      <c r="R61" s="98"/>
-      <c r="S61" s="39"/>
+      <c r="H61" s="89"/>
+      <c r="I61" s="90"/>
+      <c r="J61" s="91"/>
+      <c r="K61" s="91"/>
+      <c r="L61" s="91"/>
+      <c r="M61" s="91"/>
+      <c r="N61" s="91"/>
+      <c r="O61" s="35"/>
+      <c r="P61" s="89"/>
+      <c r="Q61" s="90"/>
+      <c r="R61" s="91"/>
+      <c r="S61" s="35"/>
     </row>
     <row r="62" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H62" s="96"/>
-      <c r="I62" s="97"/>
-      <c r="J62" s="98"/>
-      <c r="K62" s="98"/>
-      <c r="L62" s="98"/>
-      <c r="M62" s="98"/>
-      <c r="N62" s="98"/>
-      <c r="O62" s="39"/>
-      <c r="P62" s="96"/>
-      <c r="Q62" s="97"/>
-      <c r="R62" s="100"/>
-      <c r="S62" s="39"/>
+      <c r="H62" s="89"/>
+      <c r="I62" s="90"/>
+      <c r="J62" s="91"/>
+      <c r="K62" s="91"/>
+      <c r="L62" s="91"/>
+      <c r="M62" s="91"/>
+      <c r="N62" s="91"/>
+      <c r="O62" s="35"/>
+      <c r="P62" s="89"/>
+      <c r="Q62" s="90"/>
+      <c r="R62" s="93"/>
+      <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H63" s="96"/>
-      <c r="I63" s="97"/>
-      <c r="J63" s="98"/>
-      <c r="K63" s="98"/>
-      <c r="L63" s="98"/>
-      <c r="M63" s="98"/>
-      <c r="N63" s="98"/>
-      <c r="O63" s="39"/>
-      <c r="P63" s="96"/>
-      <c r="Q63" s="97"/>
-      <c r="R63" s="100"/>
-      <c r="S63" s="39"/>
+      <c r="H63" s="89"/>
+      <c r="I63" s="90"/>
+      <c r="J63" s="91"/>
+      <c r="K63" s="91"/>
+      <c r="L63" s="91"/>
+      <c r="M63" s="91"/>
+      <c r="N63" s="91"/>
+      <c r="O63" s="35"/>
+      <c r="P63" s="89"/>
+      <c r="Q63" s="90"/>
+      <c r="R63" s="93"/>
+      <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H64" s="96"/>
-      <c r="I64" s="97"/>
-      <c r="J64" s="98"/>
-      <c r="K64" s="98"/>
-      <c r="L64" s="98"/>
-      <c r="M64" s="98"/>
-      <c r="N64" s="98"/>
-      <c r="O64" s="39"/>
-      <c r="P64" s="96"/>
-      <c r="Q64" s="97"/>
-      <c r="R64" s="98"/>
-      <c r="S64" s="39"/>
+      <c r="H64" s="89"/>
+      <c r="I64" s="90"/>
+      <c r="J64" s="91"/>
+      <c r="K64" s="91"/>
+      <c r="L64" s="91"/>
+      <c r="M64" s="91"/>
+      <c r="N64" s="91"/>
+      <c r="O64" s="35"/>
+      <c r="P64" s="89"/>
+      <c r="Q64" s="90"/>
+      <c r="R64" s="91"/>
+      <c r="S64" s="35"/>
     </row>
     <row r="65" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H65" s="96"/>
-      <c r="I65" s="97"/>
-      <c r="J65" s="98"/>
-      <c r="K65" s="98"/>
-      <c r="L65" s="98"/>
-      <c r="M65" s="98"/>
-      <c r="N65" s="98"/>
-      <c r="O65" s="39"/>
-      <c r="P65" s="96"/>
-      <c r="Q65" s="97"/>
-      <c r="R65" s="100"/>
-      <c r="S65" s="39"/>
+      <c r="H65" s="89"/>
+      <c r="I65" s="90"/>
+      <c r="J65" s="91"/>
+      <c r="K65" s="91"/>
+      <c r="L65" s="91"/>
+      <c r="M65" s="91"/>
+      <c r="N65" s="91"/>
+      <c r="O65" s="35"/>
+      <c r="P65" s="89"/>
+      <c r="Q65" s="90"/>
+      <c r="R65" s="93"/>
+      <c r="S65" s="35"/>
     </row>
     <row r="66" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H66" s="96"/>
-      <c r="I66" s="88"/>
-      <c r="J66" s="100"/>
-      <c r="K66" s="98"/>
-      <c r="L66" s="98"/>
-      <c r="M66" s="98"/>
-      <c r="N66" s="98"/>
-      <c r="O66" s="39"/>
-      <c r="P66" s="96"/>
-      <c r="Q66" s="97"/>
-      <c r="R66" s="98"/>
-      <c r="S66" s="39"/>
+      <c r="H66" s="89"/>
+      <c r="I66" s="81"/>
+      <c r="J66" s="93"/>
+      <c r="K66" s="91"/>
+      <c r="L66" s="91"/>
+      <c r="M66" s="91"/>
+      <c r="N66" s="91"/>
+      <c r="O66" s="35"/>
+      <c r="P66" s="89"/>
+      <c r="Q66" s="90"/>
+      <c r="R66" s="91"/>
+      <c r="S66" s="35"/>
     </row>
     <row r="67" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H67" s="101"/>
-      <c r="I67" s="88"/>
-      <c r="J67" s="100"/>
-      <c r="K67" s="100"/>
-      <c r="L67" s="100"/>
-      <c r="M67" s="100"/>
-      <c r="N67" s="100"/>
-      <c r="O67" s="39"/>
-      <c r="P67" s="96"/>
-      <c r="Q67" s="89"/>
-      <c r="R67" s="100"/>
-      <c r="S67" s="39"/>
+      <c r="H67" s="94"/>
+      <c r="I67" s="81"/>
+      <c r="J67" s="93"/>
+      <c r="K67" s="93"/>
+      <c r="L67" s="93"/>
+      <c r="M67" s="93"/>
+      <c r="N67" s="93"/>
+      <c r="O67" s="35"/>
+      <c r="P67" s="89"/>
+      <c r="Q67" s="82"/>
+      <c r="R67" s="93"/>
+      <c r="S67" s="35"/>
     </row>
     <row r="68" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H68" s="96"/>
-      <c r="I68" s="97"/>
-      <c r="J68" s="98"/>
-      <c r="K68" s="98"/>
-      <c r="L68" s="98"/>
-      <c r="M68" s="98"/>
-      <c r="N68" s="98"/>
-      <c r="O68" s="39"/>
-      <c r="P68" s="101"/>
-      <c r="Q68" s="89"/>
-      <c r="R68" s="100"/>
-      <c r="S68" s="100"/>
+      <c r="H68" s="89"/>
+      <c r="I68" s="90"/>
+      <c r="J68" s="91"/>
+      <c r="K68" s="91"/>
+      <c r="L68" s="91"/>
+      <c r="M68" s="91"/>
+      <c r="N68" s="91"/>
+      <c r="O68" s="35"/>
+      <c r="P68" s="94"/>
+      <c r="Q68" s="82"/>
+      <c r="R68" s="93"/>
+      <c r="S68" s="93"/>
     </row>
     <row r="69" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H69" s="96"/>
-      <c r="I69" s="88"/>
-      <c r="J69" s="98"/>
-      <c r="K69" s="98"/>
-      <c r="L69" s="98"/>
-      <c r="M69" s="98"/>
-      <c r="N69" s="98"/>
-      <c r="O69" s="39"/>
-      <c r="P69" s="96"/>
-      <c r="Q69" s="97"/>
-      <c r="R69" s="98"/>
-      <c r="S69" s="39"/>
+      <c r="H69" s="89"/>
+      <c r="I69" s="81"/>
+      <c r="J69" s="91"/>
+      <c r="K69" s="91"/>
+      <c r="L69" s="91"/>
+      <c r="M69" s="91"/>
+      <c r="N69" s="91"/>
+      <c r="O69" s="35"/>
+      <c r="P69" s="89"/>
+      <c r="Q69" s="90"/>
+      <c r="R69" s="91"/>
+      <c r="S69" s="35"/>
     </row>
     <row r="70" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H70" s="101"/>
-      <c r="I70" s="88"/>
-      <c r="J70" s="100"/>
-      <c r="K70" s="100"/>
-      <c r="L70" s="100"/>
-      <c r="M70" s="100"/>
-      <c r="N70" s="100"/>
-      <c r="O70" s="39"/>
-      <c r="P70" s="96"/>
-      <c r="Q70" s="89"/>
-      <c r="R70" s="98"/>
-      <c r="S70" s="39"/>
+      <c r="H70" s="94"/>
+      <c r="I70" s="81"/>
+      <c r="J70" s="93"/>
+      <c r="K70" s="93"/>
+      <c r="L70" s="93"/>
+      <c r="M70" s="93"/>
+      <c r="N70" s="93"/>
+      <c r="O70" s="35"/>
+      <c r="P70" s="89"/>
+      <c r="Q70" s="82"/>
+      <c r="R70" s="91"/>
+      <c r="S70" s="35"/>
     </row>
     <row r="71" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H71" s="96"/>
-      <c r="I71" s="88"/>
-      <c r="J71" s="98"/>
-      <c r="K71" s="98"/>
-      <c r="L71" s="98"/>
-      <c r="M71" s="98"/>
-      <c r="N71" s="98"/>
-      <c r="O71" s="39"/>
-      <c r="P71" s="101"/>
-      <c r="Q71" s="89"/>
-      <c r="R71" s="100"/>
-      <c r="S71" s="100"/>
+      <c r="H71" s="89"/>
+      <c r="I71" s="81"/>
+      <c r="J71" s="91"/>
+      <c r="K71" s="91"/>
+      <c r="L71" s="91"/>
+      <c r="M71" s="91"/>
+      <c r="N71" s="91"/>
+      <c r="O71" s="35"/>
+      <c r="P71" s="94"/>
+      <c r="Q71" s="82"/>
+      <c r="R71" s="93"/>
+      <c r="S71" s="93"/>
     </row>
     <row r="72" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H72" s="101"/>
-      <c r="I72" s="88"/>
-      <c r="J72" s="100"/>
-      <c r="K72" s="100"/>
-      <c r="L72" s="100"/>
-      <c r="M72" s="100"/>
-      <c r="N72" s="100"/>
-      <c r="O72" s="39"/>
-      <c r="P72" s="96"/>
-      <c r="Q72" s="89"/>
-      <c r="R72" s="98"/>
-      <c r="S72" s="39"/>
+      <c r="H72" s="94"/>
+      <c r="I72" s="81"/>
+      <c r="J72" s="93"/>
+      <c r="K72" s="93"/>
+      <c r="L72" s="93"/>
+      <c r="M72" s="93"/>
+      <c r="N72" s="93"/>
+      <c r="O72" s="35"/>
+      <c r="P72" s="89"/>
+      <c r="Q72" s="82"/>
+      <c r="R72" s="91"/>
+      <c r="S72" s="35"/>
     </row>
     <row r="73" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H73" s="96"/>
-      <c r="I73" s="97"/>
-      <c r="J73" s="100"/>
-      <c r="K73" s="98"/>
-      <c r="L73" s="98"/>
-      <c r="M73" s="98"/>
-      <c r="N73" s="98"/>
-      <c r="O73" s="39"/>
-      <c r="P73" s="101"/>
-      <c r="Q73" s="89"/>
-      <c r="R73" s="100"/>
-      <c r="S73" s="100"/>
+      <c r="H73" s="89"/>
+      <c r="I73" s="90"/>
+      <c r="J73" s="93"/>
+      <c r="K73" s="91"/>
+      <c r="L73" s="91"/>
+      <c r="M73" s="91"/>
+      <c r="N73" s="91"/>
+      <c r="O73" s="35"/>
+      <c r="P73" s="94"/>
+      <c r="Q73" s="82"/>
+      <c r="R73" s="93"/>
+      <c r="S73" s="93"/>
     </row>
     <row r="74" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H74" s="96"/>
-      <c r="I74" s="97"/>
-      <c r="J74" s="100"/>
-      <c r="K74" s="98"/>
-      <c r="L74" s="98"/>
-      <c r="M74" s="98"/>
-      <c r="N74" s="98"/>
-      <c r="O74" s="39"/>
-      <c r="P74" s="96"/>
-      <c r="Q74" s="97"/>
-      <c r="R74" s="100"/>
-      <c r="S74" s="39"/>
+      <c r="H74" s="89"/>
+      <c r="I74" s="90"/>
+      <c r="J74" s="93"/>
+      <c r="K74" s="91"/>
+      <c r="L74" s="91"/>
+      <c r="M74" s="91"/>
+      <c r="N74" s="91"/>
+      <c r="O74" s="35"/>
+      <c r="P74" s="89"/>
+      <c r="Q74" s="90"/>
+      <c r="R74" s="93"/>
+      <c r="S74" s="35"/>
     </row>
     <row r="75" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H75" s="96"/>
-      <c r="I75" s="88"/>
-      <c r="J75" s="98"/>
-      <c r="K75" s="98"/>
-      <c r="L75" s="98"/>
-      <c r="M75" s="98"/>
-      <c r="N75" s="98"/>
-      <c r="O75" s="39"/>
-      <c r="P75" s="96"/>
-      <c r="Q75" s="97"/>
-      <c r="R75" s="100"/>
-      <c r="S75" s="39"/>
+      <c r="H75" s="89"/>
+      <c r="I75" s="81"/>
+      <c r="J75" s="91"/>
+      <c r="K75" s="91"/>
+      <c r="L75" s="91"/>
+      <c r="M75" s="91"/>
+      <c r="N75" s="91"/>
+      <c r="O75" s="35"/>
+      <c r="P75" s="89"/>
+      <c r="Q75" s="90"/>
+      <c r="R75" s="93"/>
+      <c r="S75" s="35"/>
     </row>
     <row r="76" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H76" s="101"/>
-      <c r="I76" s="88"/>
-      <c r="J76" s="100"/>
-      <c r="K76" s="100"/>
-      <c r="L76" s="100"/>
-      <c r="M76" s="100"/>
-      <c r="N76" s="100"/>
-      <c r="O76" s="39"/>
-      <c r="P76" s="96"/>
-      <c r="Q76" s="89"/>
-      <c r="R76" s="100"/>
-      <c r="S76" s="39"/>
+      <c r="H76" s="94"/>
+      <c r="I76" s="81"/>
+      <c r="J76" s="93"/>
+      <c r="K76" s="93"/>
+      <c r="L76" s="93"/>
+      <c r="M76" s="93"/>
+      <c r="N76" s="93"/>
+      <c r="O76" s="35"/>
+      <c r="P76" s="89"/>
+      <c r="Q76" s="82"/>
+      <c r="R76" s="93"/>
+      <c r="S76" s="35"/>
     </row>
     <row r="77" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H77" s="96"/>
-      <c r="I77" s="97"/>
-      <c r="J77" s="100"/>
-      <c r="K77" s="98"/>
-      <c r="L77" s="98"/>
-      <c r="M77" s="98"/>
-      <c r="N77" s="98"/>
-      <c r="O77" s="39"/>
-      <c r="P77" s="101"/>
-      <c r="Q77" s="89"/>
-      <c r="R77" s="100"/>
-      <c r="S77" s="100"/>
+      <c r="H77" s="89"/>
+      <c r="I77" s="90"/>
+      <c r="J77" s="93"/>
+      <c r="K77" s="91"/>
+      <c r="L77" s="91"/>
+      <c r="M77" s="91"/>
+      <c r="N77" s="91"/>
+      <c r="O77" s="35"/>
+      <c r="P77" s="94"/>
+      <c r="Q77" s="82"/>
+      <c r="R77" s="93"/>
+      <c r="S77" s="93"/>
     </row>
     <row r="78" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H78" s="96"/>
-      <c r="I78" s="88"/>
-      <c r="J78" s="100"/>
-      <c r="K78" s="98"/>
-      <c r="L78" s="98"/>
-      <c r="M78" s="98"/>
-      <c r="N78" s="98"/>
-      <c r="O78" s="39"/>
-      <c r="P78" s="96"/>
-      <c r="Q78" s="97"/>
-      <c r="R78" s="100"/>
-      <c r="S78" s="39"/>
+      <c r="H78" s="89"/>
+      <c r="I78" s="81"/>
+      <c r="J78" s="93"/>
+      <c r="K78" s="91"/>
+      <c r="L78" s="91"/>
+      <c r="M78" s="91"/>
+      <c r="N78" s="91"/>
+      <c r="O78" s="35"/>
+      <c r="P78" s="89"/>
+      <c r="Q78" s="90"/>
+      <c r="R78" s="93"/>
+      <c r="S78" s="35"/>
     </row>
     <row r="79" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H79" s="101"/>
-      <c r="I79" s="88"/>
-      <c r="J79" s="100"/>
-      <c r="K79" s="100"/>
-      <c r="L79" s="100"/>
-      <c r="M79" s="100"/>
-      <c r="N79" s="100"/>
-      <c r="O79" s="39"/>
-      <c r="P79" s="96"/>
-      <c r="Q79" s="89"/>
-      <c r="R79" s="100"/>
-      <c r="S79" s="39"/>
+      <c r="H79" s="94"/>
+      <c r="I79" s="81"/>
+      <c r="J79" s="93"/>
+      <c r="K79" s="93"/>
+      <c r="L79" s="93"/>
+      <c r="M79" s="93"/>
+      <c r="N79" s="93"/>
+      <c r="O79" s="35"/>
+      <c r="P79" s="89"/>
+      <c r="Q79" s="82"/>
+      <c r="R79" s="93"/>
+      <c r="S79" s="35"/>
     </row>
     <row r="80" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H80" s="96"/>
-      <c r="I80" s="97"/>
-      <c r="J80" s="100"/>
-      <c r="K80" s="98"/>
-      <c r="L80" s="98"/>
-      <c r="M80" s="98"/>
-      <c r="N80" s="98"/>
-      <c r="O80" s="39"/>
-      <c r="P80" s="101"/>
-      <c r="Q80" s="89"/>
-      <c r="R80" s="100"/>
-      <c r="S80" s="100"/>
+      <c r="H80" s="89"/>
+      <c r="I80" s="90"/>
+      <c r="J80" s="93"/>
+      <c r="K80" s="91"/>
+      <c r="L80" s="91"/>
+      <c r="M80" s="91"/>
+      <c r="N80" s="91"/>
+      <c r="O80" s="35"/>
+      <c r="P80" s="94"/>
+      <c r="Q80" s="82"/>
+      <c r="R80" s="93"/>
+      <c r="S80" s="93"/>
     </row>
     <row r="81" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H81" s="96"/>
-      <c r="I81" s="97"/>
-      <c r="J81" s="100"/>
-      <c r="K81" s="98"/>
-      <c r="L81" s="98"/>
-      <c r="M81" s="98"/>
-      <c r="N81" s="98"/>
-      <c r="O81" s="39"/>
-      <c r="P81" s="96"/>
-      <c r="Q81" s="97"/>
-      <c r="R81" s="100"/>
-      <c r="S81" s="39"/>
+      <c r="H81" s="89"/>
+      <c r="I81" s="90"/>
+      <c r="J81" s="93"/>
+      <c r="K81" s="91"/>
+      <c r="L81" s="91"/>
+      <c r="M81" s="91"/>
+      <c r="N81" s="91"/>
+      <c r="O81" s="35"/>
+      <c r="P81" s="89"/>
+      <c r="Q81" s="90"/>
+      <c r="R81" s="93"/>
+      <c r="S81" s="35"/>
     </row>
     <row r="82" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H82" s="96"/>
-      <c r="I82" s="90"/>
-      <c r="J82" s="100"/>
-      <c r="K82" s="98"/>
-      <c r="L82" s="98"/>
-      <c r="M82" s="98"/>
-      <c r="N82" s="98"/>
-      <c r="O82" s="39"/>
-      <c r="P82" s="96"/>
-      <c r="Q82" s="97"/>
-      <c r="R82" s="100"/>
-      <c r="S82" s="39"/>
+      <c r="H82" s="89"/>
+      <c r="I82" s="83"/>
+      <c r="J82" s="93"/>
+      <c r="K82" s="91"/>
+      <c r="L82" s="91"/>
+      <c r="M82" s="91"/>
+      <c r="N82" s="91"/>
+      <c r="O82" s="35"/>
+      <c r="P82" s="89"/>
+      <c r="Q82" s="90"/>
+      <c r="R82" s="93"/>
+      <c r="S82" s="35"/>
     </row>
     <row r="83" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H83" s="101"/>
-      <c r="I83" s="88"/>
-      <c r="J83" s="100"/>
-      <c r="K83" s="100"/>
-      <c r="L83" s="100"/>
-      <c r="M83" s="100"/>
-      <c r="N83" s="100"/>
-      <c r="O83" s="39"/>
-      <c r="P83" s="96"/>
-      <c r="Q83" s="91"/>
-      <c r="R83" s="100"/>
-      <c r="S83" s="39"/>
+      <c r="H83" s="94"/>
+      <c r="I83" s="81"/>
+      <c r="J83" s="93"/>
+      <c r="K83" s="93"/>
+      <c r="L83" s="93"/>
+      <c r="M83" s="93"/>
+      <c r="N83" s="93"/>
+      <c r="O83" s="35"/>
+      <c r="P83" s="89"/>
+      <c r="Q83" s="84"/>
+      <c r="R83" s="93"/>
+      <c r="S83" s="35"/>
     </row>
     <row r="84" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H84" s="96"/>
-      <c r="I84" s="97"/>
-      <c r="J84" s="100"/>
-      <c r="K84" s="98"/>
-      <c r="L84" s="98"/>
-      <c r="M84" s="98"/>
-      <c r="N84" s="98"/>
-      <c r="O84" s="39"/>
-      <c r="P84" s="101"/>
-      <c r="Q84" s="89"/>
-      <c r="R84" s="100"/>
-      <c r="S84" s="100"/>
+      <c r="H84" s="89"/>
+      <c r="I84" s="90"/>
+      <c r="J84" s="93"/>
+      <c r="K84" s="91"/>
+      <c r="L84" s="91"/>
+      <c r="M84" s="91"/>
+      <c r="N84" s="91"/>
+      <c r="O84" s="35"/>
+      <c r="P84" s="94"/>
+      <c r="Q84" s="82"/>
+      <c r="R84" s="93"/>
+      <c r="S84" s="93"/>
     </row>
     <row r="85" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H85" s="96"/>
-      <c r="I85" s="97"/>
-      <c r="J85" s="100"/>
-      <c r="K85" s="98"/>
-      <c r="L85" s="98"/>
-      <c r="M85" s="98"/>
-      <c r="N85" s="98"/>
-      <c r="O85" s="39"/>
-      <c r="P85" s="96"/>
-      <c r="Q85" s="97"/>
-      <c r="R85" s="100"/>
-      <c r="S85" s="39"/>
+      <c r="H85" s="89"/>
+      <c r="I85" s="90"/>
+      <c r="J85" s="93"/>
+      <c r="K85" s="91"/>
+      <c r="L85" s="91"/>
+      <c r="M85" s="91"/>
+      <c r="N85" s="91"/>
+      <c r="O85" s="35"/>
+      <c r="P85" s="89"/>
+      <c r="Q85" s="90"/>
+      <c r="R85" s="93"/>
+      <c r="S85" s="35"/>
     </row>
     <row r="86" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H86" s="96"/>
-      <c r="I86" s="88"/>
-      <c r="J86" s="98"/>
-      <c r="K86" s="98"/>
-      <c r="L86" s="98"/>
-      <c r="M86" s="98"/>
-      <c r="N86" s="98"/>
-      <c r="O86" s="39"/>
-      <c r="P86" s="96"/>
-      <c r="Q86" s="97"/>
-      <c r="R86" s="100"/>
-      <c r="S86" s="39"/>
+      <c r="H86" s="89"/>
+      <c r="I86" s="81"/>
+      <c r="J86" s="91"/>
+      <c r="K86" s="91"/>
+      <c r="L86" s="91"/>
+      <c r="M86" s="91"/>
+      <c r="N86" s="91"/>
+      <c r="O86" s="35"/>
+      <c r="P86" s="89"/>
+      <c r="Q86" s="90"/>
+      <c r="R86" s="93"/>
+      <c r="S86" s="35"/>
     </row>
     <row r="87" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H87" s="101"/>
-      <c r="I87" s="88"/>
-      <c r="J87" s="100"/>
-      <c r="K87" s="100"/>
-      <c r="L87" s="100"/>
-      <c r="M87" s="100"/>
-      <c r="N87" s="100"/>
-      <c r="O87" s="39"/>
-      <c r="P87" s="96"/>
-      <c r="Q87" s="89"/>
-      <c r="R87" s="98"/>
-      <c r="S87" s="39"/>
+      <c r="H87" s="94"/>
+      <c r="I87" s="81"/>
+      <c r="J87" s="93"/>
+      <c r="K87" s="93"/>
+      <c r="L87" s="93"/>
+      <c r="M87" s="93"/>
+      <c r="N87" s="93"/>
+      <c r="O87" s="35"/>
+      <c r="P87" s="89"/>
+      <c r="Q87" s="82"/>
+      <c r="R87" s="91"/>
+      <c r="S87" s="35"/>
     </row>
     <row r="88" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H88" s="96"/>
-      <c r="I88" s="97"/>
-      <c r="J88" s="98"/>
-      <c r="K88" s="98"/>
-      <c r="L88" s="98"/>
-      <c r="M88" s="98"/>
-      <c r="N88" s="98"/>
-      <c r="O88" s="39"/>
-      <c r="P88" s="101"/>
-      <c r="Q88" s="89"/>
-      <c r="R88" s="100"/>
-      <c r="S88" s="100"/>
+      <c r="H88" s="89"/>
+      <c r="I88" s="90"/>
+      <c r="J88" s="91"/>
+      <c r="K88" s="91"/>
+      <c r="L88" s="91"/>
+      <c r="M88" s="91"/>
+      <c r="N88" s="91"/>
+      <c r="O88" s="35"/>
+      <c r="P88" s="94"/>
+      <c r="Q88" s="82"/>
+      <c r="R88" s="93"/>
+      <c r="S88" s="93"/>
     </row>
     <row r="89" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H89" s="96"/>
-      <c r="I89" s="88"/>
-      <c r="J89" s="98"/>
-      <c r="K89" s="98"/>
-      <c r="L89" s="98"/>
-      <c r="M89" s="98"/>
-      <c r="N89" s="98"/>
-      <c r="O89" s="39"/>
-      <c r="P89" s="96"/>
-      <c r="Q89" s="97"/>
-      <c r="R89" s="100"/>
-      <c r="S89" s="39"/>
+      <c r="H89" s="89"/>
+      <c r="I89" s="81"/>
+      <c r="J89" s="91"/>
+      <c r="K89" s="91"/>
+      <c r="L89" s="91"/>
+      <c r="M89" s="91"/>
+      <c r="N89" s="91"/>
+      <c r="O89" s="35"/>
+      <c r="P89" s="89"/>
+      <c r="Q89" s="90"/>
+      <c r="R89" s="93"/>
+      <c r="S89" s="35"/>
     </row>
     <row r="90" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H90" s="102"/>
-      <c r="I90" s="88"/>
-      <c r="J90" s="100"/>
-      <c r="K90" s="100"/>
-      <c r="L90" s="100"/>
-      <c r="M90" s="100"/>
-      <c r="N90" s="100"/>
-      <c r="O90" s="39"/>
-      <c r="P90" s="96"/>
-      <c r="Q90" s="89"/>
-      <c r="R90" s="98"/>
-      <c r="S90" s="39"/>
+      <c r="H90" s="95"/>
+      <c r="I90" s="81"/>
+      <c r="J90" s="93"/>
+      <c r="K90" s="93"/>
+      <c r="L90" s="93"/>
+      <c r="M90" s="93"/>
+      <c r="N90" s="93"/>
+      <c r="O90" s="35"/>
+      <c r="P90" s="89"/>
+      <c r="Q90" s="82"/>
+      <c r="R90" s="91"/>
+      <c r="S90" s="35"/>
     </row>
     <row r="91" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H91" s="96"/>
-      <c r="I91" s="97"/>
-      <c r="J91" s="100"/>
-      <c r="K91" s="98"/>
-      <c r="L91" s="98"/>
-      <c r="M91" s="98"/>
-      <c r="N91" s="98"/>
-      <c r="O91" s="39"/>
-      <c r="P91" s="102"/>
-      <c r="Q91" s="89"/>
-      <c r="R91" s="100"/>
-      <c r="S91" s="100"/>
+      <c r="H91" s="89"/>
+      <c r="I91" s="90"/>
+      <c r="J91" s="93"/>
+      <c r="K91" s="91"/>
+      <c r="L91" s="91"/>
+      <c r="M91" s="91"/>
+      <c r="N91" s="91"/>
+      <c r="O91" s="35"/>
+      <c r="P91" s="95"/>
+      <c r="Q91" s="82"/>
+      <c r="R91" s="93"/>
+      <c r="S91" s="93"/>
     </row>
     <row r="92" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H92" s="103"/>
-      <c r="I92" s="97"/>
-      <c r="J92" s="98"/>
-      <c r="K92" s="98"/>
-      <c r="L92" s="98"/>
-      <c r="M92" s="98"/>
-      <c r="N92" s="98"/>
-      <c r="O92" s="39"/>
-      <c r="P92" s="96"/>
-      <c r="Q92" s="97"/>
-      <c r="R92" s="100"/>
-      <c r="S92" s="39"/>
+      <c r="H92" s="96"/>
+      <c r="I92" s="90"/>
+      <c r="J92" s="91"/>
+      <c r="K92" s="91"/>
+      <c r="L92" s="91"/>
+      <c r="M92" s="91"/>
+      <c r="N92" s="91"/>
+      <c r="O92" s="35"/>
+      <c r="P92" s="89"/>
+      <c r="Q92" s="90"/>
+      <c r="R92" s="93"/>
+      <c r="S92" s="35"/>
     </row>
     <row r="93" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H93" s="96"/>
-      <c r="I93" s="88"/>
-      <c r="J93" s="98"/>
-      <c r="K93" s="98"/>
-      <c r="L93" s="98"/>
-      <c r="M93" s="98"/>
-      <c r="N93" s="98"/>
-      <c r="O93" s="39"/>
-      <c r="P93" s="103"/>
-      <c r="Q93" s="97"/>
-      <c r="R93" s="100"/>
-      <c r="S93" s="39"/>
+      <c r="H93" s="89"/>
+      <c r="I93" s="81"/>
+      <c r="J93" s="91"/>
+      <c r="K93" s="91"/>
+      <c r="L93" s="91"/>
+      <c r="M93" s="91"/>
+      <c r="N93" s="91"/>
+      <c r="O93" s="35"/>
+      <c r="P93" s="96"/>
+      <c r="Q93" s="90"/>
+      <c r="R93" s="93"/>
+      <c r="S93" s="35"/>
     </row>
     <row r="94" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H94" s="102"/>
-      <c r="I94" s="88"/>
-      <c r="J94" s="100"/>
-      <c r="K94" s="100"/>
-      <c r="L94" s="100"/>
-      <c r="M94" s="100"/>
-      <c r="N94" s="100"/>
-      <c r="O94" s="39"/>
-      <c r="P94" s="96"/>
-      <c r="Q94" s="89"/>
-      <c r="R94" s="100"/>
-      <c r="S94" s="39"/>
+      <c r="H94" s="95"/>
+      <c r="I94" s="81"/>
+      <c r="J94" s="93"/>
+      <c r="K94" s="93"/>
+      <c r="L94" s="93"/>
+      <c r="M94" s="93"/>
+      <c r="N94" s="93"/>
+      <c r="O94" s="35"/>
+      <c r="P94" s="89"/>
+      <c r="Q94" s="82"/>
+      <c r="R94" s="93"/>
+      <c r="S94" s="35"/>
     </row>
     <row r="95" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H95" s="104"/>
-      <c r="I95" s="97"/>
-      <c r="J95" s="100"/>
-      <c r="K95" s="98"/>
-      <c r="L95" s="98"/>
-      <c r="M95" s="98"/>
-      <c r="N95" s="98"/>
-      <c r="O95" s="39"/>
-      <c r="P95" s="102"/>
-      <c r="Q95" s="89"/>
-      <c r="R95" s="100"/>
-      <c r="S95" s="100"/>
+      <c r="H95" s="97"/>
+      <c r="I95" s="90"/>
+      <c r="J95" s="93"/>
+      <c r="K95" s="91"/>
+      <c r="L95" s="91"/>
+      <c r="M95" s="91"/>
+      <c r="N95" s="91"/>
+      <c r="O95" s="35"/>
+      <c r="P95" s="95"/>
+      <c r="Q95" s="82"/>
+      <c r="R95" s="93"/>
+      <c r="S95" s="93"/>
     </row>
     <row r="96" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H96" s="104"/>
-      <c r="I96" s="97"/>
-      <c r="J96" s="98"/>
-      <c r="K96" s="98"/>
-      <c r="L96" s="98"/>
-      <c r="M96" s="98"/>
-      <c r="N96" s="98"/>
-      <c r="O96" s="39"/>
-      <c r="P96" s="104"/>
-      <c r="Q96" s="97"/>
-      <c r="R96" s="100"/>
-      <c r="S96" s="39"/>
+      <c r="H96" s="97"/>
+      <c r="I96" s="90"/>
+      <c r="J96" s="91"/>
+      <c r="K96" s="91"/>
+      <c r="L96" s="91"/>
+      <c r="M96" s="91"/>
+      <c r="N96" s="91"/>
+      <c r="O96" s="35"/>
+      <c r="P96" s="97"/>
+      <c r="Q96" s="90"/>
+      <c r="R96" s="93"/>
+      <c r="S96" s="35"/>
     </row>
     <row r="97" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H97" s="104"/>
-      <c r="I97" s="88"/>
-      <c r="J97" s="98"/>
-      <c r="K97" s="98"/>
-      <c r="L97" s="98"/>
-      <c r="M97" s="98"/>
-      <c r="N97" s="98"/>
-      <c r="O97" s="39"/>
-      <c r="P97" s="104"/>
-      <c r="Q97" s="97"/>
-      <c r="R97" s="100"/>
-      <c r="S97" s="39"/>
+      <c r="H97" s="97"/>
+      <c r="I97" s="81"/>
+      <c r="J97" s="91"/>
+      <c r="K97" s="91"/>
+      <c r="L97" s="91"/>
+      <c r="M97" s="91"/>
+      <c r="N97" s="91"/>
+      <c r="O97" s="35"/>
+      <c r="P97" s="97"/>
+      <c r="Q97" s="90"/>
+      <c r="R97" s="93"/>
+      <c r="S97" s="35"/>
     </row>
     <row r="98" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H98" s="39"/>
-      <c r="I98" s="97"/>
-      <c r="J98" s="39"/>
-      <c r="K98" s="39"/>
-      <c r="L98" s="39"/>
-      <c r="M98" s="39"/>
-      <c r="N98" s="39"/>
-      <c r="O98" s="39"/>
-      <c r="P98" s="104"/>
-      <c r="Q98" s="88"/>
-      <c r="R98" s="100"/>
-      <c r="S98" s="39"/>
+      <c r="H98" s="35"/>
+      <c r="I98" s="90"/>
+      <c r="J98" s="35"/>
+      <c r="K98" s="35"/>
+      <c r="L98" s="35"/>
+      <c r="M98" s="35"/>
+      <c r="N98" s="35"/>
+      <c r="O98" s="35"/>
+      <c r="P98" s="97"/>
+      <c r="Q98" s="81"/>
+      <c r="R98" s="93"/>
+      <c r="S98" s="35"/>
     </row>
     <row r="99" spans="8:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H99" s="39"/>
-      <c r="I99" s="39"/>
-      <c r="J99" s="39"/>
-      <c r="K99" s="39"/>
-      <c r="L99" s="39"/>
-      <c r="M99" s="39"/>
-      <c r="N99" s="39"/>
-      <c r="O99" s="39"/>
-      <c r="P99" s="39"/>
-      <c r="Q99" s="97"/>
-      <c r="R99" s="39"/>
-      <c r="S99" s="39"/>
+      <c r="H99" s="35"/>
+      <c r="I99" s="35"/>
+      <c r="J99" s="35"/>
+      <c r="K99" s="35"/>
+      <c r="L99" s="35"/>
+      <c r="M99" s="35"/>
+      <c r="N99" s="35"/>
+      <c r="O99" s="35"/>
+      <c r="P99" s="35"/>
+      <c r="Q99" s="90"/>
+      <c r="R99" s="35"/>
+      <c r="S99" s="35"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1" gridLines="1"/>
@@ -4501,7 +4478,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.77734375" customWidth="1"/>
@@ -4540,8 +4517,8 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -4556,8 +4533,8 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
     </row>
     <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -4572,12 +4549,12 @@
       <c r="D3" s="22">
         <v>72</v>
       </c>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29">
+      <c r="E3" s="27"/>
+      <c r="F3" s="27">
         <v>19</v>
       </c>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29">
+      <c r="G3" s="27"/>
+      <c r="H3" s="27">
         <v>12</v>
       </c>
       <c r="I3" s="11">
@@ -4588,8 +4565,8 @@
         <f t="shared" ref="J3:J42" si="0">I3*C3</f>
         <v>738000</v>
       </c>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -4602,14 +4579,14 @@
       <c r="D4" s="22">
         <v>240</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="27">
         <v>72</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="27">
         <v>17</v>
       </c>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29">
+      <c r="G4" s="27"/>
+      <c r="H4" s="27">
         <v>46</v>
       </c>
       <c r="I4" s="11">
@@ -4620,8 +4597,8 @@
         <f t="shared" si="0"/>
         <v>3984000</v>
       </c>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
     </row>
     <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
@@ -4635,16 +4612,16 @@
         <f>440+80</f>
         <v>520</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="27">
         <v>140</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="27">
         <v>21</v>
       </c>
-      <c r="G5" s="29">
+      <c r="G5" s="27">
         <v>2</v>
       </c>
-      <c r="H5" s="29">
+      <c r="H5" s="27">
         <v>85</v>
       </c>
       <c r="I5" s="11">
@@ -4655,8 +4632,8 @@
         <f t="shared" si="0"/>
         <v>6624000</v>
       </c>
-      <c r="L5" s="41"/>
-      <c r="M5" s="41"/>
+      <c r="L5" s="37"/>
+      <c r="M5" s="37"/>
     </row>
     <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
@@ -4669,12 +4646,12 @@
       <c r="D6" s="22">
         <v>24</v>
       </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29">
+      <c r="E6" s="27"/>
+      <c r="F6" s="27">
         <v>1</v>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29">
+      <c r="G6" s="27"/>
+      <c r="H6" s="27">
         <v>13</v>
       </c>
       <c r="I6" s="11">
@@ -4685,8 +4662,8 @@
         <f t="shared" si="0"/>
         <v>120000</v>
       </c>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
+      <c r="L6" s="37"/>
+      <c r="M6" s="37"/>
     </row>
     <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
@@ -4699,10 +4676,10 @@
       <c r="D7" s="22">
         <v>24</v>
       </c>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29">
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27">
         <v>19</v>
       </c>
       <c r="I7" s="11">
@@ -4713,8 +4690,8 @@
         <f t="shared" si="0"/>
         <v>60000</v>
       </c>
-      <c r="L7" s="41"/>
-      <c r="M7" s="41"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="37"/>
     </row>
     <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
@@ -4727,10 +4704,10 @@
       <c r="D8" s="22">
         <v>24</v>
       </c>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29">
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27">
         <v>13</v>
       </c>
       <c r="I8" s="11">
@@ -4741,8 +4718,8 @@
         <f t="shared" si="0"/>
         <v>132000</v>
       </c>
-      <c r="L8" s="41"/>
-      <c r="M8" s="41"/>
+      <c r="L8" s="37"/>
+      <c r="M8" s="37"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
@@ -4755,10 +4732,10 @@
       <c r="D9" s="22">
         <v>12</v>
       </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29">
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27">
         <v>5</v>
       </c>
       <c r="I9" s="11">
@@ -4769,8 +4746,8 @@
         <f t="shared" si="0"/>
         <v>84000</v>
       </c>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="37"/>
     </row>
     <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
@@ -4783,10 +4760,10 @@
       <c r="D10" s="22">
         <v>0</v>
       </c>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
       <c r="I10" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4795,8 +4772,8 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L10" s="41"/>
-      <c r="M10" s="41"/>
+      <c r="L10" s="37"/>
+      <c r="M10" s="37"/>
     </row>
     <row r="11" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
@@ -4809,12 +4786,12 @@
       <c r="D11" s="22">
         <v>48</v>
       </c>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28">
+      <c r="E11" s="26"/>
+      <c r="F11" s="26">
         <v>5</v>
       </c>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32">
+      <c r="G11" s="30"/>
+      <c r="H11" s="30">
         <v>22</v>
       </c>
       <c r="I11" s="11">
@@ -4825,8 +4802,8 @@
         <f t="shared" si="0"/>
         <v>525000</v>
       </c>
-      <c r="L11" s="41"/>
-      <c r="M11" s="41"/>
+      <c r="L11" s="37"/>
+      <c r="M11" s="37"/>
     </row>
     <row r="12" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
@@ -4835,14 +4812,14 @@
       <c r="B12" s="16"/>
       <c r="C12" s="17"/>
       <c r="D12" s="23"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
       <c r="I12" s="18"/>
       <c r="J12" s="18"/>
-      <c r="L12" s="41"/>
-      <c r="M12" s="41"/>
+      <c r="L12" s="37"/>
+      <c r="M12" s="37"/>
     </row>
     <row r="13" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
@@ -4855,12 +4832,12 @@
       <c r="D13" s="22">
         <v>240</v>
       </c>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29">
+      <c r="E13" s="27"/>
+      <c r="F13" s="27">
         <v>19</v>
       </c>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29">
+      <c r="G13" s="27"/>
+      <c r="H13" s="27">
         <v>109</v>
       </c>
       <c r="I13" s="11">
@@ -4871,8 +4848,8 @@
         <f t="shared" si="0"/>
         <v>1456000</v>
       </c>
-      <c r="L13" s="41"/>
-      <c r="M13" s="41"/>
+      <c r="L13" s="37"/>
+      <c r="M13" s="37"/>
     </row>
     <row r="14" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
@@ -4885,12 +4862,12 @@
       <c r="D14" s="22">
         <v>96</v>
       </c>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28">
+      <c r="E14" s="26"/>
+      <c r="F14" s="26">
         <v>1</v>
       </c>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32">
+      <c r="G14" s="30"/>
+      <c r="H14" s="30">
         <v>18</v>
       </c>
       <c r="I14" s="11">
@@ -4901,8 +4878,8 @@
         <f t="shared" si="0"/>
         <v>1232000</v>
       </c>
-      <c r="L14" s="41"/>
-      <c r="M14" s="41"/>
+      <c r="L14" s="37"/>
+      <c r="M14" s="37"/>
     </row>
     <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
@@ -4911,14 +4888,14 @@
       <c r="B15" s="16"/>
       <c r="C15" s="17"/>
       <c r="D15" s="23"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
       <c r="I15" s="18"/>
       <c r="J15" s="18"/>
-      <c r="L15" s="41"/>
-      <c r="M15" s="41"/>
+      <c r="L15" s="37"/>
+      <c r="M15" s="37"/>
     </row>
     <row r="16" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
@@ -4931,10 +4908,10 @@
       <c r="D16" s="22">
         <v>24</v>
       </c>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32">
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30">
         <v>15</v>
       </c>
       <c r="I16" s="11">
@@ -4945,8 +4922,8 @@
         <f t="shared" si="0"/>
         <v>225000</v>
       </c>
-      <c r="L16" s="41"/>
-      <c r="M16" s="41"/>
+      <c r="L16" s="37"/>
+      <c r="M16" s="37"/>
     </row>
     <row r="17" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
@@ -4955,14 +4932,14 @@
       <c r="B17" s="16"/>
       <c r="C17" s="17"/>
       <c r="D17" s="23"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
       <c r="I17" s="18"/>
       <c r="J17" s="18"/>
-      <c r="L17" s="41"/>
-      <c r="M17" s="41"/>
+      <c r="L17" s="37"/>
+      <c r="M17" s="37"/>
     </row>
     <row r="18" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
@@ -4975,10 +4952,10 @@
       <c r="D18" s="22">
         <v>4</v>
       </c>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29">
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27">
         <v>4</v>
       </c>
       <c r="I18" s="11">
@@ -4989,8 +4966,8 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L18" s="41"/>
-      <c r="M18" s="41"/>
+      <c r="L18" s="37"/>
+      <c r="M18" s="37"/>
     </row>
     <row r="19" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
@@ -5003,10 +4980,10 @@
       <c r="D19" s="22">
         <v>8</v>
       </c>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29">
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27">
         <v>7</v>
       </c>
       <c r="I19" s="11">
@@ -5017,8 +4994,8 @@
         <f t="shared" si="0"/>
         <v>360000</v>
       </c>
-      <c r="L19" s="41"/>
-      <c r="M19" s="41"/>
+      <c r="L19" s="37"/>
+      <c r="M19" s="37"/>
     </row>
     <row r="20" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
@@ -5028,13 +5005,13 @@
       <c r="C20" s="14">
         <v>260000</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="28">
         <v>4</v>
       </c>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32">
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30">
         <v>3</v>
       </c>
       <c r="I20" s="11">
@@ -5045,8 +5022,8 @@
         <f t="shared" si="0"/>
         <v>260000</v>
       </c>
-      <c r="L20" s="41"/>
-      <c r="M20" s="41"/>
+      <c r="L20" s="37"/>
+      <c r="M20" s="37"/>
     </row>
     <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
@@ -5055,14 +5032,14 @@
       <c r="B21" s="16"/>
       <c r="C21" s="17"/>
       <c r="D21" s="23"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
       <c r="I21" s="18"/>
       <c r="J21" s="18"/>
-      <c r="L21" s="41"/>
-      <c r="M21" s="41"/>
+      <c r="L21" s="37"/>
+      <c r="M21" s="37"/>
     </row>
     <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
@@ -5073,10 +5050,10 @@
         <v>260000</v>
       </c>
       <c r="D22" s="22"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
       <c r="I22" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -5085,8 +5062,8 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L22" s="41"/>
-      <c r="M22" s="41"/>
+      <c r="L22" s="37"/>
+      <c r="M22" s="37"/>
     </row>
     <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
@@ -5099,10 +5076,10 @@
       <c r="D23" s="22">
         <v>4</v>
       </c>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32">
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30">
         <v>4</v>
       </c>
       <c r="I23" s="11">
@@ -5113,8 +5090,8 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L23" s="48"/>
-      <c r="M23" s="48"/>
+      <c r="L23" s="44"/>
+      <c r="M23" s="44"/>
     </row>
     <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
@@ -5123,14 +5100,14 @@
       <c r="B24" s="16"/>
       <c r="C24" s="17"/>
       <c r="D24" s="23"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
       <c r="I24" s="18"/>
       <c r="J24" s="18"/>
-      <c r="L24" s="41"/>
-      <c r="M24" s="41"/>
+      <c r="L24" s="37"/>
+      <c r="M24" s="37"/>
     </row>
     <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
@@ -5143,10 +5120,10 @@
       <c r="D25" s="22">
         <v>2</v>
       </c>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29">
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27">
         <v>2</v>
       </c>
       <c r="I25" s="11">
@@ -5157,8 +5134,8 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L25" s="41"/>
-      <c r="M25" s="41"/>
+      <c r="L25" s="37"/>
+      <c r="M25" s="37"/>
     </row>
     <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
@@ -5171,10 +5148,10 @@
       <c r="D26" s="22">
         <v>2</v>
       </c>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29">
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27">
         <v>2</v>
       </c>
       <c r="I26" s="11">
@@ -5185,8 +5162,8 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L26" s="48"/>
-      <c r="M26" s="48"/>
+      <c r="L26" s="44"/>
+      <c r="M26" s="44"/>
     </row>
     <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
@@ -5199,10 +5176,10 @@
       <c r="D27" s="22">
         <v>5</v>
       </c>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34">
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32">
         <v>5</v>
       </c>
       <c r="I27" s="11">
@@ -5213,8 +5190,8 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L27" s="41"/>
-      <c r="M27" s="41"/>
+      <c r="L27" s="37"/>
+      <c r="M27" s="37"/>
     </row>
     <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
@@ -5223,14 +5200,14 @@
       <c r="B28" s="16"/>
       <c r="C28" s="17"/>
       <c r="D28" s="23"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
       <c r="I28" s="18"/>
       <c r="J28" s="18"/>
-      <c r="L28" s="41"/>
-      <c r="M28" s="41"/>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
     </row>
     <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
@@ -5243,10 +5220,10 @@
       <c r="D29" s="22">
         <v>4</v>
       </c>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29">
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27">
         <v>4</v>
       </c>
       <c r="I29" s="11">
@@ -5257,8 +5234,8 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L29" s="48"/>
-      <c r="M29" s="48"/>
+      <c r="L29" s="44"/>
+      <c r="M29" s="44"/>
     </row>
     <row r="30" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
@@ -5271,10 +5248,10 @@
       <c r="D30" s="22">
         <v>5</v>
       </c>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29">
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27">
         <v>4</v>
       </c>
       <c r="I30" s="11">
@@ -5285,8 +5262,8 @@
         <f t="shared" si="0"/>
         <v>160000</v>
       </c>
-      <c r="L30" s="41"/>
-      <c r="M30" s="41"/>
+      <c r="L30" s="37"/>
+      <c r="M30" s="37"/>
     </row>
     <row r="31" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
@@ -5299,10 +5276,10 @@
       <c r="D31" s="22">
         <v>15</v>
       </c>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32">
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30">
         <v>12</v>
       </c>
       <c r="I31" s="11">
@@ -5313,8 +5290,8 @@
         <f t="shared" si="0"/>
         <v>480000</v>
       </c>
-      <c r="L31" s="41"/>
-      <c r="M31" s="41"/>
+      <c r="L31" s="37"/>
+      <c r="M31" s="37"/>
     </row>
     <row r="32" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
@@ -5323,14 +5300,14 @@
       <c r="B32" s="16"/>
       <c r="C32" s="17"/>
       <c r="D32" s="23"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
       <c r="I32" s="18"/>
       <c r="J32" s="18"/>
-      <c r="L32" s="41"/>
-      <c r="M32" s="41"/>
+      <c r="L32" s="37"/>
+      <c r="M32" s="37"/>
     </row>
     <row r="33" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
@@ -5343,10 +5320,10 @@
       <c r="D33" s="22">
         <v>1</v>
       </c>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29">
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27">
         <v>0</v>
       </c>
       <c r="I33" s="11">
@@ -5357,8 +5334,8 @@
         <f t="shared" si="0"/>
         <v>360000</v>
       </c>
-      <c r="L33" s="48"/>
-      <c r="M33" s="48"/>
+      <c r="L33" s="44"/>
+      <c r="M33" s="44"/>
     </row>
     <row r="34" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
@@ -5371,10 +5348,10 @@
       <c r="D34" s="22">
         <v>5</v>
       </c>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32">
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30">
         <v>4</v>
       </c>
       <c r="I34" s="11">
@@ -5385,8 +5362,8 @@
         <f t="shared" si="0"/>
         <v>260000</v>
       </c>
-      <c r="L34" s="41"/>
-      <c r="M34" s="41"/>
+      <c r="L34" s="37"/>
+      <c r="M34" s="37"/>
     </row>
     <row r="35" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
@@ -5395,14 +5372,14 @@
       <c r="B35" s="16"/>
       <c r="C35" s="17"/>
       <c r="D35" s="24"/>
-      <c r="E35" s="35"/>
-      <c r="F35" s="35"/>
-      <c r="G35" s="33"/>
-      <c r="H35" s="33"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="33"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31"/>
       <c r="I35" s="18"/>
       <c r="J35" s="18"/>
-      <c r="L35" s="41"/>
-      <c r="M35" s="41"/>
+      <c r="L35" s="37"/>
+      <c r="M35" s="37"/>
     </row>
     <row r="36" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
@@ -5415,10 +5392,10 @@
       <c r="D36" s="22">
         <v>8</v>
       </c>
-      <c r="E36" s="29"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="29"/>
-      <c r="H36" s="29">
+      <c r="E36" s="27"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27">
         <v>7</v>
       </c>
       <c r="I36" s="11">
@@ -5429,8 +5406,8 @@
         <f t="shared" si="0"/>
         <v>180000</v>
       </c>
-      <c r="L36" s="41"/>
-      <c r="M36" s="41"/>
+      <c r="L36" s="37"/>
+      <c r="M36" s="37"/>
     </row>
     <row r="37" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
@@ -5443,10 +5420,10 @@
       <c r="D37" s="22">
         <v>12</v>
       </c>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32">
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30">
         <v>10</v>
       </c>
       <c r="I37" s="11">
@@ -5457,8 +5434,8 @@
         <f t="shared" si="0"/>
         <v>320000</v>
       </c>
-      <c r="L37" s="41"/>
-      <c r="M37" s="41"/>
+      <c r="L37" s="37"/>
+      <c r="M37" s="37"/>
     </row>
     <row r="38" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
@@ -5467,14 +5444,14 @@
       <c r="B38" s="16"/>
       <c r="C38" s="17"/>
       <c r="D38" s="24"/>
-      <c r="E38" s="35"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="33"/>
-      <c r="H38" s="33"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
       <c r="I38" s="18"/>
       <c r="J38" s="18"/>
-      <c r="L38" s="41"/>
-      <c r="M38" s="41"/>
+      <c r="L38" s="37"/>
+      <c r="M38" s="37"/>
     </row>
     <row r="39" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
@@ -5487,10 +5464,10 @@
       <c r="D39" s="22">
         <v>18</v>
       </c>
-      <c r="E39" s="29"/>
-      <c r="F39" s="29"/>
-      <c r="G39" s="29"/>
-      <c r="H39" s="29">
+      <c r="E39" s="27"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="27">
         <v>0</v>
       </c>
       <c r="I39" s="11">
@@ -5501,8 +5478,8 @@
         <f t="shared" si="0"/>
         <v>90000</v>
       </c>
-      <c r="L39" s="41"/>
-      <c r="M39" s="41"/>
+      <c r="L39" s="37"/>
+      <c r="M39" s="37"/>
     </row>
     <row r="40" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
@@ -5515,12 +5492,12 @@
       <c r="D40" s="22">
         <v>48</v>
       </c>
-      <c r="E40" s="29">
+      <c r="E40" s="27">
         <v>72</v>
       </c>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29">
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27">
         <v>23</v>
       </c>
       <c r="I40" s="11">
@@ -5531,8 +5508,8 @@
         <f t="shared" si="0"/>
         <v>194000</v>
       </c>
-      <c r="L40" s="49"/>
-      <c r="M40" s="49"/>
+      <c r="L40" s="45"/>
+      <c r="M40" s="45"/>
     </row>
     <row r="41" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
@@ -5545,12 +5522,12 @@
       <c r="D41" s="22">
         <v>20</v>
       </c>
-      <c r="E41" s="32">
+      <c r="E41" s="30">
         <v>20</v>
       </c>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32">
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="30">
         <v>10</v>
       </c>
       <c r="I41" s="11">
@@ -5561,8 +5538,8 @@
         <f t="shared" si="0"/>
         <v>450000</v>
       </c>
-      <c r="L41" s="41"/>
-      <c r="M41" s="41"/>
+      <c r="L41" s="37"/>
+      <c r="M41" s="37"/>
     </row>
     <row r="42" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
@@ -5575,12 +5552,12 @@
       <c r="D42" s="22">
         <v>6</v>
       </c>
-      <c r="E42" s="29">
+      <c r="E42" s="27">
         <v>6</v>
       </c>
-      <c r="F42" s="29"/>
-      <c r="G42" s="29"/>
-      <c r="H42" s="29">
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27">
         <v>4</v>
       </c>
       <c r="I42" s="11">
@@ -5591,8 +5568,8 @@
         <f t="shared" si="0"/>
         <v>2080000</v>
       </c>
-      <c r="L42" s="41"/>
-      <c r="M42" s="41"/>
+      <c r="L42" s="37"/>
+      <c r="M42" s="37"/>
     </row>
     <row r="43" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
@@ -5610,37 +5587,19 @@
         <f>SUM(J3:J42)</f>
         <v>20374000</v>
       </c>
-      <c r="L43" s="48"/>
-      <c r="M43" s="48"/>
+      <c r="L43" s="44"/>
+      <c r="M43" s="44"/>
     </row>
     <row r="44" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L44" s="41"/>
-      <c r="M44" s="41"/>
+      <c r="L44" s="37"/>
+      <c r="M44" s="37"/>
     </row>
     <row r="45" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L45" s="41"/>
-      <c r="M45" s="41"/>
+      <c r="L45" s="37"/>
+      <c r="M45" s="37"/>
     </row>
     <row r="46" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L46" s="27"/>
-    </row>
-    <row r="47" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L47" s="25"/>
-    </row>
-    <row r="48" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L48" s="25"/>
-    </row>
-    <row r="49" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L49" s="26"/>
-    </row>
-    <row r="50" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L50" s="26"/>
-    </row>
-    <row r="51" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L51" s="26"/>
-    </row>
-    <row r="52" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L52" s="26"/>
+      <c r="L46" s="25"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1" gridLines="1"/>
@@ -5661,36 +5620,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="G2" s="36" t="s">
         <v>80</v>
       </c>
     </row>
@@ -5704,10 +5663,10 @@
       <c r="C3" s="21">
         <v>2</v>
       </c>
-      <c r="D3" s="51">
+      <c r="D3" s="47">
         <v>13000</v>
       </c>
-      <c r="E3" s="51">
+      <c r="E3" s="47">
         <v>26000</v>
       </c>
       <c r="F3" s="21" t="s">
@@ -5727,10 +5686,10 @@
       <c r="C4" s="21">
         <v>2</v>
       </c>
-      <c r="D4" s="51">
+      <c r="D4" s="47">
         <v>18000</v>
       </c>
-      <c r="E4" s="51">
+      <c r="E4" s="47">
         <v>36000</v>
       </c>
       <c r="F4" s="21" t="s">
@@ -5750,10 +5709,10 @@
       <c r="C5" s="21">
         <v>2</v>
       </c>
-      <c r="D5" s="51">
+      <c r="D5" s="47">
         <v>16000</v>
       </c>
-      <c r="E5" s="51">
+      <c r="E5" s="47">
         <v>32000</v>
       </c>
       <c r="F5" s="21" t="s">
@@ -5773,10 +5732,10 @@
       <c r="C6" s="21">
         <v>2</v>
       </c>
-      <c r="D6" s="51">
+      <c r="D6" s="47">
         <v>12000</v>
       </c>
-      <c r="E6" s="51">
+      <c r="E6" s="47">
         <v>24000</v>
       </c>
       <c r="F6" s="21" t="s">
@@ -5796,10 +5755,10 @@
       <c r="C7" s="21">
         <v>1</v>
       </c>
-      <c r="D7" s="51">
+      <c r="D7" s="47">
         <v>16000</v>
       </c>
-      <c r="E7" s="51">
+      <c r="E7" s="47">
         <v>16000</v>
       </c>
       <c r="F7" s="21" t="s">
@@ -5819,10 +5778,10 @@
       <c r="C8" s="21">
         <v>1</v>
       </c>
-      <c r="D8" s="51">
+      <c r="D8" s="47">
         <v>25000</v>
       </c>
-      <c r="E8" s="51">
+      <c r="E8" s="47">
         <v>25000</v>
       </c>
       <c r="F8" s="21" t="s">
@@ -5842,10 +5801,10 @@
       <c r="C9" s="21">
         <v>1</v>
       </c>
-      <c r="D9" s="51">
+      <c r="D9" s="47">
         <v>12000</v>
       </c>
-      <c r="E9" s="51">
+      <c r="E9" s="47">
         <v>12000</v>
       </c>
       <c r="F9" s="21" t="s">
@@ -5865,10 +5824,10 @@
       <c r="C10" s="21">
         <v>3</v>
       </c>
-      <c r="D10" s="51">
+      <c r="D10" s="47">
         <v>18000</v>
       </c>
-      <c r="E10" s="51">
+      <c r="E10" s="47">
         <v>54000</v>
       </c>
       <c r="F10" s="21" t="s">
@@ -5888,10 +5847,10 @@
       <c r="C11" s="21">
         <v>4</v>
       </c>
-      <c r="D11" s="51">
+      <c r="D11" s="47">
         <v>12000</v>
       </c>
-      <c r="E11" s="51">
+      <c r="E11" s="47">
         <v>48000</v>
       </c>
       <c r="F11" s="21" t="s">
@@ -5911,10 +5870,10 @@
       <c r="C12" s="21">
         <v>2</v>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="47">
         <v>18000</v>
       </c>
-      <c r="E12" s="51">
+      <c r="E12" s="47">
         <v>36000</v>
       </c>
       <c r="F12" s="21" t="s">
@@ -5934,10 +5893,10 @@
       <c r="C13" s="21">
         <v>1</v>
       </c>
-      <c r="D13" s="51">
+      <c r="D13" s="47">
         <v>25000</v>
       </c>
-      <c r="E13" s="51">
+      <c r="E13" s="47">
         <v>25000</v>
       </c>
       <c r="F13" s="21" t="s">
@@ -5957,10 +5916,10 @@
       <c r="C14" s="21">
         <v>7</v>
       </c>
-      <c r="D14" s="51">
+      <c r="D14" s="47">
         <v>16000</v>
       </c>
-      <c r="E14" s="51">
+      <c r="E14" s="47">
         <v>112000</v>
       </c>
       <c r="F14" s="21" t="s">
@@ -5980,10 +5939,10 @@
       <c r="C15" s="21">
         <v>9</v>
       </c>
-      <c r="D15" s="51">
+      <c r="D15" s="47">
         <v>18000</v>
       </c>
-      <c r="E15" s="51">
+      <c r="E15" s="47">
         <v>162000</v>
       </c>
       <c r="F15" s="21" t="s">
@@ -6003,10 +5962,10 @@
       <c r="C16" s="21">
         <v>3</v>
       </c>
-      <c r="D16" s="51">
+      <c r="D16" s="47">
         <v>12000</v>
       </c>
-      <c r="E16" s="51">
+      <c r="E16" s="47">
         <v>36000</v>
       </c>
       <c r="F16" s="21" t="s">
@@ -6026,10 +5985,10 @@
       <c r="C17" s="21">
         <v>14</v>
       </c>
-      <c r="D17" s="51">
+      <c r="D17" s="47">
         <v>13000</v>
       </c>
-      <c r="E17" s="51">
+      <c r="E17" s="47">
         <v>182000</v>
       </c>
       <c r="F17" s="21" t="s">
@@ -6049,10 +6008,10 @@
       <c r="C18" s="21">
         <v>2</v>
       </c>
-      <c r="D18" s="51">
+      <c r="D18" s="47">
         <v>16000</v>
       </c>
-      <c r="E18" s="51">
+      <c r="E18" s="47">
         <v>32000</v>
       </c>
       <c r="F18" s="21" t="s">
@@ -6072,10 +6031,10 @@
       <c r="C19" s="21">
         <v>1</v>
       </c>
-      <c r="D19" s="51">
+      <c r="D19" s="47">
         <v>18000</v>
       </c>
-      <c r="E19" s="51">
+      <c r="E19" s="47">
         <v>18000</v>
       </c>
       <c r="F19" s="21" t="s">
@@ -6095,10 +6054,10 @@
       <c r="C20" s="21">
         <v>1</v>
       </c>
-      <c r="D20" s="51">
+      <c r="D20" s="47">
         <v>16000</v>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="47">
         <v>16000</v>
       </c>
       <c r="F20" s="21" t="s">
@@ -6118,10 +6077,10 @@
       <c r="C21" s="21">
         <v>1</v>
       </c>
-      <c r="D21" s="51">
+      <c r="D21" s="47">
         <v>18000</v>
       </c>
-      <c r="E21" s="51">
+      <c r="E21" s="47">
         <v>18000</v>
       </c>
       <c r="F21" s="21" t="s">
@@ -6141,10 +6100,10 @@
       <c r="C22" s="21">
         <v>1</v>
       </c>
-      <c r="D22" s="51">
+      <c r="D22" s="47">
         <v>18000</v>
       </c>
-      <c r="E22" s="51">
+      <c r="E22" s="47">
         <v>18000</v>
       </c>
       <c r="F22" s="21" t="s">
@@ -6164,10 +6123,10 @@
       <c r="C23" s="21">
         <v>1</v>
       </c>
-      <c r="D23" s="51">
+      <c r="D23" s="47">
         <v>16000</v>
       </c>
-      <c r="E23" s="51">
+      <c r="E23" s="47">
         <v>16000</v>
       </c>
       <c r="F23" s="21" t="s">
@@ -6187,10 +6146,10 @@
       <c r="C24" s="21">
         <v>1</v>
       </c>
-      <c r="D24" s="51">
+      <c r="D24" s="47">
         <v>25000</v>
       </c>
-      <c r="E24" s="51">
+      <c r="E24" s="47">
         <v>25000</v>
       </c>
       <c r="F24" s="21" t="s">
@@ -6210,10 +6169,10 @@
       <c r="C25" s="21">
         <v>3</v>
       </c>
-      <c r="D25" s="51">
+      <c r="D25" s="47">
         <v>16000</v>
       </c>
-      <c r="E25" s="51">
+      <c r="E25" s="47">
         <v>48000</v>
       </c>
       <c r="F25" s="21" t="s">
@@ -6233,10 +6192,10 @@
       <c r="C26" s="21">
         <v>1</v>
       </c>
-      <c r="D26" s="51">
+      <c r="D26" s="47">
         <v>12000</v>
       </c>
-      <c r="E26" s="51">
+      <c r="E26" s="47">
         <v>12000</v>
       </c>
       <c r="F26" s="21" t="s">
@@ -6256,10 +6215,10 @@
       <c r="C27" s="21">
         <v>7</v>
       </c>
-      <c r="D27" s="51">
+      <c r="D27" s="47">
         <v>12000</v>
       </c>
-      <c r="E27" s="51">
+      <c r="E27" s="47">
         <v>84000</v>
       </c>
       <c r="F27" s="21" t="s">
@@ -6279,10 +6238,10 @@
       <c r="C28" s="21">
         <v>2</v>
       </c>
-      <c r="D28" s="51">
+      <c r="D28" s="47">
         <v>12000</v>
       </c>
-      <c r="E28" s="51">
+      <c r="E28" s="47">
         <v>24000</v>
       </c>
       <c r="F28" s="21" t="s">
@@ -6302,10 +6261,10 @@
       <c r="C29" s="21">
         <v>2</v>
       </c>
-      <c r="D29" s="51">
+      <c r="D29" s="47">
         <v>25000</v>
       </c>
-      <c r="E29" s="51">
+      <c r="E29" s="47">
         <v>50000</v>
       </c>
       <c r="F29" s="21" t="s">
@@ -6325,10 +6284,10 @@
       <c r="C30" s="21">
         <v>3</v>
       </c>
-      <c r="D30" s="51">
+      <c r="D30" s="47">
         <v>13000</v>
       </c>
-      <c r="E30" s="51">
+      <c r="E30" s="47">
         <v>39000</v>
       </c>
       <c r="F30" s="21" t="s">
@@ -6348,10 +6307,10 @@
       <c r="C31" s="21">
         <v>1</v>
       </c>
-      <c r="D31" s="51">
+      <c r="D31" s="47">
         <v>16000</v>
       </c>
-      <c r="E31" s="51">
+      <c r="E31" s="47">
         <v>16000</v>
       </c>
       <c r="F31" s="21" t="s">
@@ -6371,10 +6330,10 @@
       <c r="C32" s="21">
         <v>1</v>
       </c>
-      <c r="D32" s="51">
+      <c r="D32" s="47">
         <v>12000</v>
       </c>
-      <c r="E32" s="51">
+      <c r="E32" s="47">
         <v>12000</v>
       </c>
       <c r="F32" s="21" t="s">
@@ -6394,10 +6353,10 @@
       <c r="C33" s="21">
         <v>1</v>
       </c>
-      <c r="D33" s="51">
+      <c r="D33" s="47">
         <v>12000</v>
       </c>
-      <c r="E33" s="51">
+      <c r="E33" s="47">
         <v>12000</v>
       </c>
       <c r="F33" s="21" t="s">
@@ -6408,24 +6367,24 @@
       </c>
     </row>
     <row r="35" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A35" s="50" t="s">
+      <c r="A35" s="46" t="s">
         <v>140</v>
       </c>
-      <c r="B35" s="50"/>
-      <c r="C35" s="50"/>
-      <c r="D35" s="50"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="46"/>
+      <c r="D35" s="46"/>
     </row>
     <row r="36" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A36" s="40" t="s">
+      <c r="A36" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="B36" s="40" t="s">
+      <c r="B36" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="C36" s="40" t="s">
+      <c r="C36" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="D36" s="40" t="s">
+      <c r="D36" s="36" t="s">
         <v>80</v>
       </c>
     </row>
@@ -6444,24 +6403,24 @@
       </c>
     </row>
     <row r="39" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A39" s="50" t="s">
+      <c r="A39" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="B39" s="50"/>
-      <c r="C39" s="50"/>
-      <c r="D39" s="50"/>
+      <c r="B39" s="46"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="46"/>
     </row>
     <row r="40" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A40" s="40" t="s">
+      <c r="A40" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="B40" s="40" t="s">
+      <c r="B40" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="C40" s="40" t="s">
+      <c r="C40" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="D40" s="40" t="s">
+      <c r="D40" s="36" t="s">
         <v>146</v>
       </c>
     </row>
@@ -6977,9 +6936,9 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="39"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="35"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -6994,9 +6953,9 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="39"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="35"/>
     </row>
     <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -7011,12 +6970,12 @@
       <c r="D3" s="22">
         <v>72</v>
       </c>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29">
+      <c r="E3" s="27"/>
+      <c r="F3" s="27">
         <v>10</v>
       </c>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29">
+      <c r="G3" s="27"/>
+      <c r="H3" s="27">
         <v>14</v>
       </c>
       <c r="I3" s="11">
@@ -7027,9 +6986,9 @@
         <f t="shared" ref="J3:J42" si="0">I3*C3</f>
         <v>864000</v>
       </c>
-      <c r="L3" s="69"/>
-      <c r="M3" s="69"/>
-      <c r="N3" s="38"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="35"/>
     </row>
     <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -7042,12 +7001,12 @@
       <c r="D4" s="22">
         <v>240</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="27">
         <v>60</v>
       </c>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29">
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27">
         <v>0</v>
       </c>
       <c r="I4" s="11">
@@ -7058,9 +7017,9 @@
         <f t="shared" si="0"/>
         <v>4800000</v>
       </c>
-      <c r="L4" s="69"/>
-      <c r="M4" s="69"/>
-      <c r="N4" s="38"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="35"/>
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
@@ -7074,16 +7033,16 @@
         <f>440+80</f>
         <v>520</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="27">
         <v>100</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="27">
         <v>1</v>
       </c>
-      <c r="G5" s="29">
+      <c r="G5" s="27">
         <v>2</v>
       </c>
-      <c r="H5" s="29">
+      <c r="H5" s="27">
         <v>0</v>
       </c>
       <c r="I5" s="11">
@@ -7094,9 +7053,9 @@
         <f t="shared" si="0"/>
         <v>7404000</v>
       </c>
-      <c r="L5" s="69"/>
-      <c r="M5" s="69"/>
-      <c r="N5" s="38"/>
+      <c r="L5" s="64"/>
+      <c r="M5" s="64"/>
+      <c r="N5" s="35"/>
     </row>
     <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
@@ -7109,10 +7068,10 @@
       <c r="D6" s="22">
         <v>24</v>
       </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29">
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27">
         <v>24</v>
       </c>
       <c r="I6" s="11">
@@ -7123,9 +7082,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
-      <c r="N6" s="38"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="64"/>
+      <c r="N6" s="35"/>
     </row>
     <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
@@ -7138,10 +7097,10 @@
       <c r="D7" s="22">
         <v>24</v>
       </c>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29">
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27">
         <v>23</v>
       </c>
       <c r="I7" s="11">
@@ -7152,9 +7111,9 @@
         <f t="shared" si="0"/>
         <v>12000</v>
       </c>
-      <c r="L7" s="69"/>
-      <c r="M7" s="69"/>
-      <c r="N7" s="38"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="35"/>
     </row>
     <row r="8" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
@@ -7167,10 +7126,10 @@
       <c r="D8" s="22">
         <v>24</v>
       </c>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29">
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27">
         <v>10</v>
       </c>
       <c r="I8" s="11">
@@ -7181,9 +7140,9 @@
         <f t="shared" si="0"/>
         <v>168000</v>
       </c>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
-      <c r="N8" s="38"/>
+      <c r="L8" s="64"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="35"/>
     </row>
     <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
@@ -7196,12 +7155,12 @@
       <c r="D9" s="22">
         <v>12</v>
       </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29">
+      <c r="E9" s="27"/>
+      <c r="F9" s="27">
         <v>2</v>
       </c>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29">
+      <c r="G9" s="27"/>
+      <c r="H9" s="27">
         <v>3</v>
       </c>
       <c r="I9" s="11">
@@ -7212,9 +7171,9 @@
         <f t="shared" si="0"/>
         <v>84000</v>
       </c>
-      <c r="L9" s="69"/>
-      <c r="M9" s="69"/>
-      <c r="N9" s="38"/>
+      <c r="L9" s="64"/>
+      <c r="M9" s="64"/>
+      <c r="N9" s="35"/>
     </row>
     <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
@@ -7227,10 +7186,10 @@
       <c r="D10" s="22">
         <v>0</v>
       </c>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29">
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27">
         <v>0</v>
       </c>
       <c r="I10" s="11">
@@ -7241,9 +7200,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L10" s="69"/>
-      <c r="M10" s="69"/>
-      <c r="N10" s="38"/>
+      <c r="L10" s="64"/>
+      <c r="M10" s="64"/>
+      <c r="N10" s="35"/>
     </row>
     <row r="11" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
@@ -7256,10 +7215,10 @@
       <c r="D11" s="22">
         <v>48</v>
       </c>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32">
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30">
         <v>0</v>
       </c>
       <c r="I11" s="11">
@@ -7270,9 +7229,9 @@
         <f t="shared" si="0"/>
         <v>1200000</v>
       </c>
-      <c r="L11" s="69"/>
-      <c r="M11" s="69"/>
-      <c r="N11" s="39"/>
+      <c r="L11" s="64"/>
+      <c r="M11" s="64"/>
+      <c r="N11" s="35"/>
     </row>
     <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
@@ -7281,15 +7240,15 @@
       <c r="B12" s="16"/>
       <c r="C12" s="17"/>
       <c r="D12" s="23"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
       <c r="I12" s="18"/>
       <c r="J12" s="18"/>
-      <c r="L12" s="69"/>
-      <c r="M12" s="69"/>
-      <c r="N12" s="39"/>
+      <c r="L12" s="64"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="35"/>
     </row>
     <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
@@ -7302,12 +7261,12 @@
       <c r="D13" s="22">
         <v>240</v>
       </c>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29">
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27">
         <v>2</v>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="27">
         <v>84</v>
       </c>
       <c r="I13" s="11">
@@ -7318,9 +7277,9 @@
         <f t="shared" si="0"/>
         <v>2002000</v>
       </c>
-      <c r="L13" s="69"/>
-      <c r="M13" s="69"/>
-      <c r="N13" s="39"/>
+      <c r="L13" s="64"/>
+      <c r="M13" s="64"/>
+      <c r="N13" s="35"/>
     </row>
     <row r="14" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
@@ -7333,14 +7292,14 @@
       <c r="D14" s="22">
         <v>96</v>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="26">
         <v>48</v>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="26">
         <v>1</v>
       </c>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32">
+      <c r="G14" s="30"/>
+      <c r="H14" s="30">
         <v>46</v>
       </c>
       <c r="I14" s="11">
@@ -7351,9 +7310,9 @@
         <f t="shared" si="0"/>
         <v>1552000</v>
       </c>
-      <c r="L14" s="69"/>
-      <c r="M14" s="69"/>
-      <c r="N14" s="39"/>
+      <c r="L14" s="64"/>
+      <c r="M14" s="64"/>
+      <c r="N14" s="35"/>
     </row>
     <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
@@ -7362,15 +7321,15 @@
       <c r="B15" s="16"/>
       <c r="C15" s="17"/>
       <c r="D15" s="23"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
       <c r="I15" s="18"/>
       <c r="J15" s="18"/>
-      <c r="L15" s="69"/>
-      <c r="M15" s="69"/>
-      <c r="N15" s="39"/>
+      <c r="L15" s="64"/>
+      <c r="M15" s="64"/>
+      <c r="N15" s="35"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
@@ -7383,10 +7342,10 @@
       <c r="D16" s="22">
         <v>24</v>
       </c>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32">
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30">
         <v>19</v>
       </c>
       <c r="I16" s="11">
@@ -7397,9 +7356,9 @@
         <f t="shared" si="0"/>
         <v>125000</v>
       </c>
-      <c r="L16" s="69"/>
-      <c r="M16" s="69"/>
-      <c r="N16" s="39"/>
+      <c r="L16" s="64"/>
+      <c r="M16" s="64"/>
+      <c r="N16" s="35"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
@@ -7408,15 +7367,15 @@
       <c r="B17" s="16"/>
       <c r="C17" s="17"/>
       <c r="D17" s="23"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
       <c r="I17" s="18"/>
       <c r="J17" s="18"/>
-      <c r="L17" s="69"/>
-      <c r="M17" s="69"/>
-      <c r="N17" s="39"/>
+      <c r="L17" s="64"/>
+      <c r="M17" s="64"/>
+      <c r="N17" s="35"/>
     </row>
     <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
@@ -7429,10 +7388,10 @@
       <c r="D18" s="22">
         <v>4</v>
       </c>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29">
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27">
         <v>4</v>
       </c>
       <c r="I18" s="11">
@@ -7443,9 +7402,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L18" s="69"/>
-      <c r="M18" s="69"/>
-      <c r="N18" s="39"/>
+      <c r="L18" s="64"/>
+      <c r="M18" s="64"/>
+      <c r="N18" s="35"/>
     </row>
     <row r="19" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
@@ -7458,10 +7417,10 @@
       <c r="D19" s="22">
         <v>8</v>
       </c>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29">
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27">
         <v>7</v>
       </c>
       <c r="I19" s="11">
@@ -7472,9 +7431,9 @@
         <f t="shared" si="0"/>
         <v>360000</v>
       </c>
-      <c r="L19" s="69"/>
-      <c r="M19" s="69"/>
-      <c r="N19" s="39"/>
+      <c r="L19" s="64"/>
+      <c r="M19" s="64"/>
+      <c r="N19" s="35"/>
     </row>
     <row r="20" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
@@ -7484,13 +7443,13 @@
       <c r="C20" s="14">
         <v>260000</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="28">
         <v>4</v>
       </c>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32">
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30">
         <v>2</v>
       </c>
       <c r="I20" s="11">
@@ -7501,9 +7460,9 @@
         <f t="shared" si="0"/>
         <v>520000</v>
       </c>
-      <c r="L20" s="69"/>
-      <c r="M20" s="69"/>
-      <c r="N20" s="39"/>
+      <c r="L20" s="64"/>
+      <c r="M20" s="64"/>
+      <c r="N20" s="35"/>
     </row>
     <row r="21" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
@@ -7512,15 +7471,15 @@
       <c r="B21" s="16"/>
       <c r="C21" s="17"/>
       <c r="D21" s="23"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
       <c r="I21" s="18"/>
       <c r="J21" s="18"/>
-      <c r="L21" s="69"/>
-      <c r="M21" s="69"/>
-      <c r="N21" s="39"/>
+      <c r="L21" s="64"/>
+      <c r="M21" s="64"/>
+      <c r="N21" s="35"/>
     </row>
     <row r="22" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
@@ -7531,10 +7490,10 @@
         <v>260000</v>
       </c>
       <c r="D22" s="22"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
       <c r="I22" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -7543,9 +7502,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L22" s="69"/>
-      <c r="M22" s="69"/>
-      <c r="N22" s="39"/>
+      <c r="L22" s="64"/>
+      <c r="M22" s="64"/>
+      <c r="N22" s="35"/>
     </row>
     <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
@@ -7558,10 +7517,10 @@
       <c r="D23" s="22">
         <v>4</v>
       </c>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32">
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30">
         <v>4</v>
       </c>
       <c r="I23" s="11">
@@ -7572,9 +7531,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L23" s="72"/>
-      <c r="M23" s="72"/>
-      <c r="N23" s="39"/>
+      <c r="L23" s="66"/>
+      <c r="M23" s="66"/>
+      <c r="N23" s="35"/>
     </row>
     <row r="24" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
@@ -7583,15 +7542,15 @@
       <c r="B24" s="16"/>
       <c r="C24" s="17"/>
       <c r="D24" s="23"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
       <c r="I24" s="18"/>
       <c r="J24" s="18"/>
-      <c r="L24" s="69"/>
-      <c r="M24" s="69"/>
-      <c r="N24" s="39"/>
+      <c r="L24" s="64"/>
+      <c r="M24" s="64"/>
+      <c r="N24" s="35"/>
     </row>
     <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
@@ -7604,10 +7563,10 @@
       <c r="D25" s="22">
         <v>2</v>
       </c>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29">
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27">
         <v>2</v>
       </c>
       <c r="I25" s="11">
@@ -7618,9 +7577,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L25" s="69"/>
-      <c r="M25" s="69"/>
-      <c r="N25" s="39"/>
+      <c r="L25" s="64"/>
+      <c r="M25" s="64"/>
+      <c r="N25" s="35"/>
     </row>
     <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
@@ -7633,10 +7592,10 @@
       <c r="D26" s="22">
         <v>2</v>
       </c>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29">
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27">
         <v>2</v>
       </c>
       <c r="I26" s="11">
@@ -7647,9 +7606,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L26" s="72"/>
-      <c r="M26" s="72"/>
-      <c r="N26" s="39"/>
+      <c r="L26" s="66"/>
+      <c r="M26" s="66"/>
+      <c r="N26" s="35"/>
     </row>
     <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
@@ -7662,10 +7621,10 @@
       <c r="D27" s="22">
         <v>5</v>
       </c>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34">
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32">
         <v>5</v>
       </c>
       <c r="I27" s="11">
@@ -7676,9 +7635,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L27" s="69"/>
-      <c r="M27" s="69"/>
-      <c r="N27" s="39"/>
+      <c r="L27" s="64"/>
+      <c r="M27" s="64"/>
+      <c r="N27" s="35"/>
     </row>
     <row r="28" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
@@ -7687,15 +7646,15 @@
       <c r="B28" s="16"/>
       <c r="C28" s="17"/>
       <c r="D28" s="23"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
       <c r="I28" s="18"/>
       <c r="J28" s="18"/>
-      <c r="L28" s="69"/>
-      <c r="M28" s="69"/>
-      <c r="N28" s="39"/>
+      <c r="L28" s="64"/>
+      <c r="M28" s="64"/>
+      <c r="N28" s="35"/>
     </row>
     <row r="29" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
@@ -7708,10 +7667,10 @@
       <c r="D29" s="22">
         <v>4</v>
       </c>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29">
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27">
         <v>4</v>
       </c>
       <c r="I29" s="11">
@@ -7722,9 +7681,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L29" s="72"/>
-      <c r="M29" s="72"/>
-      <c r="N29" s="39"/>
+      <c r="L29" s="66"/>
+      <c r="M29" s="66"/>
+      <c r="N29" s="35"/>
     </row>
     <row r="30" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
@@ -7737,10 +7696,10 @@
       <c r="D30" s="22">
         <v>5</v>
       </c>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29">
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27">
         <v>5</v>
       </c>
       <c r="I30" s="11">
@@ -7751,9 +7710,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L30" s="69"/>
-      <c r="M30" s="69"/>
-      <c r="N30" s="39"/>
+      <c r="L30" s="64"/>
+      <c r="M30" s="64"/>
+      <c r="N30" s="35"/>
     </row>
     <row r="31" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
@@ -7766,10 +7725,10 @@
       <c r="D31" s="22">
         <v>15</v>
       </c>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32">
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30">
         <v>10</v>
       </c>
       <c r="I31" s="11">
@@ -7780,9 +7739,9 @@
         <f t="shared" si="0"/>
         <v>800000</v>
       </c>
-      <c r="L31" s="69"/>
-      <c r="M31" s="69"/>
-      <c r="N31" s="39"/>
+      <c r="L31" s="64"/>
+      <c r="M31" s="64"/>
+      <c r="N31" s="35"/>
     </row>
     <row r="32" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
@@ -7791,15 +7750,15 @@
       <c r="B32" s="16"/>
       <c r="C32" s="17"/>
       <c r="D32" s="23"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
       <c r="I32" s="18"/>
       <c r="J32" s="18"/>
-      <c r="L32" s="69"/>
-      <c r="M32" s="69"/>
-      <c r="N32" s="39"/>
+      <c r="L32" s="64"/>
+      <c r="M32" s="64"/>
+      <c r="N32" s="35"/>
     </row>
     <row r="33" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
@@ -7812,10 +7771,10 @@
       <c r="D33" s="22">
         <v>1</v>
       </c>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29">
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27">
         <v>1</v>
       </c>
       <c r="I33" s="11">
@@ -7826,9 +7785,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L33" s="72"/>
-      <c r="M33" s="72"/>
-      <c r="N33" s="39"/>
+      <c r="L33" s="66"/>
+      <c r="M33" s="66"/>
+      <c r="N33" s="35"/>
     </row>
     <row r="34" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
@@ -7841,10 +7800,10 @@
       <c r="D34" s="22">
         <v>5</v>
       </c>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32">
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30">
         <v>5</v>
       </c>
       <c r="I34" s="11">
@@ -7855,9 +7814,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L34" s="69"/>
-      <c r="M34" s="69"/>
-      <c r="N34" s="39"/>
+      <c r="L34" s="64"/>
+      <c r="M34" s="64"/>
+      <c r="N34" s="35"/>
     </row>
     <row r="35" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
@@ -7866,15 +7825,15 @@
       <c r="B35" s="16"/>
       <c r="C35" s="17"/>
       <c r="D35" s="24"/>
-      <c r="E35" s="35"/>
-      <c r="F35" s="35"/>
-      <c r="G35" s="33"/>
-      <c r="H35" s="33"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="33"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31"/>
       <c r="I35" s="18"/>
       <c r="J35" s="18"/>
-      <c r="L35" s="69"/>
-      <c r="M35" s="69"/>
-      <c r="N35" s="39"/>
+      <c r="L35" s="64"/>
+      <c r="M35" s="64"/>
+      <c r="N35" s="35"/>
     </row>
     <row r="36" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
@@ -7887,10 +7846,10 @@
       <c r="D36" s="22">
         <v>8</v>
       </c>
-      <c r="E36" s="29"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="29"/>
-      <c r="H36" s="29">
+      <c r="E36" s="27"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27">
         <v>6</v>
       </c>
       <c r="I36" s="11">
@@ -7901,9 +7860,9 @@
         <f t="shared" si="0"/>
         <v>360000</v>
       </c>
-      <c r="L36" s="69"/>
-      <c r="M36" s="69"/>
-      <c r="N36" s="39"/>
+      <c r="L36" s="64"/>
+      <c r="M36" s="64"/>
+      <c r="N36" s="35"/>
     </row>
     <row r="37" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
@@ -7916,10 +7875,10 @@
       <c r="D37" s="22">
         <v>12</v>
       </c>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32">
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30">
         <v>8</v>
       </c>
       <c r="I37" s="11">
@@ -7930,9 +7889,9 @@
         <f t="shared" si="0"/>
         <v>640000</v>
       </c>
-      <c r="L37" s="69"/>
-      <c r="M37" s="69"/>
-      <c r="N37" s="39"/>
+      <c r="L37" s="64"/>
+      <c r="M37" s="64"/>
+      <c r="N37" s="35"/>
     </row>
     <row r="38" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
@@ -7941,15 +7900,15 @@
       <c r="B38" s="16"/>
       <c r="C38" s="17"/>
       <c r="D38" s="24"/>
-      <c r="E38" s="35"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="33"/>
-      <c r="H38" s="33"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
       <c r="I38" s="18"/>
       <c r="J38" s="18"/>
-      <c r="L38" s="69"/>
-      <c r="M38" s="69"/>
-      <c r="N38" s="39"/>
+      <c r="L38" s="64"/>
+      <c r="M38" s="64"/>
+      <c r="N38" s="35"/>
     </row>
     <row r="39" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
@@ -7962,12 +7921,12 @@
       <c r="D39" s="22">
         <v>18</v>
       </c>
-      <c r="E39" s="29">
+      <c r="E39" s="27">
         <v>18</v>
       </c>
-      <c r="F39" s="29"/>
-      <c r="G39" s="29"/>
-      <c r="H39" s="29">
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="27">
         <v>0</v>
       </c>
       <c r="I39" s="11">
@@ -7978,9 +7937,9 @@
         <f t="shared" si="0"/>
         <v>180000</v>
       </c>
-      <c r="L39" s="69"/>
-      <c r="M39" s="69"/>
-      <c r="N39" s="39"/>
+      <c r="L39" s="64"/>
+      <c r="M39" s="64"/>
+      <c r="N39" s="35"/>
     </row>
     <row r="40" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
@@ -7993,13 +7952,13 @@
       <c r="D40" s="22">
         <v>48</v>
       </c>
-      <c r="E40" s="29">
+      <c r="E40" s="27">
         <f>48+24</f>
         <v>72</v>
       </c>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29">
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27">
         <v>34</v>
       </c>
       <c r="I40" s="11">
@@ -8010,9 +7969,9 @@
         <f t="shared" si="0"/>
         <v>172000</v>
       </c>
-      <c r="L40" s="69"/>
-      <c r="M40" s="69"/>
-      <c r="N40" s="39"/>
+      <c r="L40" s="64"/>
+      <c r="M40" s="64"/>
+      <c r="N40" s="35"/>
     </row>
     <row r="41" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
@@ -8025,12 +7984,12 @@
       <c r="D41" s="22">
         <v>20</v>
       </c>
-      <c r="E41" s="32">
+      <c r="E41" s="30">
         <v>20</v>
       </c>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32">
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="30">
         <v>6</v>
       </c>
       <c r="I41" s="11">
@@ -8041,9 +8000,9 @@
         <f t="shared" si="0"/>
         <v>510000</v>
       </c>
-      <c r="L41" s="69"/>
-      <c r="M41" s="69"/>
-      <c r="N41" s="39"/>
+      <c r="L41" s="64"/>
+      <c r="M41" s="64"/>
+      <c r="N41" s="35"/>
     </row>
     <row r="42" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
@@ -8056,14 +8015,14 @@
       <c r="D42" s="22">
         <v>6</v>
       </c>
-      <c r="E42" s="29">
+      <c r="E42" s="27">
         <v>6</v>
       </c>
-      <c r="F42" s="29"/>
-      <c r="G42" s="29">
+      <c r="F42" s="27"/>
+      <c r="G42" s="27">
         <v>1</v>
       </c>
-      <c r="H42" s="29">
+      <c r="H42" s="27">
         <v>7</v>
       </c>
       <c r="I42" s="11">
@@ -8074,9 +8033,9 @@
         <f t="shared" si="0"/>
         <v>1040000</v>
       </c>
-      <c r="L42" s="69"/>
-      <c r="M42" s="69"/>
-      <c r="N42" s="39"/>
+      <c r="L42" s="64"/>
+      <c r="M42" s="64"/>
+      <c r="N42" s="35"/>
     </row>
     <row r="43" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
@@ -8094,62 +8053,62 @@
         <f>SUM(J3:J42)</f>
         <v>22793000</v>
       </c>
-      <c r="L43" s="72"/>
-      <c r="M43" s="72"/>
-      <c r="N43" s="39"/>
+      <c r="L43" s="66"/>
+      <c r="M43" s="66"/>
+      <c r="N43" s="35"/>
     </row>
     <row r="44" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L44" s="69"/>
-      <c r="M44" s="69"/>
-      <c r="N44" s="39"/>
+      <c r="L44" s="64"/>
+      <c r="M44" s="64"/>
+      <c r="N44" s="35"/>
     </row>
     <row r="45" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L45" s="69"/>
-      <c r="M45" s="69"/>
-      <c r="N45" s="39"/>
+      <c r="L45" s="64"/>
+      <c r="M45" s="64"/>
+      <c r="N45" s="35"/>
     </row>
     <row r="46" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L46" s="68"/>
-      <c r="M46" s="70"/>
+      <c r="L46" s="63"/>
+      <c r="M46" s="64"/>
     </row>
     <row r="47" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L47" s="69"/>
-      <c r="M47" s="70"/>
+      <c r="L47" s="64"/>
+      <c r="M47" s="64"/>
     </row>
     <row r="48" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L48" s="69"/>
-      <c r="M48" s="70"/>
+      <c r="L48" s="64"/>
+      <c r="M48" s="64"/>
     </row>
     <row r="49" spans="12:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L49" s="70"/>
-      <c r="M49" s="70"/>
+      <c r="L49" s="64"/>
+      <c r="M49" s="64"/>
     </row>
     <row r="50" spans="12:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L50" s="39"/>
+      <c r="L50" s="35"/>
     </row>
     <row r="51" spans="12:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L51" s="39"/>
+      <c r="L51" s="35"/>
     </row>
     <row r="52" spans="12:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L52" s="39"/>
+      <c r="L52" s="35"/>
     </row>
     <row r="53" spans="12:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L53" s="39"/>
+      <c r="L53" s="35"/>
     </row>
     <row r="54" spans="12:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L54" s="39"/>
+      <c r="L54" s="35"/>
     </row>
     <row r="55" spans="12:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L55" s="39"/>
+      <c r="L55" s="35"/>
     </row>
     <row r="56" spans="12:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L56" s="39"/>
+      <c r="L56" s="35"/>
     </row>
     <row r="57" spans="12:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L57" s="39"/>
+      <c r="L57" s="35"/>
     </row>
     <row r="58" spans="12:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L58" s="39"/>
+      <c r="L58" s="35"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1" gridLines="1"/>
@@ -8171,36 +8130,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="G2" s="36" t="s">
         <v>80</v>
       </c>
     </row>
@@ -8214,10 +8173,10 @@
       <c r="C3" s="21">
         <v>1</v>
       </c>
-      <c r="D3" s="51">
+      <c r="D3" s="47">
         <v>12000</v>
       </c>
-      <c r="E3" s="51">
+      <c r="E3" s="47">
         <v>12000</v>
       </c>
       <c r="F3" s="21" t="s">
@@ -8237,10 +8196,10 @@
       <c r="C4" s="21">
         <v>1</v>
       </c>
-      <c r="D4" s="51">
+      <c r="D4" s="47">
         <v>16000</v>
       </c>
-      <c r="E4" s="51">
+      <c r="E4" s="47">
         <v>16000</v>
       </c>
       <c r="F4" s="21" t="s">
@@ -8260,10 +8219,10 @@
       <c r="C5" s="21">
         <v>2</v>
       </c>
-      <c r="D5" s="51">
+      <c r="D5" s="47">
         <v>12000</v>
       </c>
-      <c r="E5" s="51">
+      <c r="E5" s="47">
         <v>24000</v>
       </c>
       <c r="F5" s="21" t="s">
@@ -8283,10 +8242,10 @@
       <c r="C6" s="21">
         <v>10</v>
       </c>
-      <c r="D6" s="51">
+      <c r="D6" s="47">
         <v>18000</v>
       </c>
-      <c r="E6" s="51">
+      <c r="E6" s="47">
         <v>180000</v>
       </c>
       <c r="F6" s="21" t="s">
@@ -8297,24 +8256,24 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="46" t="s">
         <v>140</v>
       </c>
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
     </row>
     <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="40" t="s">
+      <c r="D9" s="36" t="s">
         <v>80</v>
       </c>
     </row>
@@ -8361,24 +8320,24 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
     </row>
     <row r="15" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="40" t="s">
+      <c r="D15" s="36" t="s">
         <v>146</v>
       </c>
     </row>
@@ -8911,7 +8870,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R52"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.77734375" customWidth="1"/>
@@ -8951,13 +8910,13 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="71"/>
-      <c r="O1" s="70"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="64"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
     </row>
     <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -8972,13 +8931,13 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
-      <c r="O2" s="70"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="O2" s="64"/>
+      <c r="P2" s="64"/>
+      <c r="Q2" s="64"/>
+      <c r="R2" s="64"/>
     </row>
     <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -8993,12 +8952,12 @@
       <c r="D3" s="22">
         <v>72</v>
       </c>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29">
+      <c r="E3" s="27"/>
+      <c r="F3" s="27">
         <v>7</v>
       </c>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29">
+      <c r="G3" s="27"/>
+      <c r="H3" s="27">
         <v>24</v>
       </c>
       <c r="I3" s="11">
@@ -9009,13 +8968,13 @@
         <f t="shared" ref="J3:J42" si="0">I3*C3</f>
         <v>738000</v>
       </c>
-      <c r="L3" s="69"/>
-      <c r="M3" s="69"/>
-      <c r="N3" s="69"/>
-      <c r="O3" s="70"/>
-      <c r="P3" s="69"/>
-      <c r="Q3" s="69"/>
-      <c r="R3" s="69"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -9028,12 +8987,12 @@
       <c r="D4" s="22">
         <v>240</v>
       </c>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29">
+      <c r="E4" s="27"/>
+      <c r="F4" s="27">
         <v>7</v>
       </c>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29">
+      <c r="G4" s="27"/>
+      <c r="H4" s="27">
         <v>143</v>
       </c>
       <c r="I4" s="11">
@@ -9044,13 +9003,13 @@
         <f t="shared" si="0"/>
         <v>1440000</v>
       </c>
-      <c r="L4" s="69"/>
-      <c r="M4" s="69"/>
-      <c r="N4" s="69"/>
-      <c r="O4" s="70"/>
-      <c r="P4" s="72"/>
-      <c r="Q4" s="72"/>
-      <c r="R4" s="72"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
@@ -9064,12 +9023,12 @@
         <f>440-160</f>
         <v>280</v>
       </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29">
+      <c r="E5" s="27"/>
+      <c r="F5" s="27">
         <v>17</v>
       </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29">
+      <c r="G5" s="27"/>
+      <c r="H5" s="27">
         <v>84</v>
       </c>
       <c r="I5" s="11">
@@ -9080,13 +9039,13 @@
         <f t="shared" si="0"/>
         <v>2148000</v>
       </c>
-      <c r="L5" s="69"/>
-      <c r="M5" s="69"/>
-      <c r="N5" s="69"/>
-      <c r="O5" s="70"/>
-      <c r="P5" s="69"/>
-      <c r="Q5" s="69"/>
-      <c r="R5" s="69"/>
+      <c r="L5" s="64"/>
+      <c r="M5" s="64"/>
+      <c r="N5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="64"/>
+      <c r="Q5" s="64"/>
+      <c r="R5" s="64"/>
     </row>
     <row r="6" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
@@ -9099,10 +9058,10 @@
       <c r="D6" s="22">
         <v>24</v>
       </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29">
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27">
         <v>10</v>
       </c>
       <c r="I6" s="11">
@@ -9113,13 +9072,13 @@
         <f t="shared" si="0"/>
         <v>168000</v>
       </c>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
-      <c r="N6" s="69"/>
-      <c r="O6" s="70"/>
-      <c r="P6" s="69"/>
-      <c r="Q6" s="69"/>
-      <c r="R6" s="69"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="64"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="64"/>
+      <c r="P6" s="64"/>
+      <c r="Q6" s="64"/>
+      <c r="R6" s="64"/>
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
@@ -9132,12 +9091,12 @@
       <c r="D7" s="22">
         <v>24</v>
       </c>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29">
+      <c r="E7" s="27"/>
+      <c r="F7" s="27">
         <v>4</v>
       </c>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29">
+      <c r="G7" s="27"/>
+      <c r="H7" s="27">
         <v>13</v>
       </c>
       <c r="I7" s="11">
@@ -9148,13 +9107,13 @@
         <f t="shared" si="0"/>
         <v>84000</v>
       </c>
-      <c r="L7" s="69"/>
-      <c r="M7" s="69"/>
-      <c r="N7" s="69"/>
-      <c r="O7" s="70"/>
-      <c r="P7" s="72"/>
-      <c r="Q7" s="72"/>
-      <c r="R7" s="72"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="64"/>
+      <c r="P7" s="66"/>
+      <c r="Q7" s="66"/>
+      <c r="R7" s="66"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
@@ -9167,10 +9126,10 @@
       <c r="D8" s="22">
         <v>24</v>
       </c>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29">
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27">
         <v>22</v>
       </c>
       <c r="I8" s="11">
@@ -9181,13 +9140,13 @@
         <f t="shared" si="0"/>
         <v>24000</v>
       </c>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
-      <c r="N8" s="69"/>
-      <c r="O8" s="70"/>
-      <c r="P8" s="69"/>
-      <c r="Q8" s="69"/>
-      <c r="R8" s="69"/>
+      <c r="L8" s="64"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="64"/>
+      <c r="O8" s="64"/>
+      <c r="P8" s="64"/>
+      <c r="Q8" s="64"/>
+      <c r="R8" s="64"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
@@ -9200,10 +9159,10 @@
       <c r="D9" s="22">
         <v>12</v>
       </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29">
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27">
         <v>11</v>
       </c>
       <c r="I9" s="11">
@@ -9214,13 +9173,13 @@
         <f t="shared" si="0"/>
         <v>12000</v>
       </c>
-      <c r="L9" s="69"/>
-      <c r="M9" s="69"/>
-      <c r="N9" s="69"/>
-      <c r="O9" s="70"/>
-      <c r="P9" s="69"/>
-      <c r="Q9" s="69"/>
-      <c r="R9" s="69"/>
+      <c r="L9" s="64"/>
+      <c r="M9" s="64"/>
+      <c r="N9" s="64"/>
+      <c r="O9" s="64"/>
+      <c r="P9" s="64"/>
+      <c r="Q9" s="64"/>
+      <c r="R9" s="64"/>
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
@@ -9233,10 +9192,10 @@
       <c r="D10" s="22">
         <v>0</v>
       </c>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
       <c r="I10" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -9245,13 +9204,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L10" s="69"/>
-      <c r="M10" s="69"/>
-      <c r="N10" s="69"/>
-      <c r="O10" s="70"/>
-      <c r="P10" s="69"/>
-      <c r="Q10" s="69"/>
-      <c r="R10" s="69"/>
+      <c r="L10" s="64"/>
+      <c r="M10" s="64"/>
+      <c r="N10" s="64"/>
+      <c r="O10" s="64"/>
+      <c r="P10" s="64"/>
+      <c r="Q10" s="64"/>
+      <c r="R10" s="64"/>
     </row>
     <row r="11" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
@@ -9264,12 +9223,12 @@
       <c r="D11" s="22">
         <v>48</v>
       </c>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28">
+      <c r="E11" s="26"/>
+      <c r="F11" s="26">
         <v>2</v>
       </c>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32">
+      <c r="G11" s="30"/>
+      <c r="H11" s="30">
         <v>32</v>
       </c>
       <c r="I11" s="11">
@@ -9280,13 +9239,13 @@
         <f t="shared" si="0"/>
         <v>350000</v>
       </c>
-      <c r="L11" s="69"/>
-      <c r="M11" s="69"/>
-      <c r="N11" s="69"/>
-      <c r="O11" s="70"/>
-      <c r="P11" s="72"/>
-      <c r="Q11" s="72"/>
-      <c r="R11" s="72"/>
+      <c r="L11" s="64"/>
+      <c r="M11" s="64"/>
+      <c r="N11" s="64"/>
+      <c r="O11" s="64"/>
+      <c r="P11" s="66"/>
+      <c r="Q11" s="66"/>
+      <c r="R11" s="66"/>
     </row>
     <row r="12" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
@@ -9295,19 +9254,19 @@
       <c r="B12" s="16"/>
       <c r="C12" s="17"/>
       <c r="D12" s="23"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
       <c r="J12" s="18"/>
-      <c r="L12" s="69"/>
-      <c r="M12" s="69"/>
-      <c r="N12" s="69"/>
-      <c r="O12" s="70"/>
-      <c r="P12" s="69"/>
-      <c r="Q12" s="69"/>
-      <c r="R12" s="69"/>
+      <c r="L12" s="64"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="64"/>
+      <c r="O12" s="64"/>
+      <c r="P12" s="64"/>
+      <c r="Q12" s="64"/>
+      <c r="R12" s="64"/>
     </row>
     <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
@@ -9320,10 +9279,10 @@
       <c r="D13" s="22">
         <v>240</v>
       </c>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29">
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27">
         <v>191</v>
       </c>
       <c r="I13" s="11">
@@ -9334,13 +9293,13 @@
         <f t="shared" si="0"/>
         <v>637000</v>
       </c>
-      <c r="L13" s="69"/>
-      <c r="M13" s="69"/>
-      <c r="N13" s="69"/>
-      <c r="O13" s="70"/>
-      <c r="P13" s="69"/>
-      <c r="Q13" s="69"/>
-      <c r="R13" s="69"/>
+      <c r="L13" s="64"/>
+      <c r="M13" s="64"/>
+      <c r="N13" s="64"/>
+      <c r="O13" s="64"/>
+      <c r="P13" s="64"/>
+      <c r="Q13" s="64"/>
+      <c r="R13" s="64"/>
     </row>
     <row r="14" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
@@ -9353,12 +9312,12 @@
       <c r="D14" s="22">
         <v>96</v>
       </c>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28">
+      <c r="E14" s="26"/>
+      <c r="F14" s="26">
         <v>9</v>
       </c>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32">
+      <c r="G14" s="30"/>
+      <c r="H14" s="30">
         <v>40</v>
       </c>
       <c r="I14" s="11">
@@ -9369,13 +9328,13 @@
         <f t="shared" si="0"/>
         <v>752000</v>
       </c>
-      <c r="L14" s="69"/>
-      <c r="M14" s="69"/>
-      <c r="N14" s="69"/>
-      <c r="O14" s="70"/>
-      <c r="P14" s="69"/>
-      <c r="Q14" s="69"/>
-      <c r="R14" s="69"/>
+      <c r="L14" s="64"/>
+      <c r="M14" s="64"/>
+      <c r="N14" s="64"/>
+      <c r="O14" s="64"/>
+      <c r="P14" s="64"/>
+      <c r="Q14" s="64"/>
+      <c r="R14" s="64"/>
     </row>
     <row r="15" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
@@ -9384,19 +9343,19 @@
       <c r="B15" s="16"/>
       <c r="C15" s="17"/>
       <c r="D15" s="23"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
       <c r="J15" s="18"/>
-      <c r="L15" s="69"/>
-      <c r="M15" s="69"/>
-      <c r="N15" s="69"/>
-      <c r="O15" s="70"/>
-      <c r="P15" s="69"/>
-      <c r="Q15" s="69"/>
-      <c r="R15" s="69"/>
+      <c r="L15" s="64"/>
+      <c r="M15" s="64"/>
+      <c r="N15" s="64"/>
+      <c r="O15" s="64"/>
+      <c r="P15" s="64"/>
+      <c r="Q15" s="64"/>
+      <c r="R15" s="64"/>
     </row>
     <row r="16" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
@@ -9409,10 +9368,10 @@
       <c r="D16" s="22">
         <v>24</v>
       </c>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32">
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30">
         <v>20</v>
       </c>
       <c r="I16" s="11">
@@ -9423,13 +9382,13 @@
         <f t="shared" si="0"/>
         <v>100000</v>
       </c>
-      <c r="L16" s="69"/>
-      <c r="M16" s="69"/>
-      <c r="N16" s="69"/>
-      <c r="O16" s="70"/>
-      <c r="P16" s="69"/>
-      <c r="Q16" s="69"/>
-      <c r="R16" s="69"/>
+      <c r="L16" s="64"/>
+      <c r="M16" s="64"/>
+      <c r="N16" s="64"/>
+      <c r="O16" s="64"/>
+      <c r="P16" s="64"/>
+      <c r="Q16" s="64"/>
+      <c r="R16" s="64"/>
     </row>
     <row r="17" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
@@ -9438,19 +9397,19 @@
       <c r="B17" s="16"/>
       <c r="C17" s="17"/>
       <c r="D17" s="23"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
       <c r="J17" s="18"/>
-      <c r="L17" s="69"/>
-      <c r="M17" s="69"/>
-      <c r="N17" s="69"/>
-      <c r="O17" s="70"/>
-      <c r="P17" s="69"/>
-      <c r="Q17" s="69"/>
-      <c r="R17" s="69"/>
+      <c r="L17" s="64"/>
+      <c r="M17" s="64"/>
+      <c r="N17" s="64"/>
+      <c r="O17" s="64"/>
+      <c r="P17" s="64"/>
+      <c r="Q17" s="64"/>
+      <c r="R17" s="64"/>
     </row>
     <row r="18" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
@@ -9463,10 +9422,10 @@
       <c r="D18" s="22">
         <v>4</v>
       </c>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29">
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27">
         <v>4</v>
       </c>
       <c r="I18" s="11">
@@ -9477,13 +9436,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L18" s="69"/>
-      <c r="M18" s="69"/>
-      <c r="N18" s="69"/>
-      <c r="O18" s="70"/>
-      <c r="P18" s="69"/>
-      <c r="Q18" s="69"/>
-      <c r="R18" s="69"/>
+      <c r="L18" s="64"/>
+      <c r="M18" s="64"/>
+      <c r="N18" s="64"/>
+      <c r="O18" s="64"/>
+      <c r="P18" s="64"/>
+      <c r="Q18" s="64"/>
+      <c r="R18" s="64"/>
     </row>
     <row r="19" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
@@ -9496,10 +9455,10 @@
       <c r="D19" s="22">
         <v>8</v>
       </c>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29">
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27">
         <v>6</v>
       </c>
       <c r="I19" s="11">
@@ -9510,13 +9469,13 @@
         <f t="shared" si="0"/>
         <v>720000</v>
       </c>
-      <c r="L19" s="69"/>
-      <c r="M19" s="69"/>
-      <c r="N19" s="69"/>
-      <c r="O19" s="70"/>
-      <c r="P19" s="69"/>
-      <c r="Q19" s="69"/>
-      <c r="R19" s="69"/>
+      <c r="L19" s="64"/>
+      <c r="M19" s="64"/>
+      <c r="N19" s="64"/>
+      <c r="O19" s="64"/>
+      <c r="P19" s="64"/>
+      <c r="Q19" s="64"/>
+      <c r="R19" s="64"/>
     </row>
     <row r="20" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
@@ -9526,13 +9485,13 @@
       <c r="C20" s="14">
         <v>260000</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="28">
         <v>4</v>
       </c>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32">
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30">
         <v>4</v>
       </c>
       <c r="I20" s="11">
@@ -9543,13 +9502,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L20" s="69"/>
-      <c r="M20" s="69"/>
-      <c r="N20" s="69"/>
-      <c r="O20" s="70"/>
-      <c r="P20" s="69"/>
-      <c r="Q20" s="69"/>
-      <c r="R20" s="69"/>
+      <c r="L20" s="64"/>
+      <c r="M20" s="64"/>
+      <c r="N20" s="64"/>
+      <c r="O20" s="64"/>
+      <c r="P20" s="64"/>
+      <c r="Q20" s="64"/>
+      <c r="R20" s="64"/>
     </row>
     <row r="21" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
@@ -9558,19 +9517,19 @@
       <c r="B21" s="16"/>
       <c r="C21" s="17"/>
       <c r="D21" s="23"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
       <c r="J21" s="18"/>
-      <c r="L21" s="69"/>
-      <c r="M21" s="69"/>
-      <c r="N21" s="69"/>
-      <c r="O21" s="70"/>
-      <c r="P21" s="72"/>
-      <c r="Q21" s="72"/>
-      <c r="R21" s="72"/>
+      <c r="L21" s="64"/>
+      <c r="M21" s="64"/>
+      <c r="N21" s="64"/>
+      <c r="O21" s="64"/>
+      <c r="P21" s="66"/>
+      <c r="Q21" s="66"/>
+      <c r="R21" s="66"/>
     </row>
     <row r="22" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
@@ -9581,10 +9540,10 @@
         <v>260000</v>
       </c>
       <c r="D22" s="22"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
       <c r="I22" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -9593,13 +9552,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L22" s="69"/>
-      <c r="M22" s="69"/>
-      <c r="N22" s="69"/>
-      <c r="O22" s="70"/>
-      <c r="P22" s="69"/>
-      <c r="Q22" s="69"/>
-      <c r="R22" s="69"/>
+      <c r="L22" s="64"/>
+      <c r="M22" s="64"/>
+      <c r="N22" s="64"/>
+      <c r="O22" s="64"/>
+      <c r="P22" s="64"/>
+      <c r="Q22" s="64"/>
+      <c r="R22" s="64"/>
     </row>
     <row r="23" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
@@ -9612,10 +9571,10 @@
       <c r="D23" s="22">
         <v>4</v>
       </c>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32">
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30">
         <v>1</v>
       </c>
       <c r="I23" s="11">
@@ -9626,13 +9585,13 @@
         <f t="shared" si="0"/>
         <v>480000</v>
       </c>
-      <c r="L23" s="72"/>
-      <c r="M23" s="72"/>
-      <c r="N23" s="72"/>
-      <c r="O23" s="70"/>
-      <c r="P23" s="69"/>
-      <c r="Q23" s="69"/>
-      <c r="R23" s="69"/>
+      <c r="L23" s="66"/>
+      <c r="M23" s="66"/>
+      <c r="N23" s="66"/>
+      <c r="O23" s="64"/>
+      <c r="P23" s="64"/>
+      <c r="Q23" s="64"/>
+      <c r="R23" s="64"/>
     </row>
     <row r="24" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
@@ -9641,19 +9600,19 @@
       <c r="B24" s="16"/>
       <c r="C24" s="17"/>
       <c r="D24" s="23"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="31"/>
       <c r="J24" s="18"/>
-      <c r="L24" s="69"/>
-      <c r="M24" s="69"/>
-      <c r="N24" s="69"/>
-      <c r="O24" s="70"/>
-      <c r="P24" s="68"/>
-      <c r="Q24" s="70"/>
-      <c r="R24" s="69"/>
+      <c r="L24" s="64"/>
+      <c r="M24" s="64"/>
+      <c r="N24" s="64"/>
+      <c r="O24" s="64"/>
+      <c r="P24" s="63"/>
+      <c r="Q24" s="64"/>
+      <c r="R24" s="64"/>
     </row>
     <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
@@ -9666,10 +9625,10 @@
       <c r="D25" s="22">
         <v>2</v>
       </c>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29">
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27">
         <v>1</v>
       </c>
       <c r="I25" s="11">
@@ -9680,13 +9639,13 @@
         <f t="shared" si="0"/>
         <v>800000</v>
       </c>
-      <c r="L25" s="69"/>
-      <c r="M25" s="69"/>
-      <c r="N25" s="69"/>
-      <c r="O25" s="70"/>
-      <c r="P25" s="69"/>
-      <c r="Q25" s="70"/>
-      <c r="R25" s="70"/>
+      <c r="L25" s="64"/>
+      <c r="M25" s="64"/>
+      <c r="N25" s="64"/>
+      <c r="O25" s="64"/>
+      <c r="P25" s="64"/>
+      <c r="Q25" s="64"/>
+      <c r="R25" s="64"/>
     </row>
     <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
@@ -9699,10 +9658,10 @@
       <c r="D26" s="22">
         <v>2</v>
       </c>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29">
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27">
         <v>2</v>
       </c>
       <c r="I26" s="11">
@@ -9713,13 +9672,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L26" s="72"/>
-      <c r="M26" s="72"/>
-      <c r="N26" s="72"/>
-      <c r="O26" s="70"/>
-      <c r="P26" s="70"/>
-      <c r="Q26" s="70"/>
-      <c r="R26" s="70"/>
+      <c r="L26" s="66"/>
+      <c r="M26" s="66"/>
+      <c r="N26" s="66"/>
+      <c r="O26" s="64"/>
+      <c r="P26" s="64"/>
+      <c r="Q26" s="64"/>
+      <c r="R26" s="64"/>
     </row>
     <row r="27" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
@@ -9732,10 +9691,10 @@
       <c r="D27" s="22">
         <v>5</v>
       </c>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34">
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32">
         <v>3</v>
       </c>
       <c r="I27" s="11">
@@ -9746,13 +9705,13 @@
         <f t="shared" si="0"/>
         <v>520000</v>
       </c>
-      <c r="L27" s="69"/>
-      <c r="M27" s="69"/>
-      <c r="N27" s="69"/>
-      <c r="O27" s="70"/>
-      <c r="P27" s="70"/>
-      <c r="Q27" s="70"/>
-      <c r="R27" s="70"/>
+      <c r="L27" s="64"/>
+      <c r="M27" s="64"/>
+      <c r="N27" s="64"/>
+      <c r="O27" s="64"/>
+      <c r="P27" s="64"/>
+      <c r="Q27" s="64"/>
+      <c r="R27" s="64"/>
     </row>
     <row r="28" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
@@ -9761,19 +9720,19 @@
       <c r="B28" s="16"/>
       <c r="C28" s="17"/>
       <c r="D28" s="23"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
       <c r="J28" s="18"/>
-      <c r="L28" s="69"/>
-      <c r="M28" s="69"/>
-      <c r="N28" s="69"/>
-      <c r="O28" s="70"/>
-      <c r="P28" s="70"/>
-      <c r="Q28" s="70"/>
-      <c r="R28" s="70"/>
+      <c r="L28" s="64"/>
+      <c r="M28" s="64"/>
+      <c r="N28" s="64"/>
+      <c r="O28" s="64"/>
+      <c r="P28" s="64"/>
+      <c r="Q28" s="64"/>
+      <c r="R28" s="64"/>
     </row>
     <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
@@ -9786,10 +9745,10 @@
       <c r="D29" s="22">
         <v>4</v>
       </c>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29">
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27">
         <v>3</v>
       </c>
       <c r="I29" s="11">
@@ -9800,13 +9759,13 @@
         <f t="shared" si="0"/>
         <v>350000</v>
       </c>
-      <c r="L29" s="72"/>
-      <c r="M29" s="72"/>
-      <c r="N29" s="72"/>
-      <c r="O29" s="70"/>
-      <c r="P29" s="70"/>
-      <c r="Q29" s="70"/>
-      <c r="R29" s="70"/>
+      <c r="L29" s="66"/>
+      <c r="M29" s="66"/>
+      <c r="N29" s="66"/>
+      <c r="O29" s="64"/>
+      <c r="P29" s="64"/>
+      <c r="Q29" s="64"/>
+      <c r="R29" s="64"/>
     </row>
     <row r="30" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
@@ -9819,10 +9778,10 @@
       <c r="D30" s="22">
         <v>5</v>
       </c>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29">
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27">
         <v>5</v>
       </c>
       <c r="I30" s="11">
@@ -9833,13 +9792,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L30" s="69"/>
-      <c r="M30" s="69"/>
-      <c r="N30" s="69"/>
-      <c r="O30" s="70"/>
-      <c r="P30" s="70"/>
-      <c r="Q30" s="70"/>
-      <c r="R30" s="70"/>
+      <c r="L30" s="64"/>
+      <c r="M30" s="64"/>
+      <c r="N30" s="64"/>
+      <c r="O30" s="64"/>
+      <c r="P30" s="64"/>
+      <c r="Q30" s="64"/>
+      <c r="R30" s="64"/>
     </row>
     <row r="31" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
@@ -9852,10 +9811,10 @@
       <c r="D31" s="22">
         <v>15</v>
       </c>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32">
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30">
         <v>14</v>
       </c>
       <c r="I31" s="11">
@@ -9866,13 +9825,13 @@
         <f t="shared" si="0"/>
         <v>160000</v>
       </c>
-      <c r="L31" s="69"/>
-      <c r="M31" s="69"/>
-      <c r="N31" s="69"/>
-      <c r="O31" s="70"/>
-      <c r="P31" s="70"/>
-      <c r="Q31" s="70"/>
-      <c r="R31" s="70"/>
+      <c r="L31" s="64"/>
+      <c r="M31" s="64"/>
+      <c r="N31" s="64"/>
+      <c r="O31" s="64"/>
+      <c r="P31" s="64"/>
+      <c r="Q31" s="64"/>
+      <c r="R31" s="64"/>
     </row>
     <row r="32" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
@@ -9881,19 +9840,19 @@
       <c r="B32" s="16"/>
       <c r="C32" s="17"/>
       <c r="D32" s="23"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="33"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
       <c r="J32" s="18"/>
-      <c r="L32" s="69"/>
-      <c r="M32" s="69"/>
-      <c r="N32" s="69"/>
-      <c r="O32" s="70"/>
-      <c r="P32" s="70"/>
-      <c r="Q32" s="70"/>
-      <c r="R32" s="70"/>
+      <c r="L32" s="64"/>
+      <c r="M32" s="64"/>
+      <c r="N32" s="64"/>
+      <c r="O32" s="64"/>
+      <c r="P32" s="64"/>
+      <c r="Q32" s="64"/>
+      <c r="R32" s="64"/>
     </row>
     <row r="33" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
@@ -9906,10 +9865,10 @@
       <c r="D33" s="22">
         <v>1</v>
       </c>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29">
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27">
         <v>1</v>
       </c>
       <c r="I33" s="11">
@@ -9920,13 +9879,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L33" s="72"/>
-      <c r="M33" s="72"/>
-      <c r="N33" s="72"/>
-      <c r="O33" s="70"/>
-      <c r="P33" s="70"/>
-      <c r="Q33" s="70"/>
-      <c r="R33" s="70"/>
+      <c r="L33" s="66"/>
+      <c r="M33" s="66"/>
+      <c r="N33" s="66"/>
+      <c r="O33" s="64"/>
+      <c r="P33" s="64"/>
+      <c r="Q33" s="64"/>
+      <c r="R33" s="64"/>
     </row>
     <row r="34" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
@@ -9939,12 +9898,12 @@
       <c r="D34" s="22">
         <v>5</v>
       </c>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28">
+      <c r="E34" s="26"/>
+      <c r="F34" s="26">
         <v>2</v>
       </c>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32">
+      <c r="G34" s="30"/>
+      <c r="H34" s="30">
         <v>1</v>
       </c>
       <c r="I34" s="11">
@@ -9955,13 +9914,13 @@
         <f t="shared" si="0"/>
         <v>520000</v>
       </c>
-      <c r="L34" s="69"/>
-      <c r="M34" s="69"/>
-      <c r="N34" s="69"/>
-      <c r="O34" s="70"/>
-      <c r="P34" s="70"/>
-      <c r="Q34" s="70"/>
-      <c r="R34" s="70"/>
+      <c r="L34" s="64"/>
+      <c r="M34" s="64"/>
+      <c r="N34" s="64"/>
+      <c r="O34" s="64"/>
+      <c r="P34" s="64"/>
+      <c r="Q34" s="64"/>
+      <c r="R34" s="64"/>
     </row>
     <row r="35" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
@@ -9970,19 +9929,19 @@
       <c r="B35" s="16"/>
       <c r="C35" s="17"/>
       <c r="D35" s="24"/>
-      <c r="E35" s="35"/>
-      <c r="F35" s="35"/>
-      <c r="G35" s="33"/>
-      <c r="H35" s="33"/>
-      <c r="I35" s="33"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="33"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="31"/>
       <c r="J35" s="18"/>
-      <c r="L35" s="69"/>
-      <c r="M35" s="69"/>
-      <c r="N35" s="69"/>
-      <c r="O35" s="70"/>
-      <c r="P35" s="70"/>
-      <c r="Q35" s="70"/>
-      <c r="R35" s="70"/>
+      <c r="L35" s="64"/>
+      <c r="M35" s="64"/>
+      <c r="N35" s="64"/>
+      <c r="O35" s="64"/>
+      <c r="P35" s="64"/>
+      <c r="Q35" s="64"/>
+      <c r="R35" s="64"/>
     </row>
     <row r="36" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
@@ -9995,10 +9954,10 @@
       <c r="D36" s="22">
         <v>8</v>
       </c>
-      <c r="E36" s="29"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="29"/>
-      <c r="H36" s="29">
+      <c r="E36" s="27"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27">
         <v>8</v>
       </c>
       <c r="I36" s="11">
@@ -10009,13 +9968,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L36" s="69"/>
-      <c r="M36" s="69"/>
-      <c r="N36" s="69"/>
-      <c r="O36" s="70"/>
-      <c r="P36" s="70"/>
-      <c r="Q36" s="70"/>
-      <c r="R36" s="70"/>
+      <c r="L36" s="64"/>
+      <c r="M36" s="64"/>
+      <c r="N36" s="64"/>
+      <c r="O36" s="64"/>
+      <c r="P36" s="64"/>
+      <c r="Q36" s="64"/>
+      <c r="R36" s="64"/>
     </row>
     <row r="37" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
@@ -10028,10 +9987,10 @@
       <c r="D37" s="22">
         <v>12</v>
       </c>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32">
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30">
         <v>11</v>
       </c>
       <c r="I37" s="11">
@@ -10042,13 +10001,13 @@
         <f t="shared" si="0"/>
         <v>160000</v>
       </c>
-      <c r="L37" s="69"/>
-      <c r="M37" s="69"/>
-      <c r="N37" s="69"/>
-      <c r="O37" s="70"/>
-      <c r="P37" s="70"/>
-      <c r="Q37" s="70"/>
-      <c r="R37" s="70"/>
+      <c r="L37" s="64"/>
+      <c r="M37" s="64"/>
+      <c r="N37" s="64"/>
+      <c r="O37" s="64"/>
+      <c r="P37" s="64"/>
+      <c r="Q37" s="64"/>
+      <c r="R37" s="64"/>
     </row>
     <row r="38" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
@@ -10057,19 +10016,19 @@
       <c r="B38" s="16"/>
       <c r="C38" s="17"/>
       <c r="D38" s="24"/>
-      <c r="E38" s="35"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="33"/>
-      <c r="H38" s="33"/>
-      <c r="I38" s="33"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="31"/>
       <c r="J38" s="18"/>
-      <c r="L38" s="69"/>
-      <c r="M38" s="69"/>
-      <c r="N38" s="69"/>
-      <c r="O38" s="70"/>
-      <c r="P38" s="70"/>
-      <c r="Q38" s="70"/>
-      <c r="R38" s="70"/>
+      <c r="L38" s="64"/>
+      <c r="M38" s="64"/>
+      <c r="N38" s="64"/>
+      <c r="O38" s="64"/>
+      <c r="P38" s="64"/>
+      <c r="Q38" s="64"/>
+      <c r="R38" s="64"/>
     </row>
     <row r="39" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
@@ -10082,12 +10041,12 @@
       <c r="D39" s="22">
         <v>18</v>
       </c>
-      <c r="E39" s="29">
+      <c r="E39" s="27">
         <v>18</v>
       </c>
-      <c r="F39" s="29"/>
-      <c r="G39" s="29"/>
-      <c r="H39" s="29">
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="27">
         <v>22</v>
       </c>
       <c r="I39" s="11">
@@ -10098,13 +10057,13 @@
         <f t="shared" si="0"/>
         <v>70000</v>
       </c>
-      <c r="L39" s="69"/>
-      <c r="M39" s="69"/>
-      <c r="N39" s="69"/>
-      <c r="O39" s="70"/>
-      <c r="P39" s="70"/>
-      <c r="Q39" s="70"/>
-      <c r="R39" s="70"/>
+      <c r="L39" s="64"/>
+      <c r="M39" s="64"/>
+      <c r="N39" s="64"/>
+      <c r="O39" s="64"/>
+      <c r="P39" s="64"/>
+      <c r="Q39" s="64"/>
+      <c r="R39" s="64"/>
     </row>
     <row r="40" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
@@ -10117,10 +10076,10 @@
       <c r="D40" s="22">
         <v>48</v>
       </c>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29">
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27">
         <v>29</v>
       </c>
       <c r="I40" s="11">
@@ -10131,13 +10090,13 @@
         <f t="shared" si="0"/>
         <v>38000</v>
       </c>
-      <c r="L40" s="69"/>
-      <c r="M40" s="69"/>
-      <c r="N40" s="69"/>
-      <c r="O40" s="70"/>
-      <c r="P40" s="70"/>
-      <c r="Q40" s="70"/>
-      <c r="R40" s="70"/>
+      <c r="L40" s="64"/>
+      <c r="M40" s="64"/>
+      <c r="N40" s="64"/>
+      <c r="O40" s="64"/>
+      <c r="P40" s="64"/>
+      <c r="Q40" s="64"/>
+      <c r="R40" s="64"/>
     </row>
     <row r="41" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
@@ -10150,12 +10109,12 @@
       <c r="D41" s="22">
         <v>20</v>
       </c>
-      <c r="E41" s="32"/>
-      <c r="F41" s="32">
+      <c r="E41" s="30"/>
+      <c r="F41" s="30">
         <v>2</v>
       </c>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32">
+      <c r="G41" s="30"/>
+      <c r="H41" s="30">
         <v>10</v>
       </c>
       <c r="I41" s="11">
@@ -10166,13 +10125,13 @@
         <f t="shared" si="0"/>
         <v>120000</v>
       </c>
-      <c r="L41" s="69"/>
-      <c r="M41" s="69"/>
-      <c r="N41" s="69"/>
-      <c r="O41" s="70"/>
-      <c r="P41" s="70"/>
-      <c r="Q41" s="70"/>
-      <c r="R41" s="70"/>
+      <c r="L41" s="64"/>
+      <c r="M41" s="64"/>
+      <c r="N41" s="64"/>
+      <c r="O41" s="64"/>
+      <c r="P41" s="64"/>
+      <c r="Q41" s="64"/>
+      <c r="R41" s="64"/>
     </row>
     <row r="42" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
@@ -10185,10 +10144,10 @@
       <c r="D42" s="22">
         <v>6</v>
       </c>
-      <c r="E42" s="29"/>
-      <c r="F42" s="29"/>
-      <c r="G42" s="29"/>
-      <c r="H42" s="29">
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27">
         <v>5</v>
       </c>
       <c r="I42" s="11">
@@ -10199,13 +10158,13 @@
         <f t="shared" si="0"/>
         <v>260000</v>
       </c>
-      <c r="L42" s="69"/>
-      <c r="M42" s="69"/>
-      <c r="N42" s="69"/>
-      <c r="O42" s="70"/>
-      <c r="P42" s="70"/>
-      <c r="Q42" s="70"/>
-      <c r="R42" s="70"/>
+      <c r="L42" s="64"/>
+      <c r="M42" s="64"/>
+      <c r="N42" s="64"/>
+      <c r="O42" s="64"/>
+      <c r="P42" s="64"/>
+      <c r="Q42" s="64"/>
+      <c r="R42" s="64"/>
     </row>
     <row r="43" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
@@ -10223,64 +10182,49 @@
         <f>SUM(J3:J42)</f>
         <v>10651000</v>
       </c>
-      <c r="L43" s="72"/>
-      <c r="M43" s="72"/>
-      <c r="N43" s="72"/>
-      <c r="O43" s="70"/>
-      <c r="P43" s="70"/>
-      <c r="Q43" s="70"/>
-      <c r="R43" s="70"/>
+      <c r="L43" s="66"/>
+      <c r="M43" s="66"/>
+      <c r="N43" s="66"/>
+      <c r="O43" s="64"/>
+      <c r="P43" s="64"/>
+      <c r="Q43" s="64"/>
+      <c r="R43" s="64"/>
     </row>
     <row r="44" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L44" s="69"/>
-      <c r="M44" s="69"/>
-      <c r="N44" s="69"/>
-      <c r="O44" s="70"/>
-      <c r="P44" s="70"/>
-      <c r="Q44" s="70"/>
-      <c r="R44" s="70"/>
+      <c r="L44" s="64"/>
+      <c r="M44" s="64"/>
+      <c r="N44" s="64"/>
+      <c r="O44" s="64"/>
+      <c r="P44" s="64"/>
+      <c r="Q44" s="64"/>
+      <c r="R44" s="64"/>
     </row>
     <row r="45" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L45" s="69"/>
-      <c r="M45" s="69"/>
-      <c r="N45" s="69"/>
-      <c r="O45" s="70"/>
-      <c r="P45" s="70"/>
-      <c r="Q45" s="70"/>
-      <c r="R45" s="70"/>
+      <c r="L45" s="64"/>
+      <c r="M45" s="64"/>
+      <c r="N45" s="64"/>
+      <c r="O45" s="64"/>
+      <c r="P45" s="64"/>
+      <c r="Q45" s="64"/>
+      <c r="R45" s="64"/>
     </row>
     <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L46" s="68"/>
-      <c r="M46" s="70"/>
-      <c r="N46" s="69"/>
-      <c r="O46" s="70"/>
-      <c r="P46" s="70"/>
-      <c r="Q46" s="70"/>
-      <c r="R46" s="70"/>
+      <c r="L46" s="63"/>
+      <c r="M46" s="64"/>
+      <c r="N46" s="64"/>
+      <c r="O46" s="64"/>
+      <c r="P46" s="64"/>
+      <c r="Q46" s="64"/>
+      <c r="R46" s="64"/>
     </row>
     <row r="47" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L47" s="69"/>
-      <c r="M47" s="70"/>
-      <c r="N47" s="70"/>
-      <c r="O47" s="70"/>
-      <c r="P47" s="70"/>
-      <c r="Q47" s="70"/>
-      <c r="R47" s="70"/>
-    </row>
-    <row r="48" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L48" s="25"/>
-    </row>
-    <row r="49" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L49" s="26"/>
-    </row>
-    <row r="50" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L50" s="26"/>
-    </row>
-    <row r="51" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L51" s="26"/>
-    </row>
-    <row r="52" spans="12:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L52" s="26"/>
+      <c r="L47" s="64"/>
+      <c r="M47" s="64"/>
+      <c r="N47" s="64"/>
+      <c r="O47" s="64"/>
+      <c r="P47" s="64"/>
+      <c r="Q47" s="64"/>
+      <c r="R47" s="64"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1" gridLines="1"/>
@@ -10301,36 +10245,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="G2" s="36" t="s">
         <v>80</v>
       </c>
     </row>
@@ -10344,10 +10288,10 @@
       <c r="C3" s="21">
         <v>2</v>
       </c>
-      <c r="D3" s="51">
+      <c r="D3" s="47">
         <v>15000</v>
       </c>
-      <c r="E3" s="51">
+      <c r="E3" s="47">
         <v>30000</v>
       </c>
       <c r="F3" s="21" t="s">
@@ -10367,10 +10311,10 @@
       <c r="C4" s="21">
         <v>5</v>
       </c>
-      <c r="D4" s="51">
+      <c r="D4" s="47">
         <v>18000</v>
       </c>
-      <c r="E4" s="51">
+      <c r="E4" s="47">
         <v>90000</v>
       </c>
       <c r="F4" s="21" t="s">
@@ -10390,10 +10334,10 @@
       <c r="C5" s="21">
         <v>5</v>
       </c>
-      <c r="D5" s="51">
+      <c r="D5" s="47">
         <v>16000</v>
       </c>
-      <c r="E5" s="51">
+      <c r="E5" s="47">
         <v>80000</v>
       </c>
       <c r="F5" s="21" t="s">
@@ -10413,10 +10357,10 @@
       <c r="C6" s="21">
         <v>2</v>
       </c>
-      <c r="D6" s="51">
+      <c r="D6" s="47">
         <v>16000</v>
       </c>
-      <c r="E6" s="51">
+      <c r="E6" s="47">
         <v>32000</v>
       </c>
       <c r="F6" s="21" t="s">
@@ -10436,10 +10380,10 @@
       <c r="C7" s="21">
         <v>4</v>
       </c>
-      <c r="D7" s="51">
+      <c r="D7" s="47">
         <v>12000</v>
       </c>
-      <c r="E7" s="51">
+      <c r="E7" s="47">
         <v>48000</v>
       </c>
       <c r="F7" s="21" t="s">
@@ -10459,10 +10403,10 @@
       <c r="C8" s="21">
         <v>2</v>
       </c>
-      <c r="D8" s="51">
+      <c r="D8" s="47">
         <v>12000</v>
       </c>
-      <c r="E8" s="51">
+      <c r="E8" s="47">
         <v>24000</v>
       </c>
       <c r="F8" s="21" t="s">
@@ -10482,10 +10426,10 @@
       <c r="C9" s="21">
         <v>4</v>
       </c>
-      <c r="D9" s="51">
+      <c r="D9" s="47">
         <v>12000</v>
       </c>
-      <c r="E9" s="51">
+      <c r="E9" s="47">
         <v>48000</v>
       </c>
       <c r="F9" s="21" t="s">
@@ -10505,10 +10449,10 @@
       <c r="C10" s="21">
         <v>2</v>
       </c>
-      <c r="D10" s="51">
+      <c r="D10" s="47">
         <v>12000</v>
       </c>
-      <c r="E10" s="51">
+      <c r="E10" s="47">
         <v>24000</v>
       </c>
       <c r="F10" s="21" t="s">
@@ -10528,10 +10472,10 @@
       <c r="C11" s="21">
         <v>1</v>
       </c>
-      <c r="D11" s="51">
+      <c r="D11" s="47">
         <v>16000</v>
       </c>
-      <c r="E11" s="51">
+      <c r="E11" s="47">
         <v>16000</v>
       </c>
       <c r="F11" s="21" t="s">
@@ -10551,10 +10495,10 @@
       <c r="C12" s="21">
         <v>1</v>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="47">
         <v>16000</v>
       </c>
-      <c r="E12" s="51">
+      <c r="E12" s="47">
         <v>16000</v>
       </c>
       <c r="F12" s="21" t="s">
@@ -10574,10 +10518,10 @@
       <c r="C13" s="21">
         <v>1</v>
       </c>
-      <c r="D13" s="51">
+      <c r="D13" s="47">
         <v>25000</v>
       </c>
-      <c r="E13" s="51">
+      <c r="E13" s="47">
         <v>25000</v>
       </c>
       <c r="F13" s="21" t="s">
@@ -10597,10 +10541,10 @@
       <c r="C14" s="21">
         <v>1</v>
       </c>
-      <c r="D14" s="51">
+      <c r="D14" s="47">
         <v>260000</v>
       </c>
-      <c r="E14" s="51">
+      <c r="E14" s="47">
         <v>260000</v>
       </c>
       <c r="F14" s="21" t="s">
@@ -10620,10 +10564,10 @@
       <c r="C15" s="21">
         <v>2</v>
       </c>
-      <c r="D15" s="51">
+      <c r="D15" s="47">
         <v>12000</v>
       </c>
-      <c r="E15" s="51">
+      <c r="E15" s="47">
         <v>24000</v>
       </c>
       <c r="F15" s="21" t="s">
@@ -10643,10 +10587,10 @@
       <c r="C16" s="21">
         <v>1</v>
       </c>
-      <c r="D16" s="51">
+      <c r="D16" s="47">
         <v>260000</v>
       </c>
-      <c r="E16" s="51">
+      <c r="E16" s="47">
         <v>260000</v>
       </c>
       <c r="F16" s="21" t="s">
@@ -10666,10 +10610,10 @@
       <c r="C17" s="21">
         <v>2</v>
       </c>
-      <c r="D17" s="51">
+      <c r="D17" s="47">
         <v>12000</v>
       </c>
-      <c r="E17" s="51">
+      <c r="E17" s="47">
         <v>24000</v>
       </c>
       <c r="F17" s="21" t="s">
@@ -10689,10 +10633,10 @@
       <c r="C18" s="21">
         <v>1</v>
       </c>
-      <c r="D18" s="51">
+      <c r="D18" s="47">
         <v>12000</v>
       </c>
-      <c r="E18" s="51">
+      <c r="E18" s="47">
         <v>12000</v>
       </c>
       <c r="F18" s="21" t="s">
@@ -10712,10 +10656,10 @@
       <c r="C19" s="21">
         <v>1</v>
       </c>
-      <c r="D19" s="51">
+      <c r="D19" s="47">
         <v>16000</v>
       </c>
-      <c r="E19" s="51">
+      <c r="E19" s="47">
         <v>16000</v>
       </c>
       <c r="F19" s="21" t="s">
@@ -10735,10 +10679,10 @@
       <c r="C20" s="21">
         <v>1</v>
       </c>
-      <c r="D20" s="51">
+      <c r="D20" s="47">
         <v>18000</v>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="47">
         <v>18000</v>
       </c>
       <c r="F20" s="21" t="s">
@@ -10758,10 +10702,10 @@
       <c r="C21" s="21">
         <v>1</v>
       </c>
-      <c r="D21" s="51">
+      <c r="D21" s="47">
         <v>25000</v>
       </c>
-      <c r="E21" s="51">
+      <c r="E21" s="47">
         <v>25000</v>
       </c>
       <c r="F21" s="21" t="s">
@@ -10781,10 +10725,10 @@
       <c r="C22" s="21">
         <v>1</v>
       </c>
-      <c r="D22" s="51">
+      <c r="D22" s="47">
         <v>18000</v>
       </c>
-      <c r="E22" s="51">
+      <c r="E22" s="47">
         <v>18000</v>
       </c>
       <c r="F22" s="21" t="s">
@@ -10804,10 +10748,10 @@
       <c r="C23" s="21">
         <v>1</v>
       </c>
-      <c r="D23" s="51">
+      <c r="D23" s="47">
         <v>16000</v>
       </c>
-      <c r="E23" s="51">
+      <c r="E23" s="47">
         <v>16000</v>
       </c>
       <c r="F23" s="21" t="s">
@@ -10827,10 +10771,10 @@
       <c r="C24" s="21">
         <v>1</v>
       </c>
-      <c r="D24" s="51">
+      <c r="D24" s="47">
         <v>16000</v>
       </c>
-      <c r="E24" s="51">
+      <c r="E24" s="47">
         <v>16000</v>
       </c>
       <c r="F24" s="21" t="s">
@@ -10850,10 +10794,10 @@
       <c r="C25" s="21">
         <v>2</v>
       </c>
-      <c r="D25" s="51">
+      <c r="D25" s="47">
         <v>16000</v>
       </c>
-      <c r="E25" s="51">
+      <c r="E25" s="47">
         <v>32000</v>
       </c>
       <c r="F25" s="21" t="s">
@@ -10873,10 +10817,10 @@
       <c r="C26" s="21">
         <v>3</v>
       </c>
-      <c r="D26" s="51">
+      <c r="D26" s="47">
         <v>12000</v>
       </c>
-      <c r="E26" s="51">
+      <c r="E26" s="47">
         <v>36000</v>
       </c>
       <c r="F26" s="21" t="s">
@@ -10896,10 +10840,10 @@
       <c r="C27" s="21">
         <v>2</v>
       </c>
-      <c r="D27" s="51">
+      <c r="D27" s="47">
         <v>16000</v>
       </c>
-      <c r="E27" s="51">
+      <c r="E27" s="47">
         <v>32000</v>
       </c>
       <c r="F27" s="21" t="s">
@@ -10919,10 +10863,10 @@
       <c r="C28" s="21">
         <v>1</v>
       </c>
-      <c r="D28" s="51">
+      <c r="D28" s="47">
         <v>12000</v>
       </c>
-      <c r="E28" s="51">
+      <c r="E28" s="47">
         <v>12000</v>
       </c>
       <c r="F28" s="21" t="s">
@@ -10933,24 +10877,24 @@
       </c>
     </row>
     <row r="30" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A30" s="50" t="s">
+      <c r="A30" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="B30" s="50"/>
-      <c r="C30" s="50"/>
-      <c r="D30" s="50"/>
+      <c r="B30" s="46"/>
+      <c r="C30" s="46"/>
+      <c r="D30" s="46"/>
     </row>
     <row r="31" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A31" s="40" t="s">
+      <c r="A31" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="B31" s="40" t="s">
+      <c r="B31" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="C31" s="40" t="s">
+      <c r="C31" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="40" t="s">
+      <c r="D31" s="36" t="s">
         <v>146</v>
       </c>
     </row>
